--- a/MAXIMETRO_GRUPO_ALBACETE_medias.xlsx
+++ b/MAXIMETRO_GRUPO_ALBACETE_medias.xlsx
@@ -82,7 +82,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,66 +507,66 @@
     <col width="17.36328125" bestFit="1" customWidth="1" min="20" max="20"/>
     <col width="15.08984375" bestFit="1" customWidth="1" min="21" max="26"/>
     <col width="24.6328125" bestFit="1" customWidth="1" min="27" max="32"/>
-    <col width="27.1796875" bestFit="1" customWidth="1" min="33" max="33"/>
-    <col width="30.08984375" bestFit="1" customWidth="1" min="34" max="34"/>
-    <col width="28.453125" bestFit="1" customWidth="1" min="35" max="35"/>
-    <col width="16.90625" bestFit="1" customWidth="1" min="36" max="36"/>
-    <col width="16.81640625" bestFit="1" customWidth="1" min="37" max="37"/>
-    <col width="25.54296875" bestFit="1" customWidth="1" min="38" max="38"/>
-    <col width="11" bestFit="1" customWidth="1" min="39" max="39"/>
-    <col width="16.36328125" bestFit="1" customWidth="1" min="40" max="40"/>
-    <col width="19.90625" bestFit="1" customWidth="1" min="41" max="41"/>
-    <col width="15" bestFit="1" customWidth="1" min="42" max="42"/>
-    <col width="22.6328125" bestFit="1" customWidth="1" min="43" max="43"/>
-    <col width="17" bestFit="1" customWidth="1" min="44" max="44"/>
-    <col width="16.36328125" bestFit="1" customWidth="1" min="45" max="45"/>
-    <col width="25.7265625" bestFit="1" customWidth="1" min="46" max="46"/>
-    <col width="9.6328125" bestFit="1" customWidth="1" min="47" max="47"/>
-    <col width="16.453125" bestFit="1" customWidth="1" min="48" max="48"/>
-    <col width="17" bestFit="1" customWidth="1" min="49" max="49"/>
-    <col width="9.81640625" bestFit="1" customWidth="1" min="50" max="50"/>
-    <col width="15.54296875" bestFit="1" customWidth="1" min="51" max="51"/>
-    <col width="18" bestFit="1" customWidth="1" min="52" max="52"/>
-    <col width="28.36328125" bestFit="1" customWidth="1" min="53" max="53"/>
-    <col width="5.08984375" bestFit="1" customWidth="1" min="54" max="54"/>
-    <col width="23.81640625" bestFit="1" customWidth="1" min="55" max="55"/>
-    <col width="12.7265625" bestFit="1" customWidth="1" min="56" max="56"/>
-    <col width="23.08984375" bestFit="1" customWidth="1" min="57" max="57"/>
-    <col width="24.36328125" bestFit="1" customWidth="1" min="58" max="58"/>
-    <col width="17.90625" bestFit="1" customWidth="1" min="59" max="59"/>
-    <col width="23.26953125" bestFit="1" customWidth="1" min="60" max="60"/>
-    <col width="18.453125" bestFit="1" customWidth="1" min="61" max="61"/>
-    <col width="19.6328125" bestFit="1" customWidth="1" min="62" max="62"/>
-    <col width="20.36328125" bestFit="1" customWidth="1" min="63" max="63"/>
-    <col width="18.36328125" bestFit="1" customWidth="1" min="64" max="64"/>
-    <col width="18.08984375" bestFit="1" customWidth="1" min="65" max="65"/>
-    <col width="19.90625" bestFit="1" customWidth="1" min="66" max="66"/>
-    <col width="22" bestFit="1" customWidth="1" min="67" max="67"/>
-    <col width="9.08984375" bestFit="1" customWidth="1" min="68" max="68"/>
-    <col width="5.54296875" bestFit="1" customWidth="1" min="69" max="69"/>
-    <col width="11.36328125" bestFit="1" customWidth="1" min="70" max="70"/>
-    <col width="7.6328125" bestFit="1" customWidth="1" min="71" max="71"/>
-    <col width="9.6328125" bestFit="1" customWidth="1" min="72" max="72"/>
-    <col width="6.36328125" bestFit="1" customWidth="1" min="73" max="73"/>
-    <col width="8.1796875" bestFit="1" customWidth="1" min="74" max="74"/>
-    <col width="12.1796875" bestFit="1" customWidth="1" min="75" max="75"/>
-    <col width="17.1796875" bestFit="1" customWidth="1" min="76" max="76"/>
-    <col width="22.81640625" bestFit="1" customWidth="1" min="77" max="77"/>
-    <col width="17.54296875" bestFit="1" customWidth="1" min="78" max="78"/>
-    <col width="10.54296875" bestFit="1" customWidth="1" min="79" max="79"/>
-    <col width="19.54296875" bestFit="1" customWidth="1" min="80" max="80"/>
-    <col width="22.90625" bestFit="1" customWidth="1" min="81" max="81"/>
-    <col width="13.54296875" bestFit="1" customWidth="1" min="82" max="82"/>
-    <col width="13.81640625" bestFit="1" customWidth="1" min="83" max="83"/>
-    <col width="11.453125" bestFit="1" customWidth="1" min="84" max="84"/>
-    <col width="20.36328125" bestFit="1" customWidth="1" min="85" max="85"/>
-    <col width="15.26953125" bestFit="1" customWidth="1" min="86" max="86"/>
-    <col width="22" customWidth="1" min="87" max="87"/>
-    <col width="22" customWidth="1" min="88" max="88"/>
-    <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="22" customWidth="1" min="91" max="91"/>
-    <col width="22" customWidth="1" min="92" max="92"/>
+    <col width="22" bestFit="1" customWidth="1" min="33" max="33"/>
+    <col width="22" bestFit="1" customWidth="1" min="34" max="34"/>
+    <col width="22" bestFit="1" customWidth="1" min="35" max="35"/>
+    <col width="22" bestFit="1" customWidth="1" min="36" max="36"/>
+    <col width="22" bestFit="1" customWidth="1" min="37" max="37"/>
+    <col width="22" bestFit="1" customWidth="1" min="38" max="38"/>
+    <col width="27.1796875" bestFit="1" customWidth="1" min="39" max="39"/>
+    <col width="30.08984375" bestFit="1" customWidth="1" min="40" max="40"/>
+    <col width="28.453125" bestFit="1" customWidth="1" min="41" max="41"/>
+    <col width="16.90625" bestFit="1" customWidth="1" min="42" max="42"/>
+    <col width="16.81640625" bestFit="1" customWidth="1" min="43" max="43"/>
+    <col width="25.54296875" bestFit="1" customWidth="1" min="44" max="44"/>
+    <col width="11" bestFit="1" customWidth="1" min="45" max="45"/>
+    <col width="16.36328125" bestFit="1" customWidth="1" min="46" max="46"/>
+    <col width="19.90625" bestFit="1" customWidth="1" min="47" max="47"/>
+    <col width="15" bestFit="1" customWidth="1" min="48" max="48"/>
+    <col width="22.6328125" bestFit="1" customWidth="1" min="49" max="49"/>
+    <col width="17" bestFit="1" customWidth="1" min="50" max="50"/>
+    <col width="16.36328125" bestFit="1" customWidth="1" min="51" max="51"/>
+    <col width="25.7265625" bestFit="1" customWidth="1" min="52" max="52"/>
+    <col width="9.6328125" bestFit="1" customWidth="1" min="53" max="53"/>
+    <col width="16.453125" bestFit="1" customWidth="1" min="54" max="54"/>
+    <col width="17" bestFit="1" customWidth="1" min="55" max="55"/>
+    <col width="9.81640625" bestFit="1" customWidth="1" min="56" max="56"/>
+    <col width="15.54296875" bestFit="1" customWidth="1" min="57" max="57"/>
+    <col width="18" bestFit="1" customWidth="1" min="58" max="58"/>
+    <col width="28.36328125" bestFit="1" customWidth="1" min="59" max="59"/>
+    <col width="5.08984375" bestFit="1" customWidth="1" min="60" max="60"/>
+    <col width="23.81640625" bestFit="1" customWidth="1" min="61" max="61"/>
+    <col width="12.7265625" bestFit="1" customWidth="1" min="62" max="62"/>
+    <col width="23.08984375" bestFit="1" customWidth="1" min="63" max="63"/>
+    <col width="24.36328125" bestFit="1" customWidth="1" min="64" max="64"/>
+    <col width="17.90625" bestFit="1" customWidth="1" min="65" max="65"/>
+    <col width="23.26953125" bestFit="1" customWidth="1" min="66" max="66"/>
+    <col width="18.453125" bestFit="1" customWidth="1" min="67" max="67"/>
+    <col width="19.6328125" bestFit="1" customWidth="1" min="68" max="68"/>
+    <col width="20.36328125" bestFit="1" customWidth="1" min="69" max="69"/>
+    <col width="18.36328125" bestFit="1" customWidth="1" min="70" max="70"/>
+    <col width="18.08984375" bestFit="1" customWidth="1" min="71" max="71"/>
+    <col width="19.90625" bestFit="1" customWidth="1" min="72" max="72"/>
+    <col width="22" bestFit="1" customWidth="1" min="73" max="73"/>
+    <col width="9.08984375" bestFit="1" customWidth="1" min="74" max="74"/>
+    <col width="5.54296875" bestFit="1" customWidth="1" min="75" max="75"/>
+    <col width="11.36328125" bestFit="1" customWidth="1" min="76" max="76"/>
+    <col width="7.6328125" bestFit="1" customWidth="1" min="77" max="77"/>
+    <col width="9.6328125" bestFit="1" customWidth="1" min="78" max="78"/>
+    <col width="6.36328125" bestFit="1" customWidth="1" min="79" max="79"/>
+    <col width="8.1796875" bestFit="1" customWidth="1" min="80" max="80"/>
+    <col width="12.1796875" bestFit="1" customWidth="1" min="81" max="81"/>
+    <col width="17.1796875" bestFit="1" customWidth="1" min="82" max="82"/>
+    <col width="22.81640625" bestFit="1" customWidth="1" min="83" max="83"/>
+    <col width="17.54296875" bestFit="1" customWidth="1" min="84" max="84"/>
+    <col width="10.54296875" bestFit="1" customWidth="1" min="85" max="85"/>
+    <col width="19.54296875" bestFit="1" customWidth="1" min="86" max="86"/>
+    <col width="22.90625" customWidth="1" min="87" max="87"/>
+    <col width="13.54296875" customWidth="1" min="88" max="88"/>
+    <col width="13.81640625" customWidth="1" min="89" max="89"/>
+    <col width="11.453125" customWidth="1" min="90" max="90"/>
+    <col width="20.36328125" customWidth="1" min="91" max="91"/>
+    <col width="15.26953125" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -730,302 +732,302 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>Media Maximetro P1 (sin 0s)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Media Maximetro P2 (sin 0s)</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Media Maximetro P3 (sin 0s)</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Media Maximetro P4 (sin 0s)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Media Maximetro P5 (sin 0s)</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Media Maximetro P6 (sin 0s)</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>Fecha Ultimo Movimiento Contrato</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Fecha Ultimo Cambio Comercializador</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Fecha Limite Derechos Reconocidos</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Fecha Ultima Lectura</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Informacion Impagos</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Importe Deposito Garantia Euros</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Tipo Id Titular</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Es Vivienda Habitual</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Codigo Comercializadora</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Codigo Telegestion</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Codigo Fases Equipo Medida</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Codigo Autoconsumo</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Codigo TipoContrato</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Codigo Periodicidad Facturacion</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Codigo BIE</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Fecha Emision BIE</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Fecha Caducidad BIE</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Codigo APM</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Fecha Emision APM</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Fecha Caducidad APM</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Relacion Transformacion Intensidad</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>CNAE</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Codigo Modo Control Potencia</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Potencia CGPW</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Codigo DH Equipo De Medida</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Codigo Accesibilidad Contador</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Codigo PS Contratable</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Motivo Estado No Contratable</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>Codigo Tension Medida</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Codigo Clase Expediente</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Codigo Motivo Expediente</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Codigo Tipo Suministro</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Aplicacion Bono Social</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Descripcion Provincia PS</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>Descripcion Municipio PS</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Tipo Via PS</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Via PS</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Num Finca PS</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Portal PS</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>Escalera PS</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>Piso PS</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Puerta PS</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Codigo Presion</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Codigo Peaje En Vigor</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>Caudal Maximo Diario En Wh</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>Caudal Horario En Wh</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>Derecho TUR</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>Fecha Ultima Inspeccion</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>Codigo Resultado Inspeccion</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>Codigo Contador</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>Calibre Contador</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>Tipo Contador</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>Propiedad Equipo Medida</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Codigo Telemedida</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>Media Maximetro P1 (sin 0s)</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>Media Maximetro P2 (sin 0s)</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>Media Maximetro P3 (sin 0s)</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>Media Maximetro P4 (sin 0s)</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>Media Maximetro P5 (sin 0s)</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>Media Maximetro P6 (sin 0s)</t>
         </is>
       </c>
     </row>
@@ -1138,99 +1140,117 @@
       <c r="AF2" s="2" t="n">
         <v>17.32</v>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AG2" s="6">
+        <f>IFERROR(AVERAGEIF(P34:P71,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH2" s="6">
+        <f>IFERROR(AVERAGEIF(Q34:Q71,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI2" s="6">
+        <f>IFERROR(AVERAGEIF(R34:R71,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ2" s="6">
+        <f>IFERROR(AVERAGEIF(S34:S71,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK2" s="6">
+        <f>IFERROR(AVERAGEIF(T34:T71,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL2" s="6">
+        <f>IFERROR(AVERAGEIF(U34:U71,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>2025-10-28T00:00:00</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>2025-10-28T00:00:00</t>
         </is>
       </c>
-      <c r="AI2" s="3" t="n"/>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AO2" s="3" t="n"/>
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM2" s="3" t="n"/>
-      <c r="AN2" s="3" t="n"/>
-      <c r="AO2" s="3" t="n"/>
-      <c r="AP2" s="2" t="n">
+      <c r="AS2" s="3" t="n"/>
+      <c r="AT2" s="3" t="n"/>
+      <c r="AU2" s="3" t="n"/>
+      <c r="AV2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="n">
+      <c r="AX2" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AS2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="3" t="n"/>
-      <c r="AV2" s="3" t="n"/>
-      <c r="AW2" s="3" t="n"/>
-      <c r="AX2" s="3" t="n"/>
-      <c r="AY2" s="3" t="n"/>
-      <c r="AZ2" s="3" t="n"/>
+      <c r="AY2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA2" s="3" t="n"/>
-      <c r="BB2" s="2" t="n">
-        <v>9531</v>
-      </c>
+      <c r="BB2" s="3" t="n"/>
       <c r="BC2" s="3" t="n"/>
       <c r="BD2" s="3" t="n"/>
       <c r="BE2" s="3" t="n"/>
       <c r="BF2" s="3" t="n"/>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH2" s="3" t="n"/>
-      <c r="BI2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG2" s="3" t="n"/>
+      <c r="BH2" s="2" t="n">
+        <v>9531</v>
+      </c>
+      <c r="BI2" s="3" t="n"/>
       <c r="BJ2" s="3" t="n"/>
       <c r="BK2" s="3" t="n"/>
       <c r="BL2" s="3" t="n"/>
       <c r="BM2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN2" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO2" s="2" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN2" s="3" t="n"/>
+      <c r="BO2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP2" s="3" t="n"/>
       <c r="BQ2" s="3" t="n"/>
       <c r="BR2" s="3" t="n"/>
-      <c r="BS2" s="3" t="n"/>
-      <c r="BT2" s="3" t="n"/>
-      <c r="BU2" s="3" t="n"/>
+      <c r="BS2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT2" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU2" s="2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
       <c r="BV2" s="3" t="n"/>
       <c r="BW2" s="3" t="n"/>
       <c r="BX2" s="3" t="n"/>
@@ -1244,30 +1264,12 @@
       <c r="CF2" s="3" t="n"/>
       <c r="CG2" s="3" t="n"/>
       <c r="CH2" s="3" t="n"/>
-      <c r="CI2" s="6">
-        <f>IFERROR(AVERAGEIF(P34:P71,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ2" s="6">
-        <f>IFERROR(AVERAGEIF(Q34:Q71,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK2" s="6">
-        <f>IFERROR(AVERAGEIF(R34:R71,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL2" s="6">
-        <f>IFERROR(AVERAGEIF(S34:S71,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM2" s="6">
-        <f>IFERROR(AVERAGEIF(T34:T71,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN2" s="6">
-        <f>IFERROR(AVERAGEIF(U34:U71,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI2" s="3" t="n"/>
+      <c r="CJ2" s="3" t="n"/>
+      <c r="CK2" s="3" t="n"/>
+      <c r="CL2" s="3" t="n"/>
+      <c r="CM2" s="3" t="n"/>
+      <c r="CN2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1378,103 +1380,121 @@
       <c r="AF3" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="AG3" s="2" t="inlineStr">
+      <c r="AG3" s="6">
+        <f>IFERROR(AVERAGEIF(P73:P110,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH3" s="6">
+        <f>IFERROR(AVERAGEIF(Q73:Q110,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI3" s="6">
+        <f>IFERROR(AVERAGEIF(R73:R110,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="6">
+        <f>IFERROR(AVERAGEIF(S73:S110,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK3" s="6">
+        <f>IFERROR(AVERAGEIF(T73:T110,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL3" s="6">
+        <f>IFERROR(AVERAGEIF(U73:U110,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="inlineStr">
+      <c r="AN3" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AI3" s="2" t="inlineStr">
+      <c r="AO3" s="2" t="inlineStr">
         <is>
           <t>2027-01-10T00:00:00</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK3" s="2" t="inlineStr">
+      <c r="AQ3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL3" s="2" t="inlineStr">
+      <c r="AR3" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="n"/>
-      <c r="AN3" s="3" t="n"/>
-      <c r="AO3" s="3" t="n"/>
-      <c r="AP3" s="2" t="n">
+      <c r="AS3" s="3" t="n"/>
+      <c r="AT3" s="3" t="n"/>
+      <c r="AU3" s="3" t="n"/>
+      <c r="AV3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ3" s="2" t="inlineStr">
+      <c r="AW3" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="3" t="n"/>
-      <c r="AV3" s="3" t="n"/>
-      <c r="AW3" s="3" t="n"/>
-      <c r="AX3" s="3" t="n"/>
-      <c r="AY3" s="3" t="n"/>
-      <c r="AZ3" s="3" t="n"/>
+      <c r="AX3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA3" s="3" t="n"/>
-      <c r="BB3" s="2" t="n">
-        <v>5210</v>
-      </c>
+      <c r="BB3" s="3" t="n"/>
       <c r="BC3" s="3" t="n"/>
       <c r="BD3" s="3" t="n"/>
       <c r="BE3" s="3" t="n"/>
       <c r="BF3" s="3" t="n"/>
-      <c r="BG3" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH3" s="3" t="n"/>
-      <c r="BI3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG3" s="3" t="n"/>
+      <c r="BH3" s="2" t="n">
+        <v>5210</v>
+      </c>
+      <c r="BI3" s="3" t="n"/>
       <c r="BJ3" s="3" t="n"/>
       <c r="BK3" s="3" t="n"/>
       <c r="BL3" s="3" t="n"/>
       <c r="BM3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN3" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO3" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN3" s="3" t="n"/>
+      <c r="BO3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP3" s="3" t="n"/>
       <c r="BQ3" s="3" t="n"/>
       <c r="BR3" s="3" t="n"/>
-      <c r="BS3" s="3" t="n"/>
-      <c r="BT3" s="3" t="n"/>
-      <c r="BU3" s="3" t="n"/>
+      <c r="BS3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT3" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU3" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BV3" s="3" t="n"/>
       <c r="BW3" s="3" t="n"/>
       <c r="BX3" s="3" t="n"/>
@@ -1488,30 +1508,12 @@
       <c r="CF3" s="3" t="n"/>
       <c r="CG3" s="3" t="n"/>
       <c r="CH3" s="3" t="n"/>
-      <c r="CI3" s="6">
-        <f>IFERROR(AVERAGEIF(P73:P110,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ3" s="6">
-        <f>IFERROR(AVERAGEIF(Q73:Q110,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK3" s="6">
-        <f>IFERROR(AVERAGEIF(R73:R110,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL3" s="6">
-        <f>IFERROR(AVERAGEIF(S73:S110,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM3" s="6">
-        <f>IFERROR(AVERAGEIF(T73:T110,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN3" s="6">
-        <f>IFERROR(AVERAGEIF(U73:U110,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI3" s="3" t="n"/>
+      <c r="CJ3" s="3" t="n"/>
+      <c r="CK3" s="3" t="n"/>
+      <c r="CL3" s="3" t="n"/>
+      <c r="CM3" s="3" t="n"/>
+      <c r="CN3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1616,101 +1618,119 @@
       <c r="AF4" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AG4" s="6">
+        <f>IFERROR(AVERAGEIF(P112:P146,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH4" s="6">
+        <f>IFERROR(AVERAGEIF(Q112:Q146,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI4" s="6">
+        <f>IFERROR(AVERAGEIF(R112:R146,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="6">
+        <f>IFERROR(AVERAGEIF(S112:S146,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK4" s="6">
+        <f>IFERROR(AVERAGEIF(T112:T146,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL4" s="6">
+        <f>IFERROR(AVERAGEIF(U112:U146,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
         <is>
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr">
+      <c r="AN4" s="2" t="inlineStr">
         <is>
           <t>2022-05-28T00:00:00</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="n"/>
-      <c r="AJ4" s="2" t="inlineStr">
+      <c r="AO4" s="3" t="n"/>
+      <c r="AP4" s="2" t="inlineStr">
         <is>
           <t>2026-05-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK4" s="2" t="inlineStr">
+      <c r="AQ4" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL4" s="2" t="inlineStr">
+      <c r="AR4" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="n"/>
-      <c r="AN4" s="3" t="n"/>
-      <c r="AO4" s="3" t="n"/>
-      <c r="AP4" s="2" t="n">
+      <c r="AS4" s="3" t="n"/>
+      <c r="AT4" s="3" t="n"/>
+      <c r="AU4" s="3" t="n"/>
+      <c r="AV4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AQ4" s="2" t="inlineStr">
+      <c r="AW4" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="2" t="n">
+      <c r="AX4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AT4" s="2" t="n">
+      <c r="AZ4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" s="3" t="n"/>
-      <c r="AV4" s="3" t="n"/>
-      <c r="AW4" s="3" t="n"/>
-      <c r="AX4" s="3" t="n"/>
-      <c r="AY4" s="3" t="n"/>
-      <c r="AZ4" s="3" t="n"/>
-      <c r="BA4" s="2" t="inlineStr">
-        <is>
-          <t>100/5</t>
-        </is>
-      </c>
-      <c r="BB4" s="2" t="n">
-        <v>3511</v>
-      </c>
-      <c r="BC4" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="BA4" s="3" t="n"/>
+      <c r="BB4" s="3" t="n"/>
+      <c r="BC4" s="3" t="n"/>
       <c r="BD4" s="3" t="n"/>
       <c r="BE4" s="3" t="n"/>
       <c r="BF4" s="3" t="n"/>
-      <c r="BG4" s="3" t="n"/>
-      <c r="BH4" s="3" t="n"/>
+      <c r="BG4" s="2" t="inlineStr">
+        <is>
+          <t>100/5</t>
+        </is>
+      </c>
+      <c r="BH4" s="2" t="n">
+        <v>3511</v>
+      </c>
       <c r="BI4" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="BJ4" s="3" t="n"/>
       <c r="BK4" s="3" t="n"/>
       <c r="BL4" s="3" t="n"/>
-      <c r="BM4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN4" s="2" t="inlineStr">
-        <is>
-          <t>TOLEDO</t>
-        </is>
-      </c>
-      <c r="BO4" s="2" t="inlineStr">
-        <is>
-          <t>Villafranca de los Caballeros</t>
-        </is>
+      <c r="BM4" s="3" t="n"/>
+      <c r="BN4" s="3" t="n"/>
+      <c r="BO4" s="2" t="n">
+        <v>26</v>
       </c>
       <c r="BP4" s="3" t="n"/>
       <c r="BQ4" s="3" t="n"/>
       <c r="BR4" s="3" t="n"/>
-      <c r="BS4" s="3" t="n"/>
-      <c r="BT4" s="3" t="n"/>
-      <c r="BU4" s="3" t="n"/>
+      <c r="BS4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT4" s="2" t="inlineStr">
+        <is>
+          <t>TOLEDO</t>
+        </is>
+      </c>
+      <c r="BU4" s="2" t="inlineStr">
+        <is>
+          <t>Villafranca de los Caballeros</t>
+        </is>
+      </c>
       <c r="BV4" s="3" t="n"/>
       <c r="BW4" s="3" t="n"/>
       <c r="BX4" s="3" t="n"/>
@@ -1724,30 +1744,12 @@
       <c r="CF4" s="3" t="n"/>
       <c r="CG4" s="3" t="n"/>
       <c r="CH4" s="3" t="n"/>
-      <c r="CI4" s="6">
-        <f>IFERROR(AVERAGEIF(P112:P146,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ4" s="6">
-        <f>IFERROR(AVERAGEIF(Q112:Q146,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK4" s="6">
-        <f>IFERROR(AVERAGEIF(R112:R146,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL4" s="6">
-        <f>IFERROR(AVERAGEIF(S112:S146,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM4" s="6">
-        <f>IFERROR(AVERAGEIF(T112:T146,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN4" s="6">
-        <f>IFERROR(AVERAGEIF(U112:U146,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI4" s="3" t="n"/>
+      <c r="CJ4" s="3" t="n"/>
+      <c r="CK4" s="3" t="n"/>
+      <c r="CL4" s="3" t="n"/>
+      <c r="CM4" s="3" t="n"/>
+      <c r="CN4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1858,99 +1860,117 @@
       <c r="AF5" s="2" t="n">
         <v>17.32</v>
       </c>
-      <c r="AG5" s="2" t="inlineStr">
+      <c r="AG5" s="6">
+        <f>IFERROR(AVERAGEIF(P148:P182,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH5" s="6">
+        <f>IFERROR(AVERAGEIF(Q148:Q182,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI5" s="6">
+        <f>IFERROR(AVERAGEIF(R148:R182,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="6">
+        <f>IFERROR(AVERAGEIF(S148:S182,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK5" s="6">
+        <f>IFERROR(AVERAGEIF(T148:T182,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL5" s="6">
+        <f>IFERROR(AVERAGEIF(U148:U182,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
         <is>
           <t>2026-02-28T00:00:00</t>
         </is>
       </c>
-      <c r="AH5" s="2" t="inlineStr">
+      <c r="AN5" s="2" t="inlineStr">
         <is>
           <t>2021-11-22T00:00:00</t>
         </is>
       </c>
-      <c r="AI5" s="3" t="n"/>
-      <c r="AJ5" s="2" t="inlineStr">
+      <c r="AO5" s="3" t="n"/>
+      <c r="AP5" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK5" s="2" t="inlineStr">
+      <c r="AQ5" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL5" s="2" t="inlineStr">
+      <c r="AR5" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM5" s="3" t="n"/>
-      <c r="AN5" s="3" t="n"/>
-      <c r="AO5" s="3" t="n"/>
-      <c r="AP5" s="2" t="n">
+      <c r="AS5" s="3" t="n"/>
+      <c r="AT5" s="3" t="n"/>
+      <c r="AU5" s="3" t="n"/>
+      <c r="AV5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ5" s="2" t="inlineStr">
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="3" t="n"/>
-      <c r="AV5" s="3" t="n"/>
-      <c r="AW5" s="3" t="n"/>
-      <c r="AX5" s="3" t="n"/>
-      <c r="AY5" s="3" t="n"/>
-      <c r="AZ5" s="3" t="n"/>
+      <c r="AX5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA5" s="3" t="n"/>
-      <c r="BB5" s="2" t="n">
-        <v>9820</v>
-      </c>
+      <c r="BB5" s="3" t="n"/>
       <c r="BC5" s="3" t="n"/>
       <c r="BD5" s="3" t="n"/>
       <c r="BE5" s="3" t="n"/>
       <c r="BF5" s="3" t="n"/>
-      <c r="BG5" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH5" s="3" t="n"/>
-      <c r="BI5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG5" s="3" t="n"/>
+      <c r="BH5" s="2" t="n">
+        <v>9820</v>
+      </c>
+      <c r="BI5" s="3" t="n"/>
       <c r="BJ5" s="3" t="n"/>
       <c r="BK5" s="3" t="n"/>
       <c r="BL5" s="3" t="n"/>
       <c r="BM5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN5" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO5" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN5" s="3" t="n"/>
+      <c r="BO5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP5" s="3" t="n"/>
       <c r="BQ5" s="3" t="n"/>
       <c r="BR5" s="3" t="n"/>
-      <c r="BS5" s="3" t="n"/>
-      <c r="BT5" s="3" t="n"/>
-      <c r="BU5" s="3" t="n"/>
+      <c r="BS5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT5" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU5" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BV5" s="3" t="n"/>
       <c r="BW5" s="3" t="n"/>
       <c r="BX5" s="3" t="n"/>
@@ -1964,30 +1984,12 @@
       <c r="CF5" s="3" t="n"/>
       <c r="CG5" s="3" t="n"/>
       <c r="CH5" s="3" t="n"/>
-      <c r="CI5" s="6">
-        <f>IFERROR(AVERAGEIF(P148:P182,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ5" s="6">
-        <f>IFERROR(AVERAGEIF(Q148:Q182,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK5" s="6">
-        <f>IFERROR(AVERAGEIF(R148:R182,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL5" s="6">
-        <f>IFERROR(AVERAGEIF(S148:S182,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM5" s="6">
-        <f>IFERROR(AVERAGEIF(T148:T182,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN5" s="6">
-        <f>IFERROR(AVERAGEIF(U148:U182,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI5" s="3" t="n"/>
+      <c r="CJ5" s="3" t="n"/>
+      <c r="CK5" s="3" t="n"/>
+      <c r="CL5" s="3" t="n"/>
+      <c r="CM5" s="3" t="n"/>
+      <c r="CN5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2098,99 +2100,117 @@
       <c r="AF6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG6" s="2" t="inlineStr">
+      <c r="AG6" s="6">
+        <f>IFERROR(AVERAGEIF(P184:P218,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH6" s="6">
+        <f>IFERROR(AVERAGEIF(Q184:Q218,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI6" s="6">
+        <f>IFERROR(AVERAGEIF(R184:R218,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="6">
+        <f>IFERROR(AVERAGEIF(S184:S218,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK6" s="6">
+        <f>IFERROR(AVERAGEIF(T184:T218,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL6" s="6">
+        <f>IFERROR(AVERAGEIF(U184:U218,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
         <is>
           <t>2021-05-31T00:00:00</t>
         </is>
       </c>
-      <c r="AH6" s="2" t="inlineStr">
+      <c r="AN6" s="2" t="inlineStr">
         <is>
           <t>2018-05-22T00:00:00</t>
         </is>
       </c>
-      <c r="AI6" s="3" t="n"/>
-      <c r="AJ6" s="2" t="inlineStr">
+      <c r="AO6" s="3" t="n"/>
+      <c r="AP6" s="2" t="inlineStr">
         <is>
           <t>2026-08-02T00:00:00</t>
         </is>
       </c>
-      <c r="AK6" s="2" t="inlineStr">
+      <c r="AQ6" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL6" s="2" t="inlineStr">
+      <c r="AR6" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM6" s="3" t="n"/>
-      <c r="AN6" s="3" t="n"/>
-      <c r="AO6" s="3" t="n"/>
-      <c r="AP6" s="2" t="n">
+      <c r="AS6" s="3" t="n"/>
+      <c r="AT6" s="3" t="n"/>
+      <c r="AU6" s="3" t="n"/>
+      <c r="AV6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ6" s="2" t="inlineStr">
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AR6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="3" t="n"/>
-      <c r="AV6" s="3" t="n"/>
-      <c r="AW6" s="3" t="n"/>
-      <c r="AX6" s="3" t="n"/>
-      <c r="AY6" s="3" t="n"/>
-      <c r="AZ6" s="3" t="n"/>
+      <c r="AX6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA6" s="3" t="n"/>
-      <c r="BB6" s="2" t="n">
-        <v>9820</v>
-      </c>
+      <c r="BB6" s="3" t="n"/>
       <c r="BC6" s="3" t="n"/>
       <c r="BD6" s="3" t="n"/>
       <c r="BE6" s="3" t="n"/>
       <c r="BF6" s="3" t="n"/>
-      <c r="BG6" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="n"/>
-      <c r="BI6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG6" s="3" t="n"/>
+      <c r="BH6" s="2" t="n">
+        <v>9820</v>
+      </c>
+      <c r="BI6" s="3" t="n"/>
       <c r="BJ6" s="3" t="n"/>
       <c r="BK6" s="3" t="n"/>
       <c r="BL6" s="3" t="n"/>
       <c r="BM6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN6" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO6" s="2" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN6" s="3" t="n"/>
+      <c r="BO6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP6" s="3" t="n"/>
       <c r="BQ6" s="3" t="n"/>
       <c r="BR6" s="3" t="n"/>
-      <c r="BS6" s="3" t="n"/>
-      <c r="BT6" s="3" t="n"/>
-      <c r="BU6" s="3" t="n"/>
+      <c r="BS6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT6" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU6" s="2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
       <c r="BV6" s="3" t="n"/>
       <c r="BW6" s="3" t="n"/>
       <c r="BX6" s="3" t="n"/>
@@ -2204,30 +2224,12 @@
       <c r="CF6" s="3" t="n"/>
       <c r="CG6" s="3" t="n"/>
       <c r="CH6" s="3" t="n"/>
-      <c r="CI6" s="6">
-        <f>IFERROR(AVERAGEIF(P184:P218,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ6" s="6">
-        <f>IFERROR(AVERAGEIF(Q184:Q218,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK6" s="6">
-        <f>IFERROR(AVERAGEIF(R184:R218,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL6" s="6">
-        <f>IFERROR(AVERAGEIF(S184:S218,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM6" s="6">
-        <f>IFERROR(AVERAGEIF(T184:T218,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN6" s="6">
-        <f>IFERROR(AVERAGEIF(U184:U218,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI6" s="3" t="n"/>
+      <c r="CJ6" s="3" t="n"/>
+      <c r="CK6" s="3" t="n"/>
+      <c r="CL6" s="3" t="n"/>
+      <c r="CM6" s="3" t="n"/>
+      <c r="CN6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2338,99 +2340,117 @@
       <c r="AF7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AG7" s="2" t="inlineStr">
+      <c r="AG7" s="6">
+        <f>IFERROR(AVERAGEIF(P220:P255,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH7" s="6">
+        <f>IFERROR(AVERAGEIF(Q220:Q255,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI7" s="6">
+        <f>IFERROR(AVERAGEIF(R220:R255,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="6">
+        <f>IFERROR(AVERAGEIF(S220:S255,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK7" s="6">
+        <f>IFERROR(AVERAGEIF(T220:T255,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL7" s="6">
+        <f>IFERROR(AVERAGEIF(U220:U255,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
         <is>
           <t>2025-10-28T00:00:00</t>
         </is>
       </c>
-      <c r="AH7" s="2" t="inlineStr">
+      <c r="AN7" s="2" t="inlineStr">
         <is>
           <t>2025-10-28T00:00:00</t>
         </is>
       </c>
-      <c r="AI7" s="3" t="n"/>
-      <c r="AJ7" s="2" t="inlineStr">
+      <c r="AO7" s="3" t="n"/>
+      <c r="AP7" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK7" s="2" t="inlineStr">
+      <c r="AQ7" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL7" s="2" t="inlineStr">
+      <c r="AR7" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM7" s="3" t="n"/>
-      <c r="AN7" s="3" t="n"/>
-      <c r="AO7" s="3" t="n"/>
-      <c r="AP7" s="2" t="n">
+      <c r="AS7" s="3" t="n"/>
+      <c r="AT7" s="3" t="n"/>
+      <c r="AU7" s="3" t="n"/>
+      <c r="AV7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ7" s="2" t="inlineStr">
+      <c r="AW7" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR7" s="2" t="n">
+      <c r="AX7" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AS7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="3" t="n"/>
-      <c r="AV7" s="3" t="n"/>
-      <c r="AW7" s="3" t="n"/>
-      <c r="AX7" s="3" t="n"/>
-      <c r="AY7" s="3" t="n"/>
-      <c r="AZ7" s="3" t="n"/>
+      <c r="AY7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA7" s="3" t="n"/>
-      <c r="BB7" s="2" t="n">
-        <v>4321</v>
-      </c>
+      <c r="BB7" s="3" t="n"/>
       <c r="BC7" s="3" t="n"/>
       <c r="BD7" s="3" t="n"/>
       <c r="BE7" s="3" t="n"/>
       <c r="BF7" s="3" t="n"/>
-      <c r="BG7" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="n"/>
-      <c r="BI7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG7" s="3" t="n"/>
+      <c r="BH7" s="2" t="n">
+        <v>4321</v>
+      </c>
+      <c r="BI7" s="3" t="n"/>
       <c r="BJ7" s="3" t="n"/>
       <c r="BK7" s="3" t="n"/>
       <c r="BL7" s="3" t="n"/>
       <c r="BM7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN7" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO7" s="2" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN7" s="3" t="n"/>
+      <c r="BO7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP7" s="3" t="n"/>
       <c r="BQ7" s="3" t="n"/>
       <c r="BR7" s="3" t="n"/>
-      <c r="BS7" s="3" t="n"/>
-      <c r="BT7" s="3" t="n"/>
-      <c r="BU7" s="3" t="n"/>
+      <c r="BS7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT7" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU7" s="2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
       <c r="BV7" s="3" t="n"/>
       <c r="BW7" s="3" t="n"/>
       <c r="BX7" s="3" t="n"/>
@@ -2444,30 +2464,12 @@
       <c r="CF7" s="3" t="n"/>
       <c r="CG7" s="3" t="n"/>
       <c r="CH7" s="3" t="n"/>
-      <c r="CI7" s="6">
-        <f>IFERROR(AVERAGEIF(P220:P255,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ7" s="6">
-        <f>IFERROR(AVERAGEIF(Q220:Q255,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK7" s="6">
-        <f>IFERROR(AVERAGEIF(R220:R255,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL7" s="6">
-        <f>IFERROR(AVERAGEIF(S220:S255,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM7" s="6">
-        <f>IFERROR(AVERAGEIF(T220:T255,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN7" s="6">
-        <f>IFERROR(AVERAGEIF(U220:U255,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI7" s="3" t="n"/>
+      <c r="CJ7" s="3" t="n"/>
+      <c r="CK7" s="3" t="n"/>
+      <c r="CL7" s="3" t="n"/>
+      <c r="CM7" s="3" t="n"/>
+      <c r="CN7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2578,103 +2580,121 @@
       <c r="AF8" s="2" t="n">
         <v>15.01</v>
       </c>
-      <c r="AG8" s="2" t="inlineStr">
+      <c r="AG8" s="6">
+        <f>IFERROR(AVERAGEIF(P257:P292,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH8" s="6">
+        <f>IFERROR(AVERAGEIF(Q257:Q292,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI8" s="6">
+        <f>IFERROR(AVERAGEIF(R257:R292,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="6">
+        <f>IFERROR(AVERAGEIF(S257:S292,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK8" s="6">
+        <f>IFERROR(AVERAGEIF(T257:T292,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL8" s="6">
+        <f>IFERROR(AVERAGEIF(U257:U292,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM8" s="2" t="inlineStr">
         <is>
           <t>2024-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AH8" s="2" t="inlineStr">
+      <c r="AN8" s="2" t="inlineStr">
         <is>
           <t>2024-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AI8" s="2" t="inlineStr">
+      <c r="AO8" s="2" t="inlineStr">
         <is>
           <t>2027-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK8" s="2" t="inlineStr">
+      <c r="AQ8" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL8" s="2" t="inlineStr">
+      <c r="AR8" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM8" s="3" t="n"/>
-      <c r="AN8" s="3" t="n"/>
-      <c r="AO8" s="3" t="n"/>
-      <c r="AP8" s="2" t="n">
+      <c r="AS8" s="3" t="n"/>
+      <c r="AT8" s="3" t="n"/>
+      <c r="AU8" s="3" t="n"/>
+      <c r="AV8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ8" s="2" t="inlineStr">
+      <c r="AW8" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="3" t="n"/>
-      <c r="AV8" s="3" t="n"/>
-      <c r="AW8" s="3" t="n"/>
-      <c r="AX8" s="3" t="n"/>
-      <c r="AY8" s="3" t="n"/>
-      <c r="AZ8" s="3" t="n"/>
+      <c r="AX8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA8" s="3" t="n"/>
-      <c r="BB8" s="2" t="n">
-        <v>4321</v>
-      </c>
+      <c r="BB8" s="3" t="n"/>
       <c r="BC8" s="3" t="n"/>
       <c r="BD8" s="3" t="n"/>
       <c r="BE8" s="3" t="n"/>
       <c r="BF8" s="3" t="n"/>
-      <c r="BG8" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH8" s="3" t="n"/>
-      <c r="BI8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG8" s="3" t="n"/>
+      <c r="BH8" s="2" t="n">
+        <v>4321</v>
+      </c>
+      <c r="BI8" s="3" t="n"/>
       <c r="BJ8" s="3" t="n"/>
       <c r="BK8" s="3" t="n"/>
       <c r="BL8" s="3" t="n"/>
       <c r="BM8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN8" s="2" t="inlineStr">
-        <is>
-          <t>MADRID</t>
-        </is>
-      </c>
-      <c r="BO8" s="2" t="inlineStr">
-        <is>
-          <t>Camarma de Esteruelas</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN8" s="3" t="n"/>
+      <c r="BO8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP8" s="3" t="n"/>
       <c r="BQ8" s="3" t="n"/>
       <c r="BR8" s="3" t="n"/>
-      <c r="BS8" s="3" t="n"/>
-      <c r="BT8" s="3" t="n"/>
-      <c r="BU8" s="3" t="n"/>
+      <c r="BS8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT8" s="2" t="inlineStr">
+        <is>
+          <t>MADRID</t>
+        </is>
+      </c>
+      <c r="BU8" s="2" t="inlineStr">
+        <is>
+          <t>Camarma de Esteruelas</t>
+        </is>
+      </c>
       <c r="BV8" s="3" t="n"/>
       <c r="BW8" s="3" t="n"/>
       <c r="BX8" s="3" t="n"/>
@@ -2688,30 +2708,12 @@
       <c r="CF8" s="3" t="n"/>
       <c r="CG8" s="3" t="n"/>
       <c r="CH8" s="3" t="n"/>
-      <c r="CI8" s="6">
-        <f>IFERROR(AVERAGEIF(P257:P292,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ8" s="6">
-        <f>IFERROR(AVERAGEIF(Q257:Q292,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK8" s="6">
-        <f>IFERROR(AVERAGEIF(R257:R292,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL8" s="6">
-        <f>IFERROR(AVERAGEIF(S257:S292,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM8" s="6">
-        <f>IFERROR(AVERAGEIF(T257:T292,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN8" s="6">
-        <f>IFERROR(AVERAGEIF(U257:U292,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI8" s="3" t="n"/>
+      <c r="CJ8" s="3" t="n"/>
+      <c r="CK8" s="3" t="n"/>
+      <c r="CL8" s="3" t="n"/>
+      <c r="CM8" s="3" t="n"/>
+      <c r="CN8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2822,99 +2824,117 @@
       <c r="AF9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AG9" s="2" t="inlineStr">
+      <c r="AG9" s="6">
+        <f>IFERROR(AVERAGEIF(P294:P329,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH9" s="6">
+        <f>IFERROR(AVERAGEIF(Q294:Q329,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI9" s="6">
+        <f>IFERROR(AVERAGEIF(R294:R329,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="6">
+        <f>IFERROR(AVERAGEIF(S294:S329,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK9" s="6">
+        <f>IFERROR(AVERAGEIF(T294:T329,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL9" s="6">
+        <f>IFERROR(AVERAGEIF(U294:U329,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
         <is>
           <t>2024-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AH9" s="2" t="inlineStr">
+      <c r="AN9" s="2" t="inlineStr">
         <is>
           <t>2024-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AI9" s="3" t="n"/>
-      <c r="AJ9" s="2" t="inlineStr">
+      <c r="AO9" s="3" t="n"/>
+      <c r="AP9" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK9" s="2" t="inlineStr">
+      <c r="AQ9" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL9" s="2" t="inlineStr">
+      <c r="AR9" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM9" s="3" t="n"/>
-      <c r="AN9" s="3" t="n"/>
-      <c r="AO9" s="3" t="n"/>
-      <c r="AP9" s="2" t="n">
+      <c r="AS9" s="3" t="n"/>
+      <c r="AT9" s="3" t="n"/>
+      <c r="AU9" s="3" t="n"/>
+      <c r="AV9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ9" s="2" t="inlineStr">
+      <c r="AW9" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="3" t="n"/>
-      <c r="AV9" s="3" t="n"/>
-      <c r="AW9" s="3" t="n"/>
-      <c r="AX9" s="3" t="n"/>
-      <c r="AY9" s="3" t="n"/>
-      <c r="AZ9" s="3" t="n"/>
+      <c r="AX9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA9" s="3" t="n"/>
-      <c r="BB9" s="2" t="n">
-        <v>4321</v>
-      </c>
+      <c r="BB9" s="3" t="n"/>
       <c r="BC9" s="3" t="n"/>
       <c r="BD9" s="3" t="n"/>
       <c r="BE9" s="3" t="n"/>
       <c r="BF9" s="3" t="n"/>
-      <c r="BG9" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH9" s="3" t="n"/>
-      <c r="BI9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG9" s="3" t="n"/>
+      <c r="BH9" s="2" t="n">
+        <v>4321</v>
+      </c>
+      <c r="BI9" s="3" t="n"/>
       <c r="BJ9" s="3" t="n"/>
       <c r="BK9" s="3" t="n"/>
       <c r="BL9" s="3" t="n"/>
       <c r="BM9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN9" s="2" t="inlineStr">
-        <is>
-          <t>MADRID</t>
-        </is>
-      </c>
-      <c r="BO9" s="2" t="inlineStr">
-        <is>
-          <t>Camarma de Esteruelas</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN9" s="3" t="n"/>
+      <c r="BO9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP9" s="3" t="n"/>
       <c r="BQ9" s="3" t="n"/>
       <c r="BR9" s="3" t="n"/>
-      <c r="BS9" s="3" t="n"/>
-      <c r="BT9" s="3" t="n"/>
-      <c r="BU9" s="3" t="n"/>
+      <c r="BS9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT9" s="2" t="inlineStr">
+        <is>
+          <t>MADRID</t>
+        </is>
+      </c>
+      <c r="BU9" s="2" t="inlineStr">
+        <is>
+          <t>Camarma de Esteruelas</t>
+        </is>
+      </c>
       <c r="BV9" s="3" t="n"/>
       <c r="BW9" s="3" t="n"/>
       <c r="BX9" s="3" t="n"/>
@@ -2928,30 +2948,12 @@
       <c r="CF9" s="3" t="n"/>
       <c r="CG9" s="3" t="n"/>
       <c r="CH9" s="3" t="n"/>
-      <c r="CI9" s="6">
-        <f>IFERROR(AVERAGEIF(P294:P329,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ9" s="6">
-        <f>IFERROR(AVERAGEIF(Q294:Q329,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK9" s="6">
-        <f>IFERROR(AVERAGEIF(R294:R329,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL9" s="6">
-        <f>IFERROR(AVERAGEIF(S294:S329,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM9" s="6">
-        <f>IFERROR(AVERAGEIF(T294:T329,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN9" s="6">
-        <f>IFERROR(AVERAGEIF(U294:U329,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI9" s="3" t="n"/>
+      <c r="CJ9" s="3" t="n"/>
+      <c r="CK9" s="3" t="n"/>
+      <c r="CL9" s="3" t="n"/>
+      <c r="CM9" s="3" t="n"/>
+      <c r="CN9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3062,99 +3064,117 @@
       <c r="AF10" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="AG10" s="2" t="inlineStr">
+      <c r="AG10" s="6">
+        <f>IFERROR(AVERAGEIF(P331:P368,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH10" s="6">
+        <f>IFERROR(AVERAGEIF(Q331:Q368,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI10" s="6">
+        <f>IFERROR(AVERAGEIF(R331:R368,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="6">
+        <f>IFERROR(AVERAGEIF(S331:S368,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK10" s="6">
+        <f>IFERROR(AVERAGEIF(T331:T368,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL10" s="6">
+        <f>IFERROR(AVERAGEIF(U331:U368,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM10" s="2" t="inlineStr">
         <is>
           <t>2025-10-22T00:00:00</t>
         </is>
       </c>
-      <c r="AH10" s="2" t="inlineStr">
+      <c r="AN10" s="2" t="inlineStr">
         <is>
           <t>2025-10-22T00:00:00</t>
         </is>
       </c>
-      <c r="AI10" s="3" t="n"/>
-      <c r="AJ10" s="2" t="inlineStr">
+      <c r="AO10" s="3" t="n"/>
+      <c r="AP10" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK10" s="2" t="inlineStr">
+      <c r="AQ10" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL10" s="2" t="inlineStr">
+      <c r="AR10" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM10" s="3" t="n"/>
-      <c r="AN10" s="3" t="n"/>
-      <c r="AO10" s="3" t="n"/>
-      <c r="AP10" s="2" t="n">
+      <c r="AS10" s="3" t="n"/>
+      <c r="AT10" s="3" t="n"/>
+      <c r="AU10" s="3" t="n"/>
+      <c r="AV10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ10" s="2" t="inlineStr">
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR10" s="2" t="n">
+      <c r="AX10" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AS10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="n"/>
-      <c r="AV10" s="3" t="n"/>
-      <c r="AW10" s="3" t="n"/>
-      <c r="AX10" s="3" t="n"/>
-      <c r="AY10" s="3" t="n"/>
-      <c r="AZ10" s="3" t="n"/>
+      <c r="AY10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA10" s="3" t="n"/>
-      <c r="BB10" s="2" t="n">
-        <v>5520</v>
-      </c>
+      <c r="BB10" s="3" t="n"/>
       <c r="BC10" s="3" t="n"/>
       <c r="BD10" s="3" t="n"/>
       <c r="BE10" s="3" t="n"/>
       <c r="BF10" s="3" t="n"/>
-      <c r="BG10" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH10" s="3" t="n"/>
-      <c r="BI10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG10" s="3" t="n"/>
+      <c r="BH10" s="2" t="n">
+        <v>5520</v>
+      </c>
+      <c r="BI10" s="3" t="n"/>
       <c r="BJ10" s="3" t="n"/>
       <c r="BK10" s="3" t="n"/>
       <c r="BL10" s="3" t="n"/>
       <c r="BM10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN10" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO10" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN10" s="3" t="n"/>
+      <c r="BO10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP10" s="3" t="n"/>
       <c r="BQ10" s="3" t="n"/>
       <c r="BR10" s="3" t="n"/>
-      <c r="BS10" s="3" t="n"/>
-      <c r="BT10" s="3" t="n"/>
-      <c r="BU10" s="3" t="n"/>
+      <c r="BS10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT10" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU10" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BV10" s="3" t="n"/>
       <c r="BW10" s="3" t="n"/>
       <c r="BX10" s="3" t="n"/>
@@ -3168,30 +3188,12 @@
       <c r="CF10" s="3" t="n"/>
       <c r="CG10" s="3" t="n"/>
       <c r="CH10" s="3" t="n"/>
-      <c r="CI10" s="6">
-        <f>IFERROR(AVERAGEIF(P331:P368,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ10" s="6">
-        <f>IFERROR(AVERAGEIF(Q331:Q368,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK10" s="6">
-        <f>IFERROR(AVERAGEIF(R331:R368,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL10" s="6">
-        <f>IFERROR(AVERAGEIF(S331:S368,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM10" s="6">
-        <f>IFERROR(AVERAGEIF(T331:T368,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN10" s="6">
-        <f>IFERROR(AVERAGEIF(U331:U368,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI10" s="3" t="n"/>
+      <c r="CJ10" s="3" t="n"/>
+      <c r="CK10" s="3" t="n"/>
+      <c r="CL10" s="3" t="n"/>
+      <c r="CM10" s="3" t="n"/>
+      <c r="CN10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3302,99 +3304,117 @@
       <c r="AF11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG11" s="2" t="inlineStr">
+      <c r="AG11" s="6">
+        <f>IFERROR(AVERAGEIF(P370:P407,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="6">
+        <f>IFERROR(AVERAGEIF(Q370:Q407,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI11" s="6">
+        <f>IFERROR(AVERAGEIF(R370:R407,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="6">
+        <f>IFERROR(AVERAGEIF(S370:S407,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK11" s="6">
+        <f>IFERROR(AVERAGEIF(T370:T407,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL11" s="6">
+        <f>IFERROR(AVERAGEIF(U370:U407,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AH11" s="2" t="inlineStr">
+      <c r="AN11" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AI11" s="3" t="n"/>
-      <c r="AJ11" s="2" t="inlineStr">
+      <c r="AO11" s="3" t="n"/>
+      <c r="AP11" s="2" t="inlineStr">
         <is>
           <t>2026-08-05T00:00:00</t>
         </is>
       </c>
-      <c r="AK11" s="2" t="inlineStr">
+      <c r="AQ11" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL11" s="2" t="inlineStr">
+      <c r="AR11" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM11" s="3" t="n"/>
-      <c r="AN11" s="3" t="n"/>
-      <c r="AO11" s="3" t="n"/>
-      <c r="AP11" s="2" t="n">
+      <c r="AS11" s="3" t="n"/>
+      <c r="AT11" s="3" t="n"/>
+      <c r="AU11" s="3" t="n"/>
+      <c r="AV11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ11" s="2" t="inlineStr">
+      <c r="AW11" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AR11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="3" t="n"/>
-      <c r="AV11" s="3" t="n"/>
-      <c r="AW11" s="3" t="n"/>
-      <c r="AX11" s="3" t="n"/>
-      <c r="AY11" s="3" t="n"/>
-      <c r="AZ11" s="3" t="n"/>
+      <c r="AX11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA11" s="3" t="n"/>
-      <c r="BB11" s="2" t="n">
-        <v>4321</v>
-      </c>
+      <c r="BB11" s="3" t="n"/>
       <c r="BC11" s="3" t="n"/>
       <c r="BD11" s="3" t="n"/>
       <c r="BE11" s="3" t="n"/>
       <c r="BF11" s="3" t="n"/>
-      <c r="BG11" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH11" s="3" t="n"/>
-      <c r="BI11" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG11" s="3" t="n"/>
+      <c r="BH11" s="2" t="n">
+        <v>4321</v>
+      </c>
+      <c r="BI11" s="3" t="n"/>
       <c r="BJ11" s="3" t="n"/>
       <c r="BK11" s="3" t="n"/>
       <c r="BL11" s="3" t="n"/>
       <c r="BM11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN11" s="2" t="inlineStr">
-        <is>
-          <t>VALENCIA</t>
-        </is>
-      </c>
-      <c r="BO11" s="2" t="inlineStr">
-        <is>
-          <t>Manises</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN11" s="3" t="n"/>
+      <c r="BO11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP11" s="3" t="n"/>
       <c r="BQ11" s="3" t="n"/>
       <c r="BR11" s="3" t="n"/>
-      <c r="BS11" s="3" t="n"/>
-      <c r="BT11" s="3" t="n"/>
-      <c r="BU11" s="3" t="n"/>
+      <c r="BS11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT11" s="2" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="BU11" s="2" t="inlineStr">
+        <is>
+          <t>Manises</t>
+        </is>
+      </c>
       <c r="BV11" s="3" t="n"/>
       <c r="BW11" s="3" t="n"/>
       <c r="BX11" s="3" t="n"/>
@@ -3408,30 +3428,12 @@
       <c r="CF11" s="3" t="n"/>
       <c r="CG11" s="3" t="n"/>
       <c r="CH11" s="3" t="n"/>
-      <c r="CI11" s="6">
-        <f>IFERROR(AVERAGEIF(P370:P407,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ11" s="6">
-        <f>IFERROR(AVERAGEIF(Q370:Q407,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK11" s="6">
-        <f>IFERROR(AVERAGEIF(R370:R407,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL11" s="6">
-        <f>IFERROR(AVERAGEIF(S370:S407,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM11" s="6">
-        <f>IFERROR(AVERAGEIF(T370:T407,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN11" s="6">
-        <f>IFERROR(AVERAGEIF(U370:U407,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI11" s="3" t="n"/>
+      <c r="CJ11" s="3" t="n"/>
+      <c r="CK11" s="3" t="n"/>
+      <c r="CL11" s="3" t="n"/>
+      <c r="CM11" s="3" t="n"/>
+      <c r="CN11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3542,99 +3544,117 @@
       <c r="AF12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG12" s="2" t="inlineStr">
+      <c r="AG12" s="6">
+        <f>IFERROR(AVERAGEIF(P409:P446,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH12" s="6">
+        <f>IFERROR(AVERAGEIF(Q409:Q446,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI12" s="6">
+        <f>IFERROR(AVERAGEIF(R409:R446,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="6">
+        <f>IFERROR(AVERAGEIF(S409:S446,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK12" s="6">
+        <f>IFERROR(AVERAGEIF(T409:T446,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL12" s="6">
+        <f>IFERROR(AVERAGEIF(U409:U446,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM12" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AH12" s="2" t="inlineStr">
+      <c r="AN12" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AI12" s="3" t="n"/>
-      <c r="AJ12" s="2" t="inlineStr">
+      <c r="AO12" s="3" t="n"/>
+      <c r="AP12" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T00:00:00</t>
         </is>
       </c>
-      <c r="AK12" s="2" t="inlineStr">
+      <c r="AQ12" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL12" s="2" t="inlineStr">
+      <c r="AR12" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM12" s="3" t="n"/>
-      <c r="AN12" s="3" t="n"/>
-      <c r="AO12" s="3" t="n"/>
-      <c r="AP12" s="2" t="n">
+      <c r="AS12" s="3" t="n"/>
+      <c r="AT12" s="3" t="n"/>
+      <c r="AU12" s="3" t="n"/>
+      <c r="AV12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ12" s="2" t="inlineStr">
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="3" t="n"/>
-      <c r="AV12" s="3" t="n"/>
-      <c r="AW12" s="3" t="n"/>
-      <c r="AX12" s="3" t="n"/>
-      <c r="AY12" s="3" t="n"/>
-      <c r="AZ12" s="3" t="n"/>
+      <c r="AX12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA12" s="3" t="n"/>
-      <c r="BB12" s="2" t="n">
-        <v>2370</v>
-      </c>
+      <c r="BB12" s="3" t="n"/>
       <c r="BC12" s="3" t="n"/>
       <c r="BD12" s="3" t="n"/>
       <c r="BE12" s="3" t="n"/>
       <c r="BF12" s="3" t="n"/>
-      <c r="BG12" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH12" s="3" t="n"/>
-      <c r="BI12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG12" s="3" t="n"/>
+      <c r="BH12" s="2" t="n">
+        <v>2370</v>
+      </c>
+      <c r="BI12" s="3" t="n"/>
       <c r="BJ12" s="3" t="n"/>
       <c r="BK12" s="3" t="n"/>
       <c r="BL12" s="3" t="n"/>
       <c r="BM12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN12" s="2" t="inlineStr">
-        <is>
-          <t>BIZKAIA</t>
-        </is>
-      </c>
-      <c r="BO12" s="2" t="inlineStr">
-        <is>
-          <t>Gatika</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN12" s="3" t="n"/>
+      <c r="BO12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP12" s="3" t="n"/>
       <c r="BQ12" s="3" t="n"/>
       <c r="BR12" s="3" t="n"/>
-      <c r="BS12" s="3" t="n"/>
-      <c r="BT12" s="3" t="n"/>
-      <c r="BU12" s="3" t="n"/>
+      <c r="BS12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT12" s="2" t="inlineStr">
+        <is>
+          <t>BIZKAIA</t>
+        </is>
+      </c>
+      <c r="BU12" s="2" t="inlineStr">
+        <is>
+          <t>Gatika</t>
+        </is>
+      </c>
       <c r="BV12" s="3" t="n"/>
       <c r="BW12" s="3" t="n"/>
       <c r="BX12" s="3" t="n"/>
@@ -3648,30 +3668,12 @@
       <c r="CF12" s="3" t="n"/>
       <c r="CG12" s="3" t="n"/>
       <c r="CH12" s="3" t="n"/>
-      <c r="CI12" s="6">
-        <f>IFERROR(AVERAGEIF(P409:P446,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ12" s="6">
-        <f>IFERROR(AVERAGEIF(Q409:Q446,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK12" s="6">
-        <f>IFERROR(AVERAGEIF(R409:R446,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL12" s="6">
-        <f>IFERROR(AVERAGEIF(S409:S446,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM12" s="6">
-        <f>IFERROR(AVERAGEIF(T409:T446,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN12" s="6">
-        <f>IFERROR(AVERAGEIF(U409:U446,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI12" s="3" t="n"/>
+      <c r="CJ12" s="3" t="n"/>
+      <c r="CK12" s="3" t="n"/>
+      <c r="CL12" s="3" t="n"/>
+      <c r="CM12" s="3" t="n"/>
+      <c r="CN12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3782,99 +3784,117 @@
       <c r="AF13" s="2" t="n">
         <v>17.32</v>
       </c>
-      <c r="AG13" s="2" t="inlineStr">
+      <c r="AG13" s="6">
+        <f>IFERROR(AVERAGEIF(P448:P485,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH13" s="6">
+        <f>IFERROR(AVERAGEIF(Q448:Q485,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI13" s="6">
+        <f>IFERROR(AVERAGEIF(R448:R485,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="6">
+        <f>IFERROR(AVERAGEIF(S448:S485,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK13" s="6">
+        <f>IFERROR(AVERAGEIF(T448:T485,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL13" s="6">
+        <f>IFERROR(AVERAGEIF(U448:U485,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="2" t="inlineStr">
         <is>
           <t>2025-10-23T00:00:00</t>
         </is>
       </c>
-      <c r="AH13" s="2" t="inlineStr">
+      <c r="AN13" s="2" t="inlineStr">
         <is>
           <t>2025-10-23T00:00:00</t>
         </is>
       </c>
-      <c r="AI13" s="3" t="n"/>
-      <c r="AJ13" s="2" t="inlineStr">
+      <c r="AO13" s="3" t="n"/>
+      <c r="AP13" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK13" s="2" t="inlineStr">
+      <c r="AQ13" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL13" s="2" t="inlineStr">
+      <c r="AR13" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM13" s="3" t="n"/>
-      <c r="AN13" s="3" t="n"/>
-      <c r="AO13" s="3" t="n"/>
-      <c r="AP13" s="2" t="n">
+      <c r="AS13" s="3" t="n"/>
+      <c r="AT13" s="3" t="n"/>
+      <c r="AU13" s="3" t="n"/>
+      <c r="AV13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ13" s="2" t="inlineStr">
+      <c r="AW13" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR13" s="2" t="n">
+      <c r="AX13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AS13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="3" t="n"/>
-      <c r="AV13" s="3" t="n"/>
-      <c r="AW13" s="3" t="n"/>
-      <c r="AX13" s="3" t="n"/>
-      <c r="AY13" s="3" t="n"/>
-      <c r="AZ13" s="3" t="n"/>
+      <c r="AY13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA13" s="3" t="n"/>
-      <c r="BB13" s="2" t="n">
-        <v>5630</v>
-      </c>
+      <c r="BB13" s="3" t="n"/>
       <c r="BC13" s="3" t="n"/>
       <c r="BD13" s="3" t="n"/>
       <c r="BE13" s="3" t="n"/>
       <c r="BF13" s="3" t="n"/>
-      <c r="BG13" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH13" s="3" t="n"/>
-      <c r="BI13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG13" s="3" t="n"/>
+      <c r="BH13" s="2" t="n">
+        <v>5630</v>
+      </c>
+      <c r="BI13" s="3" t="n"/>
       <c r="BJ13" s="3" t="n"/>
       <c r="BK13" s="3" t="n"/>
       <c r="BL13" s="3" t="n"/>
       <c r="BM13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN13" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO13" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN13" s="3" t="n"/>
+      <c r="BO13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP13" s="3" t="n"/>
       <c r="BQ13" s="3" t="n"/>
       <c r="BR13" s="3" t="n"/>
-      <c r="BS13" s="3" t="n"/>
-      <c r="BT13" s="3" t="n"/>
-      <c r="BU13" s="3" t="n"/>
+      <c r="BS13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT13" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU13" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BV13" s="3" t="n"/>
       <c r="BW13" s="3" t="n"/>
       <c r="BX13" s="3" t="n"/>
@@ -3888,30 +3908,12 @@
       <c r="CF13" s="3" t="n"/>
       <c r="CG13" s="3" t="n"/>
       <c r="CH13" s="3" t="n"/>
-      <c r="CI13" s="6">
-        <f>IFERROR(AVERAGEIF(P448:P485,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ13" s="6">
-        <f>IFERROR(AVERAGEIF(Q448:Q485,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK13" s="6">
-        <f>IFERROR(AVERAGEIF(R448:R485,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL13" s="6">
-        <f>IFERROR(AVERAGEIF(S448:S485,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM13" s="6">
-        <f>IFERROR(AVERAGEIF(T448:T485,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN13" s="6">
-        <f>IFERROR(AVERAGEIF(U448:U485,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI13" s="3" t="n"/>
+      <c r="CJ13" s="3" t="n"/>
+      <c r="CK13" s="3" t="n"/>
+      <c r="CL13" s="3" t="n"/>
+      <c r="CM13" s="3" t="n"/>
+      <c r="CN13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4016,127 +4018,145 @@
       <c r="AF14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG14" s="2" t="inlineStr">
+      <c r="AG14" s="6">
+        <f>IFERROR(AVERAGEIF(P487:P522,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH14" s="6">
+        <f>IFERROR(AVERAGEIF(Q487:Q522,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI14" s="6">
+        <f>IFERROR(AVERAGEIF(R487:R522,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="6">
+        <f>IFERROR(AVERAGEIF(S487:S522,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK14" s="6">
+        <f>IFERROR(AVERAGEIF(T487:T522,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL14" s="6">
+        <f>IFERROR(AVERAGEIF(U487:U522,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
         <is>
           <t>2021-05-31T00:00:00</t>
         </is>
       </c>
-      <c r="AH14" s="2" t="inlineStr">
+      <c r="AN14" s="2" t="inlineStr">
         <is>
           <t>2021-02-19T00:00:00</t>
         </is>
       </c>
-      <c r="AI14" s="2" t="inlineStr">
+      <c r="AO14" s="2" t="inlineStr">
         <is>
           <t>2099-12-31T00:00:00</t>
         </is>
       </c>
-      <c r="AJ14" s="2" t="inlineStr">
+      <c r="AP14" s="2" t="inlineStr">
         <is>
           <t>2026-08-11T00:00:00</t>
         </is>
       </c>
-      <c r="AK14" s="2" t="inlineStr">
+      <c r="AQ14" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL14" s="2" t="inlineStr">
+      <c r="AR14" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="n"/>
-      <c r="AN14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3" t="n"/>
-      <c r="AP14" s="2" t="n">
+      <c r="AS14" s="3" t="n"/>
+      <c r="AT14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3" t="n"/>
+      <c r="AV14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AQ14" s="2" t="inlineStr">
+      <c r="AW14" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="2" t="n">
+      <c r="AX14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AT14" s="2" t="n">
+      <c r="AZ14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AU14" s="2" t="inlineStr">
+      <c r="BA14" s="2" t="inlineStr">
         <is>
           <t>A000775/09</t>
         </is>
       </c>
-      <c r="AV14" s="2" t="inlineStr">
+      <c r="BB14" s="2" t="inlineStr">
         <is>
           <t>2009-04-13T00:00:00</t>
         </is>
       </c>
-      <c r="AW14" s="2" t="inlineStr">
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>9999-12-31T00:00:00</t>
         </is>
       </c>
-      <c r="AX14" s="3" t="n"/>
-      <c r="AY14" s="3" t="n"/>
-      <c r="AZ14" s="3" t="n"/>
-      <c r="BA14" s="3" t="n"/>
-      <c r="BB14" s="2" t="n">
+      <c r="BD14" s="3" t="n"/>
+      <c r="BE14" s="3" t="n"/>
+      <c r="BF14" s="3" t="n"/>
+      <c r="BG14" s="3" t="n"/>
+      <c r="BH14" s="2" t="n">
         <v>5210</v>
       </c>
-      <c r="BC14" s="2" t="n">
+      <c r="BI14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="BD14" s="2" t="n">
+      <c r="BJ14" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="BE14" s="2" t="n">
+      <c r="BK14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BF14" s="3" t="n"/>
-      <c r="BG14" s="2" t="inlineStr">
+      <c r="BL14" s="3" t="n"/>
+      <c r="BM14" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="n"/>
-      <c r="BI14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ14" s="3" t="n"/>
-      <c r="BK14" s="3" t="n"/>
-      <c r="BL14" s="2" t="inlineStr">
-        <is>
-          <t>UV</t>
-        </is>
-      </c>
-      <c r="BM14" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN14" s="2" t="inlineStr">
-        <is>
-          <t>SEVILLA</t>
-        </is>
-      </c>
-      <c r="BO14" s="2" t="inlineStr">
-        <is>
-          <t>CAMAS</t>
-        </is>
+      <c r="BN14" s="3" t="n"/>
+      <c r="BO14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP14" s="3" t="n"/>
       <c r="BQ14" s="3" t="n"/>
-      <c r="BR14" s="3" t="n"/>
-      <c r="BS14" s="3" t="n"/>
-      <c r="BT14" s="3" t="n"/>
-      <c r="BU14" s="3" t="n"/>
+      <c r="BR14" s="2" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="BS14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT14" s="2" t="inlineStr">
+        <is>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="BU14" s="2" t="inlineStr">
+        <is>
+          <t>CAMAS</t>
+        </is>
+      </c>
       <c r="BV14" s="3" t="n"/>
       <c r="BW14" s="3" t="n"/>
       <c r="BX14" s="3" t="n"/>
@@ -4150,30 +4170,12 @@
       <c r="CF14" s="3" t="n"/>
       <c r="CG14" s="3" t="n"/>
       <c r="CH14" s="3" t="n"/>
-      <c r="CI14" s="6">
-        <f>IFERROR(AVERAGEIF(P487:P522,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ14" s="6">
-        <f>IFERROR(AVERAGEIF(Q487:Q522,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK14" s="6">
-        <f>IFERROR(AVERAGEIF(R487:R522,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL14" s="6">
-        <f>IFERROR(AVERAGEIF(S487:S522,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM14" s="6">
-        <f>IFERROR(AVERAGEIF(T487:T522,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN14" s="6">
-        <f>IFERROR(AVERAGEIF(U487:U522,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI14" s="3" t="n"/>
+      <c r="CJ14" s="3" t="n"/>
+      <c r="CK14" s="3" t="n"/>
+      <c r="CL14" s="3" t="n"/>
+      <c r="CM14" s="3" t="n"/>
+      <c r="CN14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -4278,125 +4280,143 @@
       <c r="AF15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG15" s="2" t="inlineStr">
+      <c r="AG15" s="6">
+        <f>IFERROR(AVERAGEIF(P524:P559,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="6">
+        <f>IFERROR(AVERAGEIF(Q524:Q559,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI15" s="6">
+        <f>IFERROR(AVERAGEIF(R524:R559,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="6">
+        <f>IFERROR(AVERAGEIF(S524:S559,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK15" s="6">
+        <f>IFERROR(AVERAGEIF(T524:T559,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="6">
+        <f>IFERROR(AVERAGEIF(U524:U559,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="2" t="inlineStr">
         <is>
           <t>2021-05-31T00:00:00</t>
         </is>
       </c>
-      <c r="AH15" s="2" t="inlineStr">
+      <c r="AN15" s="2" t="inlineStr">
         <is>
           <t>2021-03-01T00:00:00</t>
         </is>
       </c>
-      <c r="AI15" s="2" t="inlineStr">
+      <c r="AO15" s="2" t="inlineStr">
         <is>
           <t>2099-12-31T00:00:00</t>
         </is>
       </c>
-      <c r="AJ15" s="2" t="inlineStr">
+      <c r="AP15" s="2" t="inlineStr">
         <is>
           <t>2026-08-09T00:00:00</t>
         </is>
       </c>
-      <c r="AK15" s="2" t="inlineStr">
+      <c r="AQ15" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL15" s="2" t="inlineStr">
+      <c r="AR15" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM15" s="3" t="n"/>
-      <c r="AN15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="3" t="n"/>
-      <c r="AP15" s="2" t="n">
+      <c r="AS15" s="3" t="n"/>
+      <c r="AT15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="3" t="n"/>
+      <c r="AV15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AQ15" s="2" t="inlineStr">
+      <c r="AW15" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" s="2" t="n">
+      <c r="AX15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AT15" s="2" t="n">
+      <c r="AZ15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AU15" s="2" t="n">
+      <c r="BA15" s="2" t="n">
         <v>9999</v>
       </c>
-      <c r="AV15" s="2" t="inlineStr">
+      <c r="BB15" s="2" t="inlineStr">
         <is>
           <t>2004-11-05T00:00:00</t>
         </is>
       </c>
-      <c r="AW15" s="2" t="inlineStr">
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>9999-12-31T00:00:00</t>
         </is>
       </c>
-      <c r="AX15" s="3" t="n"/>
-      <c r="AY15" s="3" t="n"/>
-      <c r="AZ15" s="3" t="n"/>
-      <c r="BA15" s="3" t="n"/>
-      <c r="BB15" s="2" t="n">
+      <c r="BD15" s="3" t="n"/>
+      <c r="BE15" s="3" t="n"/>
+      <c r="BF15" s="3" t="n"/>
+      <c r="BG15" s="3" t="n"/>
+      <c r="BH15" s="2" t="n">
         <v>9820</v>
       </c>
-      <c r="BC15" s="2" t="n">
+      <c r="BI15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="BD15" s="2" t="n">
+      <c r="BJ15" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="BE15" s="2" t="n">
+      <c r="BK15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BF15" s="3" t="n"/>
-      <c r="BG15" s="2" t="inlineStr">
+      <c r="BL15" s="3" t="n"/>
+      <c r="BM15" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="BH15" s="3" t="n"/>
-      <c r="BI15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ15" s="3" t="n"/>
-      <c r="BK15" s="3" t="n"/>
-      <c r="BL15" s="2" t="inlineStr">
-        <is>
-          <t>UV</t>
-        </is>
-      </c>
-      <c r="BM15" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN15" s="2" t="inlineStr">
-        <is>
-          <t>BARCELONA</t>
-        </is>
-      </c>
-      <c r="BO15" s="2" t="inlineStr">
-        <is>
-          <t>MONTMELO</t>
-        </is>
+      <c r="BN15" s="3" t="n"/>
+      <c r="BO15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP15" s="3" t="n"/>
       <c r="BQ15" s="3" t="n"/>
-      <c r="BR15" s="3" t="n"/>
-      <c r="BS15" s="3" t="n"/>
-      <c r="BT15" s="3" t="n"/>
-      <c r="BU15" s="3" t="n"/>
+      <c r="BR15" s="2" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="BS15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT15" s="2" t="inlineStr">
+        <is>
+          <t>BARCELONA</t>
+        </is>
+      </c>
+      <c r="BU15" s="2" t="inlineStr">
+        <is>
+          <t>MONTMELO</t>
+        </is>
+      </c>
       <c r="BV15" s="3" t="n"/>
       <c r="BW15" s="3" t="n"/>
       <c r="BX15" s="3" t="n"/>
@@ -4410,30 +4430,12 @@
       <c r="CF15" s="3" t="n"/>
       <c r="CG15" s="3" t="n"/>
       <c r="CH15" s="3" t="n"/>
-      <c r="CI15" s="6">
-        <f>IFERROR(AVERAGEIF(P524:P559,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ15" s="6">
-        <f>IFERROR(AVERAGEIF(Q524:Q559,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK15" s="6">
-        <f>IFERROR(AVERAGEIF(R524:R559,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL15" s="6">
-        <f>IFERROR(AVERAGEIF(S524:S559,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM15" s="6">
-        <f>IFERROR(AVERAGEIF(T524:T559,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN15" s="6">
-        <f>IFERROR(AVERAGEIF(U524:U559,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI15" s="3" t="n"/>
+      <c r="CJ15" s="3" t="n"/>
+      <c r="CK15" s="3" t="n"/>
+      <c r="CL15" s="3" t="n"/>
+      <c r="CM15" s="3" t="n"/>
+      <c r="CN15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4538,97 +4540,115 @@
       <c r="AF16" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="AG16" s="2" t="inlineStr">
+      <c r="AG16" s="6">
+        <f>IFERROR(AVERAGEIF(P561:P599,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH16" s="6">
+        <f>IFERROR(AVERAGEIF(Q561:Q599,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI16" s="6">
+        <f>IFERROR(AVERAGEIF(R561:R599,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="6">
+        <f>IFERROR(AVERAGEIF(S561:S599,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK16" s="6">
+        <f>IFERROR(AVERAGEIF(T561:T599,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL16" s="6">
+        <f>IFERROR(AVERAGEIF(U561:U599,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
         <is>
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="AH16" s="2" t="inlineStr">
+      <c r="AN16" s="2" t="inlineStr">
         <is>
           <t>2025-03-20T00:00:00</t>
         </is>
       </c>
-      <c r="AI16" s="3" t="n"/>
-      <c r="AJ16" s="2" t="inlineStr">
+      <c r="AO16" s="3" t="n"/>
+      <c r="AP16" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AK16" s="2" t="inlineStr">
+      <c r="AQ16" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL16" s="2" t="inlineStr">
+      <c r="AR16" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM16" s="3" t="n"/>
-      <c r="AN16" s="3" t="n"/>
-      <c r="AO16" s="3" t="n"/>
-      <c r="AP16" s="2" t="n">
+      <c r="AS16" s="3" t="n"/>
+      <c r="AT16" s="3" t="n"/>
+      <c r="AU16" s="3" t="n"/>
+      <c r="AV16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AQ16" s="2" t="inlineStr">
+      <c r="AW16" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="2" t="n">
+      <c r="AX16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AT16" s="2" t="n">
+      <c r="AZ16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AU16" s="3" t="n"/>
-      <c r="AV16" s="3" t="n"/>
-      <c r="AW16" s="3" t="n"/>
-      <c r="AX16" s="3" t="n"/>
-      <c r="AY16" s="3" t="n"/>
-      <c r="AZ16" s="3" t="n"/>
       <c r="BA16" s="3" t="n"/>
-      <c r="BB16" s="2" t="n">
-        <v>9810</v>
-      </c>
-      <c r="BC16" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="BB16" s="3" t="n"/>
+      <c r="BC16" s="3" t="n"/>
       <c r="BD16" s="3" t="n"/>
       <c r="BE16" s="3" t="n"/>
       <c r="BF16" s="3" t="n"/>
       <c r="BG16" s="3" t="n"/>
-      <c r="BH16" s="3" t="n"/>
+      <c r="BH16" s="2" t="n">
+        <v>9810</v>
+      </c>
       <c r="BI16" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BJ16" s="3" t="n"/>
       <c r="BK16" s="3" t="n"/>
       <c r="BL16" s="3" t="n"/>
-      <c r="BM16" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN16" s="2" t="inlineStr">
-        <is>
-          <t>TOLEDO</t>
-        </is>
-      </c>
-      <c r="BO16" s="2" t="inlineStr">
-        <is>
-          <t>Villafranca de los Caballeros</t>
-        </is>
+      <c r="BM16" s="3" t="n"/>
+      <c r="BN16" s="3" t="n"/>
+      <c r="BO16" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="BP16" s="3" t="n"/>
       <c r="BQ16" s="3" t="n"/>
       <c r="BR16" s="3" t="n"/>
-      <c r="BS16" s="3" t="n"/>
-      <c r="BT16" s="3" t="n"/>
-      <c r="BU16" s="3" t="n"/>
+      <c r="BS16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT16" s="2" t="inlineStr">
+        <is>
+          <t>TOLEDO</t>
+        </is>
+      </c>
+      <c r="BU16" s="2" t="inlineStr">
+        <is>
+          <t>Villafranca de los Caballeros</t>
+        </is>
+      </c>
       <c r="BV16" s="3" t="n"/>
       <c r="BW16" s="3" t="n"/>
       <c r="BX16" s="3" t="n"/>
@@ -4642,30 +4662,12 @@
       <c r="CF16" s="3" t="n"/>
       <c r="CG16" s="3" t="n"/>
       <c r="CH16" s="3" t="n"/>
-      <c r="CI16" s="6">
-        <f>IFERROR(AVERAGEIF(P561:P599,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ16" s="6">
-        <f>IFERROR(AVERAGEIF(Q561:Q599,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK16" s="6">
-        <f>IFERROR(AVERAGEIF(R561:R599,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL16" s="6">
-        <f>IFERROR(AVERAGEIF(S561:S599,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM16" s="6">
-        <f>IFERROR(AVERAGEIF(T561:T599,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN16" s="6">
-        <f>IFERROR(AVERAGEIF(U561:U599,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI16" s="3" t="n"/>
+      <c r="CJ16" s="3" t="n"/>
+      <c r="CK16" s="3" t="n"/>
+      <c r="CL16" s="3" t="n"/>
+      <c r="CM16" s="3" t="n"/>
+      <c r="CN16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4776,99 +4778,117 @@
       <c r="AF17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG17" s="2" t="inlineStr">
+      <c r="AG17" s="6">
+        <f>IFERROR(AVERAGEIF(P601:P638,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH17" s="6">
+        <f>IFERROR(AVERAGEIF(Q601:Q638,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI17" s="6">
+        <f>IFERROR(AVERAGEIF(R601:R638,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="6">
+        <f>IFERROR(AVERAGEIF(S601:S638,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK17" s="6">
+        <f>IFERROR(AVERAGEIF(T601:T638,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL17" s="6">
+        <f>IFERROR(AVERAGEIF(U601:U638,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AH17" s="2" t="inlineStr">
+      <c r="AN17" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AI17" s="3" t="n"/>
-      <c r="AJ17" s="2" t="inlineStr">
+      <c r="AO17" s="3" t="n"/>
+      <c r="AP17" s="2" t="inlineStr">
         <is>
           <t>2026-08-12T00:00:00</t>
         </is>
       </c>
-      <c r="AK17" s="2" t="inlineStr">
+      <c r="AQ17" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL17" s="2" t="inlineStr">
+      <c r="AR17" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM17" s="3" t="n"/>
-      <c r="AN17" s="3" t="n"/>
-      <c r="AO17" s="3" t="n"/>
-      <c r="AP17" s="2" t="n">
+      <c r="AS17" s="3" t="n"/>
+      <c r="AT17" s="3" t="n"/>
+      <c r="AU17" s="3" t="n"/>
+      <c r="AV17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ17" s="2" t="inlineStr">
+      <c r="AW17" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" s="3" t="n"/>
-      <c r="AV17" s="3" t="n"/>
-      <c r="AW17" s="3" t="n"/>
-      <c r="AX17" s="3" t="n"/>
-      <c r="AY17" s="3" t="n"/>
-      <c r="AZ17" s="3" t="n"/>
+      <c r="AX17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA17" s="3" t="n"/>
-      <c r="BB17" s="2" t="n">
-        <v>9810</v>
-      </c>
+      <c r="BB17" s="3" t="n"/>
       <c r="BC17" s="3" t="n"/>
       <c r="BD17" s="3" t="n"/>
       <c r="BE17" s="3" t="n"/>
       <c r="BF17" s="3" t="n"/>
-      <c r="BG17" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH17" s="3" t="n"/>
-      <c r="BI17" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG17" s="3" t="n"/>
+      <c r="BH17" s="2" t="n">
+        <v>9810</v>
+      </c>
+      <c r="BI17" s="3" t="n"/>
       <c r="BJ17" s="3" t="n"/>
       <c r="BK17" s="3" t="n"/>
       <c r="BL17" s="3" t="n"/>
       <c r="BM17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN17" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO17" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN17" s="3" t="n"/>
+      <c r="BO17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP17" s="3" t="n"/>
       <c r="BQ17" s="3" t="n"/>
       <c r="BR17" s="3" t="n"/>
-      <c r="BS17" s="3" t="n"/>
-      <c r="BT17" s="3" t="n"/>
-      <c r="BU17" s="3" t="n"/>
+      <c r="BS17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT17" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU17" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BV17" s="3" t="n"/>
       <c r="BW17" s="3" t="n"/>
       <c r="BX17" s="3" t="n"/>
@@ -4882,30 +4902,12 @@
       <c r="CF17" s="3" t="n"/>
       <c r="CG17" s="3" t="n"/>
       <c r="CH17" s="3" t="n"/>
-      <c r="CI17" s="6">
-        <f>IFERROR(AVERAGEIF(P601:P638,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ17" s="6">
-        <f>IFERROR(AVERAGEIF(Q601:Q638,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK17" s="6">
-        <f>IFERROR(AVERAGEIF(R601:R638,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL17" s="6">
-        <f>IFERROR(AVERAGEIF(S601:S638,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM17" s="6">
-        <f>IFERROR(AVERAGEIF(T601:T638,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN17" s="6">
-        <f>IFERROR(AVERAGEIF(U601:U638,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI17" s="3" t="n"/>
+      <c r="CJ17" s="3" t="n"/>
+      <c r="CK17" s="3" t="n"/>
+      <c r="CL17" s="3" t="n"/>
+      <c r="CM17" s="3" t="n"/>
+      <c r="CN17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5016,99 +5018,117 @@
       <c r="AF18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG18" s="2" t="inlineStr">
+      <c r="AG18" s="6">
+        <f>IFERROR(AVERAGEIF(P640:P677,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH18" s="6">
+        <f>IFERROR(AVERAGEIF(Q640:Q677,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI18" s="6">
+        <f>IFERROR(AVERAGEIF(R640:R677,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="6">
+        <f>IFERROR(AVERAGEIF(S640:S677,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK18" s="6">
+        <f>IFERROR(AVERAGEIF(T640:T677,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL18" s="6">
+        <f>IFERROR(AVERAGEIF(U640:U677,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM18" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AH18" s="2" t="inlineStr">
+      <c r="AN18" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AI18" s="3" t="n"/>
-      <c r="AJ18" s="2" t="inlineStr">
+      <c r="AO18" s="3" t="n"/>
+      <c r="AP18" s="2" t="inlineStr">
         <is>
           <t>2026-08-12T00:00:00</t>
         </is>
       </c>
-      <c r="AK18" s="2" t="inlineStr">
+      <c r="AQ18" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL18" s="2" t="inlineStr">
+      <c r="AR18" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM18" s="3" t="n"/>
-      <c r="AN18" s="3" t="n"/>
-      <c r="AO18" s="3" t="n"/>
-      <c r="AP18" s="2" t="n">
+      <c r="AS18" s="3" t="n"/>
+      <c r="AT18" s="3" t="n"/>
+      <c r="AU18" s="3" t="n"/>
+      <c r="AV18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ18" s="2" t="inlineStr">
+      <c r="AW18" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" s="3" t="n"/>
-      <c r="AV18" s="3" t="n"/>
-      <c r="AW18" s="3" t="n"/>
-      <c r="AX18" s="3" t="n"/>
-      <c r="AY18" s="3" t="n"/>
-      <c r="AZ18" s="3" t="n"/>
+      <c r="AX18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA18" s="3" t="n"/>
-      <c r="BB18" s="2" t="n">
-        <v>6820</v>
-      </c>
+      <c r="BB18" s="3" t="n"/>
       <c r="BC18" s="3" t="n"/>
       <c r="BD18" s="3" t="n"/>
       <c r="BE18" s="3" t="n"/>
       <c r="BF18" s="3" t="n"/>
-      <c r="BG18" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH18" s="3" t="n"/>
-      <c r="BI18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG18" s="3" t="n"/>
+      <c r="BH18" s="2" t="n">
+        <v>6820</v>
+      </c>
+      <c r="BI18" s="3" t="n"/>
       <c r="BJ18" s="3" t="n"/>
       <c r="BK18" s="3" t="n"/>
       <c r="BL18" s="3" t="n"/>
       <c r="BM18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN18" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO18" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN18" s="3" t="n"/>
+      <c r="BO18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP18" s="3" t="n"/>
       <c r="BQ18" s="3" t="n"/>
       <c r="BR18" s="3" t="n"/>
-      <c r="BS18" s="3" t="n"/>
-      <c r="BT18" s="3" t="n"/>
-      <c r="BU18" s="3" t="n"/>
+      <c r="BS18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT18" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU18" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BV18" s="3" t="n"/>
       <c r="BW18" s="3" t="n"/>
       <c r="BX18" s="3" t="n"/>
@@ -5122,30 +5142,12 @@
       <c r="CF18" s="3" t="n"/>
       <c r="CG18" s="3" t="n"/>
       <c r="CH18" s="3" t="n"/>
-      <c r="CI18" s="6">
-        <f>IFERROR(AVERAGEIF(P640:P677,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ18" s="6">
-        <f>IFERROR(AVERAGEIF(Q640:Q677,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK18" s="6">
-        <f>IFERROR(AVERAGEIF(R640:R677,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL18" s="6">
-        <f>IFERROR(AVERAGEIF(S640:S677,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM18" s="6">
-        <f>IFERROR(AVERAGEIF(T640:T677,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN18" s="6">
-        <f>IFERROR(AVERAGEIF(U640:U677,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI18" s="3" t="n"/>
+      <c r="CJ18" s="3" t="n"/>
+      <c r="CK18" s="3" t="n"/>
+      <c r="CL18" s="3" t="n"/>
+      <c r="CM18" s="3" t="n"/>
+      <c r="CN18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -5256,99 +5258,117 @@
       <c r="AF19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG19" s="2" t="inlineStr">
+      <c r="AG19" s="6">
+        <f>IFERROR(AVERAGEIF(P679:P716,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="6">
+        <f>IFERROR(AVERAGEIF(Q679:Q716,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI19" s="6">
+        <f>IFERROR(AVERAGEIF(R679:R716,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="6">
+        <f>IFERROR(AVERAGEIF(S679:S716,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="6">
+        <f>IFERROR(AVERAGEIF(T679:T716,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="6">
+        <f>IFERROR(AVERAGEIF(U679:U716,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AH19" s="2" t="inlineStr">
+      <c r="AN19" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AI19" s="3" t="n"/>
-      <c r="AJ19" s="2" t="inlineStr">
+      <c r="AO19" s="3" t="n"/>
+      <c r="AP19" s="2" t="inlineStr">
         <is>
           <t>2026-08-12T00:00:00</t>
         </is>
       </c>
-      <c r="AK19" s="2" t="inlineStr">
+      <c r="AQ19" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL19" s="2" t="inlineStr">
+      <c r="AR19" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM19" s="3" t="n"/>
-      <c r="AN19" s="3" t="n"/>
-      <c r="AO19" s="3" t="n"/>
-      <c r="AP19" s="2" t="n">
+      <c r="AS19" s="3" t="n"/>
+      <c r="AT19" s="3" t="n"/>
+      <c r="AU19" s="3" t="n"/>
+      <c r="AV19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ19" s="2" t="inlineStr">
+      <c r="AW19" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" s="3" t="n"/>
-      <c r="AV19" s="3" t="n"/>
-      <c r="AW19" s="3" t="n"/>
-      <c r="AX19" s="3" t="n"/>
-      <c r="AY19" s="3" t="n"/>
-      <c r="AZ19" s="3" t="n"/>
+      <c r="AX19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA19" s="3" t="n"/>
-      <c r="BB19" s="2" t="n">
-        <v>5221</v>
-      </c>
+      <c r="BB19" s="3" t="n"/>
       <c r="BC19" s="3" t="n"/>
       <c r="BD19" s="3" t="n"/>
       <c r="BE19" s="3" t="n"/>
       <c r="BF19" s="3" t="n"/>
-      <c r="BG19" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH19" s="3" t="n"/>
-      <c r="BI19" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG19" s="3" t="n"/>
+      <c r="BH19" s="2" t="n">
+        <v>5221</v>
+      </c>
+      <c r="BI19" s="3" t="n"/>
       <c r="BJ19" s="3" t="n"/>
       <c r="BK19" s="3" t="n"/>
       <c r="BL19" s="3" t="n"/>
       <c r="BM19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN19" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO19" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN19" s="3" t="n"/>
+      <c r="BO19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP19" s="3" t="n"/>
       <c r="BQ19" s="3" t="n"/>
       <c r="BR19" s="3" t="n"/>
-      <c r="BS19" s="3" t="n"/>
-      <c r="BT19" s="3" t="n"/>
-      <c r="BU19" s="3" t="n"/>
+      <c r="BS19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT19" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU19" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BV19" s="3" t="n"/>
       <c r="BW19" s="3" t="n"/>
       <c r="BX19" s="3" t="n"/>
@@ -5362,30 +5382,12 @@
       <c r="CF19" s="3" t="n"/>
       <c r="CG19" s="3" t="n"/>
       <c r="CH19" s="3" t="n"/>
-      <c r="CI19" s="6">
-        <f>IFERROR(AVERAGEIF(P679:P716,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ19" s="6">
-        <f>IFERROR(AVERAGEIF(Q679:Q716,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK19" s="6">
-        <f>IFERROR(AVERAGEIF(R679:R716,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL19" s="6">
-        <f>IFERROR(AVERAGEIF(S679:S716,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM19" s="6">
-        <f>IFERROR(AVERAGEIF(T679:T716,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN19" s="6">
-        <f>IFERROR(AVERAGEIF(U679:U716,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI19" s="3" t="n"/>
+      <c r="CJ19" s="3" t="n"/>
+      <c r="CK19" s="3" t="n"/>
+      <c r="CL19" s="3" t="n"/>
+      <c r="CM19" s="3" t="n"/>
+      <c r="CN19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5496,99 +5498,117 @@
       <c r="AF20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG20" s="2" t="inlineStr">
+      <c r="AG20" s="6">
+        <f>IFERROR(AVERAGEIF(P718:P754,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="6">
+        <f>IFERROR(AVERAGEIF(Q718:Q754,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI20" s="6">
+        <f>IFERROR(AVERAGEIF(R718:R754,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="6">
+        <f>IFERROR(AVERAGEIF(S718:S754,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK20" s="6">
+        <f>IFERROR(AVERAGEIF(T718:T754,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL20" s="6">
+        <f>IFERROR(AVERAGEIF(U718:U754,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM20" s="2" t="inlineStr">
         <is>
           <t>2025-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AH20" s="2" t="inlineStr">
+      <c r="AN20" s="2" t="inlineStr">
         <is>
           <t>2025-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AI20" s="3" t="n"/>
-      <c r="AJ20" s="2" t="inlineStr">
+      <c r="AO20" s="3" t="n"/>
+      <c r="AP20" s="2" t="inlineStr">
         <is>
           <t>2026-08-12T00:00:00</t>
         </is>
       </c>
-      <c r="AK20" s="2" t="inlineStr">
+      <c r="AQ20" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL20" s="2" t="inlineStr">
+      <c r="AR20" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM20" s="3" t="n"/>
-      <c r="AN20" s="3" t="n"/>
-      <c r="AO20" s="3" t="n"/>
-      <c r="AP20" s="2" t="n">
+      <c r="AS20" s="3" t="n"/>
+      <c r="AT20" s="3" t="n"/>
+      <c r="AU20" s="3" t="n"/>
+      <c r="AV20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ20" s="2" t="inlineStr">
+      <c r="AW20" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="3" t="n"/>
-      <c r="AV20" s="3" t="n"/>
-      <c r="AW20" s="3" t="n"/>
-      <c r="AX20" s="3" t="n"/>
-      <c r="AY20" s="3" t="n"/>
-      <c r="AZ20" s="3" t="n"/>
+      <c r="AX20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA20" s="3" t="n"/>
-      <c r="BB20" s="2" t="n">
-        <v>5210</v>
-      </c>
+      <c r="BB20" s="3" t="n"/>
       <c r="BC20" s="3" t="n"/>
       <c r="BD20" s="3" t="n"/>
       <c r="BE20" s="3" t="n"/>
       <c r="BF20" s="3" t="n"/>
-      <c r="BG20" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH20" s="3" t="n"/>
-      <c r="BI20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG20" s="3" t="n"/>
+      <c r="BH20" s="2" t="n">
+        <v>5210</v>
+      </c>
+      <c r="BI20" s="3" t="n"/>
       <c r="BJ20" s="3" t="n"/>
       <c r="BK20" s="3" t="n"/>
       <c r="BL20" s="3" t="n"/>
       <c r="BM20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN20" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO20" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN20" s="3" t="n"/>
+      <c r="BO20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP20" s="3" t="n"/>
       <c r="BQ20" s="3" t="n"/>
       <c r="BR20" s="3" t="n"/>
-      <c r="BS20" s="3" t="n"/>
-      <c r="BT20" s="3" t="n"/>
-      <c r="BU20" s="3" t="n"/>
+      <c r="BS20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT20" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU20" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BV20" s="3" t="n"/>
       <c r="BW20" s="3" t="n"/>
       <c r="BX20" s="3" t="n"/>
@@ -5602,30 +5622,12 @@
       <c r="CF20" s="3" t="n"/>
       <c r="CG20" s="3" t="n"/>
       <c r="CH20" s="3" t="n"/>
-      <c r="CI20" s="6">
-        <f>IFERROR(AVERAGEIF(P718:P754,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ20" s="6">
-        <f>IFERROR(AVERAGEIF(Q718:Q754,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK20" s="6">
-        <f>IFERROR(AVERAGEIF(R718:R754,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL20" s="6">
-        <f>IFERROR(AVERAGEIF(S718:S754,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM20" s="6">
-        <f>IFERROR(AVERAGEIF(T718:T754,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN20" s="6">
-        <f>IFERROR(AVERAGEIF(U718:U754,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI20" s="3" t="n"/>
+      <c r="CJ20" s="3" t="n"/>
+      <c r="CK20" s="3" t="n"/>
+      <c r="CL20" s="3" t="n"/>
+      <c r="CM20" s="3" t="n"/>
+      <c r="CN20" s="3" t="n"/>
     </row>
     <row r="21" ht="26.5" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -5736,97 +5738,115 @@
       <c r="AF21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG21" s="2" t="inlineStr">
+      <c r="AG21" s="6">
+        <f>IFERROR(AVERAGEIF(P756:P786,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="6">
+        <f>IFERROR(AVERAGEIF(Q756:Q786,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI21" s="6">
+        <f>IFERROR(AVERAGEIF(R756:R786,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="6">
+        <f>IFERROR(AVERAGEIF(S756:S786,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="6">
+        <f>IFERROR(AVERAGEIF(T756:T786,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="6">
+        <f>IFERROR(AVERAGEIF(U756:U786,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="2" t="inlineStr">
         <is>
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="AH21" s="3" t="n"/>
-      <c r="AI21" s="2" t="inlineStr">
+      <c r="AN21" s="3" t="n"/>
+      <c r="AO21" s="2" t="inlineStr">
         <is>
           <t>9999-12-31T00:00:00</t>
         </is>
       </c>
-      <c r="AJ21" s="2" t="inlineStr">
+      <c r="AP21" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T00:00:00</t>
         </is>
       </c>
-      <c r="AK21" s="2" t="inlineStr">
+      <c r="AQ21" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL21" s="2" t="inlineStr">
+      <c r="AR21" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="n"/>
-      <c r="AN21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="3" t="n"/>
-      <c r="AP21" s="2" t="n">
+      <c r="AS21" s="3" t="n"/>
+      <c r="AT21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="3" t="n"/>
+      <c r="AV21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ21" s="2" t="inlineStr">
+      <c r="AW21" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" s="3" t="n"/>
-      <c r="AV21" s="3" t="n"/>
-      <c r="AW21" s="3" t="n"/>
-      <c r="AX21" s="3" t="n"/>
-      <c r="AY21" s="3" t="n"/>
-      <c r="AZ21" s="3" t="n"/>
+      <c r="AX21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA21" s="3" t="n"/>
-      <c r="BB21" s="2" t="n">
-        <v>4321</v>
-      </c>
+      <c r="BB21" s="3" t="n"/>
       <c r="BC21" s="3" t="n"/>
       <c r="BD21" s="3" t="n"/>
       <c r="BE21" s="3" t="n"/>
       <c r="BF21" s="3" t="n"/>
       <c r="BG21" s="3" t="n"/>
-      <c r="BH21" s="3" t="n"/>
-      <c r="BI21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BH21" s="2" t="n">
+        <v>4321</v>
+      </c>
+      <c r="BI21" s="3" t="n"/>
       <c r="BJ21" s="3" t="n"/>
       <c r="BK21" s="3" t="n"/>
       <c r="BL21" s="3" t="n"/>
-      <c r="BM21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN21" s="2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="BO21" s="2" t="inlineStr">
-        <is>
-          <t>RIBA-ROJA DE TURIA</t>
-        </is>
+      <c r="BM21" s="3" t="n"/>
+      <c r="BN21" s="3" t="n"/>
+      <c r="BO21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP21" s="3" t="n"/>
       <c r="BQ21" s="3" t="n"/>
       <c r="BR21" s="3" t="n"/>
-      <c r="BS21" s="3" t="n"/>
-      <c r="BT21" s="3" t="n"/>
-      <c r="BU21" s="3" t="n"/>
+      <c r="BS21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT21" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="BU21" s="2" t="inlineStr">
+        <is>
+          <t>RIBA-ROJA DE TURIA</t>
+        </is>
+      </c>
       <c r="BV21" s="3" t="n"/>
       <c r="BW21" s="3" t="n"/>
       <c r="BX21" s="3" t="n"/>
@@ -5840,30 +5860,12 @@
       <c r="CF21" s="3" t="n"/>
       <c r="CG21" s="3" t="n"/>
       <c r="CH21" s="3" t="n"/>
-      <c r="CI21" s="6">
-        <f>IFERROR(AVERAGEIF(P756:P786,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ21" s="6">
-        <f>IFERROR(AVERAGEIF(Q756:Q786,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK21" s="6">
-        <f>IFERROR(AVERAGEIF(R756:R786,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL21" s="6">
-        <f>IFERROR(AVERAGEIF(S756:S786,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM21" s="6">
-        <f>IFERROR(AVERAGEIF(T756:T786,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN21" s="6">
-        <f>IFERROR(AVERAGEIF(U756:U786,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI21" s="3" t="n"/>
+      <c r="CJ21" s="3" t="n"/>
+      <c r="CK21" s="3" t="n"/>
+      <c r="CL21" s="3" t="n"/>
+      <c r="CM21" s="3" t="n"/>
+      <c r="CN21" s="3" t="n"/>
     </row>
     <row r="22" ht="26.5" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -5974,97 +5976,115 @@
       <c r="AF22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG22" s="2" t="inlineStr">
+      <c r="AG22" s="6">
+        <f>IFERROR(AVERAGEIF(P788:P818,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="6">
+        <f>IFERROR(AVERAGEIF(Q788:Q818,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI22" s="6">
+        <f>IFERROR(AVERAGEIF(R788:R818,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="6">
+        <f>IFERROR(AVERAGEIF(S788:S818,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK22" s="6">
+        <f>IFERROR(AVERAGEIF(T788:T818,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL22" s="6">
+        <f>IFERROR(AVERAGEIF(U788:U818,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM22" s="2" t="inlineStr">
         <is>
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="AH22" s="3" t="n"/>
-      <c r="AI22" s="2" t="inlineStr">
+      <c r="AN22" s="3" t="n"/>
+      <c r="AO22" s="2" t="inlineStr">
         <is>
           <t>9999-12-31T00:00:00</t>
         </is>
       </c>
-      <c r="AJ22" s="2" t="inlineStr">
+      <c r="AP22" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T00:00:00</t>
         </is>
       </c>
-      <c r="AK22" s="2" t="inlineStr">
+      <c r="AQ22" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL22" s="2" t="inlineStr">
+      <c r="AR22" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM22" s="3" t="n"/>
-      <c r="AN22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="3" t="n"/>
-      <c r="AP22" s="2" t="n">
+      <c r="AS22" s="3" t="n"/>
+      <c r="AT22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="3" t="n"/>
+      <c r="AV22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ22" s="2" t="inlineStr">
+      <c r="AW22" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AR22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" s="3" t="n"/>
-      <c r="AV22" s="3" t="n"/>
-      <c r="AW22" s="3" t="n"/>
-      <c r="AX22" s="3" t="n"/>
-      <c r="AY22" s="3" t="n"/>
-      <c r="AZ22" s="3" t="n"/>
+      <c r="AX22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA22" s="3" t="n"/>
-      <c r="BB22" s="2" t="n">
-        <v>5210</v>
-      </c>
+      <c r="BB22" s="3" t="n"/>
       <c r="BC22" s="3" t="n"/>
       <c r="BD22" s="3" t="n"/>
       <c r="BE22" s="3" t="n"/>
       <c r="BF22" s="3" t="n"/>
       <c r="BG22" s="3" t="n"/>
-      <c r="BH22" s="3" t="n"/>
-      <c r="BI22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BH22" s="2" t="n">
+        <v>5210</v>
+      </c>
+      <c r="BI22" s="3" t="n"/>
       <c r="BJ22" s="3" t="n"/>
       <c r="BK22" s="3" t="n"/>
       <c r="BL22" s="3" t="n"/>
-      <c r="BM22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN22" s="2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="BO22" s="2" t="inlineStr">
-        <is>
-          <t>RIBA-ROJA DE TURIA</t>
-        </is>
+      <c r="BM22" s="3" t="n"/>
+      <c r="BN22" s="3" t="n"/>
+      <c r="BO22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP22" s="3" t="n"/>
       <c r="BQ22" s="3" t="n"/>
       <c r="BR22" s="3" t="n"/>
-      <c r="BS22" s="3" t="n"/>
-      <c r="BT22" s="3" t="n"/>
-      <c r="BU22" s="3" t="n"/>
+      <c r="BS22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT22" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="BU22" s="2" t="inlineStr">
+        <is>
+          <t>RIBA-ROJA DE TURIA</t>
+        </is>
+      </c>
       <c r="BV22" s="3" t="n"/>
       <c r="BW22" s="3" t="n"/>
       <c r="BX22" s="3" t="n"/>
@@ -6078,30 +6098,12 @@
       <c r="CF22" s="3" t="n"/>
       <c r="CG22" s="3" t="n"/>
       <c r="CH22" s="3" t="n"/>
-      <c r="CI22" s="6">
-        <f>IFERROR(AVERAGEIF(P788:P818,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ22" s="6">
-        <f>IFERROR(AVERAGEIF(Q788:Q818,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK22" s="6">
-        <f>IFERROR(AVERAGEIF(R788:R818,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL22" s="6">
-        <f>IFERROR(AVERAGEIF(S788:S818,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM22" s="6">
-        <f>IFERROR(AVERAGEIF(T788:T818,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN22" s="6">
-        <f>IFERROR(AVERAGEIF(U788:U818,"&gt;0"),0)</f>
-        <v/>
-      </c>
+      <c r="CI22" s="3" t="n"/>
+      <c r="CJ22" s="3" t="n"/>
+      <c r="CK22" s="3" t="n"/>
+      <c r="CL22" s="3" t="n"/>
+      <c r="CM22" s="3" t="n"/>
+      <c r="CN22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -6212,99 +6214,117 @@
       <c r="AF23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AG23" s="2" t="inlineStr">
+      <c r="AG23" s="6">
+        <f>IFERROR(AVERAGEIF(P820:P857,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AH23" s="6">
+        <f>IFERROR(AVERAGEIF(Q820:Q857,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AI23" s="6">
+        <f>IFERROR(AVERAGEIF(R820:R857,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="6">
+        <f>IFERROR(AVERAGEIF(S820:S857,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AK23" s="6">
+        <f>IFERROR(AVERAGEIF(T820:T857,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AL23" s="6">
+        <f>IFERROR(AVERAGEIF(U820:U857,"&gt;0"),0)</f>
+        <v/>
+      </c>
+      <c r="AM23" s="2" t="inlineStr">
         <is>
           <t>2025-12-10T00:00:00</t>
         </is>
       </c>
-      <c r="AH23" s="2" t="inlineStr">
+      <c r="AN23" s="2" t="inlineStr">
         <is>
           <t>2025-12-10T00:00:00</t>
         </is>
       </c>
-      <c r="AI23" s="3" t="n"/>
-      <c r="AJ23" s="2" t="inlineStr">
+      <c r="AO23" s="3" t="n"/>
+      <c r="AP23" s="2" t="inlineStr">
         <is>
           <t>2026-08-12T00:00:00</t>
         </is>
       </c>
-      <c r="AK23" s="2" t="inlineStr">
+      <c r="AQ23" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL23" s="2" t="inlineStr">
+      <c r="AR23" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
-      <c r="AM23" s="3" t="n"/>
-      <c r="AN23" s="3" t="n"/>
-      <c r="AO23" s="3" t="n"/>
-      <c r="AP23" s="2" t="n">
+      <c r="AS23" s="3" t="n"/>
+      <c r="AT23" s="3" t="n"/>
+      <c r="AU23" s="3" t="n"/>
+      <c r="AV23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AQ23" s="2" t="inlineStr">
+      <c r="AW23" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AR23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" s="3" t="n"/>
-      <c r="AV23" s="3" t="n"/>
-      <c r="AW23" s="3" t="n"/>
-      <c r="AX23" s="3" t="n"/>
-      <c r="AY23" s="3" t="n"/>
-      <c r="AZ23" s="3" t="n"/>
+      <c r="AX23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA23" s="3" t="n"/>
-      <c r="BB23" s="2" t="n">
-        <v>9820</v>
-      </c>
+      <c r="BB23" s="3" t="n"/>
       <c r="BC23" s="3" t="n"/>
       <c r="BD23" s="3" t="n"/>
       <c r="BE23" s="3" t="n"/>
       <c r="BF23" s="3" t="n"/>
-      <c r="BG23" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="BH23" s="3" t="n"/>
-      <c r="BI23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG23" s="3" t="n"/>
+      <c r="BH23" s="2" t="n">
+        <v>9820</v>
+      </c>
+      <c r="BI23" s="3" t="n"/>
       <c r="BJ23" s="3" t="n"/>
       <c r="BK23" s="3" t="n"/>
       <c r="BL23" s="3" t="n"/>
       <c r="BM23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BN23" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BO23" s="2" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN23" s="3" t="n"/>
+      <c r="BO23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BP23" s="3" t="n"/>
       <c r="BQ23" s="3" t="n"/>
       <c r="BR23" s="3" t="n"/>
-      <c r="BS23" s="3" t="n"/>
-      <c r="BT23" s="3" t="n"/>
-      <c r="BU23" s="3" t="n"/>
+      <c r="BS23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BT23" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BU23" s="2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
       <c r="BV23" s="3" t="n"/>
       <c r="BW23" s="3" t="n"/>
       <c r="BX23" s="3" t="n"/>
@@ -6318,32 +6338,21 @@
       <c r="CF23" s="3" t="n"/>
       <c r="CG23" s="3" t="n"/>
       <c r="CH23" s="3" t="n"/>
-      <c r="CI23" s="6">
-        <f>IFERROR(AVERAGEIF(P820:P857,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CJ23" s="6">
-        <f>IFERROR(AVERAGEIF(Q820:Q857,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CK23" s="6">
-        <f>IFERROR(AVERAGEIF(R820:R857,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CL23" s="6">
-        <f>IFERROR(AVERAGEIF(S820:S857,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CM23" s="6">
-        <f>IFERROR(AVERAGEIF(T820:T857,"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="CN23" s="6">
-        <f>IFERROR(AVERAGEIF(U820:U857,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="CI23" s="3" t="n"/>
+      <c r="CJ23" s="3" t="n"/>
+      <c r="CK23" s="3" t="n"/>
+      <c r="CL23" s="3" t="n"/>
+      <c r="CM23" s="3" t="n"/>
+      <c r="CN23" s="3" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29" customFormat="1" s="5"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>

--- a/MAXIMETRO_GRUPO_ALBACETE_medias.xlsx
+++ b/MAXIMETRO_GRUPO_ALBACETE_medias.xlsx
@@ -577,459 +577,411 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Empresa Distribuidora</t>
+          <t>Codigo Postal PS</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Nombre Empresa Distribuidora</t>
+          <t>Municipio PS</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Postal PS</t>
+          <t>Tarifa</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Municipio PS</t>
+          <t>Consumo Anual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Provincia PS</t>
+          <t>Potencia Maxima BIEW</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Tension</t>
+          <t>Valor Derechos ExtensionW</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Tarifa</t>
+          <t>Valor Derechos AccesoW</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Consumo Anual</t>
+          <t>Consumo Anual P1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Alta Suministro</t>
+          <t>Consumo Anual P2</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Codigo TensionV</t>
+          <t>Consumo Anual P3</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Potencia Maxima BIEW</t>
+          <t>Consumo Anual P4</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Potencia Maxima APMW</t>
+          <t>Consumo Anual P5</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Clasificacion PS</t>
+          <t>Consumo Anual P6</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Disponibilidad ICP</t>
+          <t>Potencias Contratadas En W P1</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Tipo Perfil Consumo</t>
+          <t>Potencias Contratadas En W P2</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Valor Derechos ExtensionW</t>
+          <t>Potencias Contratadas En W P3</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Valor Derechos AccesoW</t>
+          <t>Potencias Contratadas En W P4</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Propiedad EquipoMedida</t>
+          <t>Potencias Contratadas En W P5</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Propiedad ICP</t>
+          <t>Potencias Contratadas En W P6</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Consumo Anual P1</t>
+          <t>Media Maximetro P1 (sin 0s)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Consumo Anual P2</t>
+          <t>Media Maximetro P2 (sin 0s)</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Consumo Anual P3</t>
+          <t>Media Maximetro P3 (sin 0s)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Consumo Anual P4</t>
+          <t>Media Maximetro P4 (sin 0s)</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Consumo Anual P5</t>
+          <t>Media Maximetro P5 (sin 0s)</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Consumo Anual P6</t>
+          <t>Media Maximetro P6 (sin 0s)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Potencias Contratadas En W P1</t>
+          <t>Fecha Ultimo Movimiento Contrato</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Potencias Contratadas En W P2</t>
+          <t>Fecha Ultimo Cambio Comercializador</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Potencias Contratadas En W P3</t>
+          <t>Fecha Limite Derechos Reconocidos</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Potencias Contratadas En W P4</t>
+          <t>Fecha Ultima Lectura</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Potencias Contratadas En W P5</t>
+          <t>Informacion Impagos</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Potencias Contratadas En W P6</t>
+          <t>Importe Deposito Garantia Euros</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Media Maximetro P1 (sin 0s)</t>
+          <t>Tipo Id Titular</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Media Maximetro P2 (sin 0s)</t>
+          <t>Es Vivienda Habitual</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Media Maximetro P3 (sin 0s)</t>
+          <t>Codigo Comercializadora</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Media Maximetro P4 (sin 0s)</t>
+          <t>Codigo Telegestion</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Media Maximetro P5 (sin 0s)</t>
+          <t>Codigo Fases Equipo Medida</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Media Maximetro P6 (sin 0s)</t>
+          <t>Codigo Autoconsumo</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Ultimo Movimiento Contrato</t>
+          <t>Codigo TipoContrato</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Ultimo Cambio Comercializador</t>
+          <t>Codigo Periodicidad Facturacion</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Limite Derechos Reconocidos</t>
+          <t>Codigo BIE</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Ultima Lectura</t>
+          <t>Fecha Emision BIE</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Informacion Impagos</t>
+          <t>Fecha Caducidad BIE</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Importe Deposito Garantia Euros</t>
+          <t>Codigo APM</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Tipo Id Titular</t>
+          <t>Fecha Emision APM</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Es Vivienda Habitual</t>
+          <t>Fecha Caducidad APM</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Comercializadora</t>
+          <t>Relacion Transformacion Intensidad</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Telegestion</t>
+          <t>CNAE</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Fases Equipo Medida</t>
+          <t>Codigo Modo Control Potencia</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Autoconsumo</t>
+          <t>Potencia CGPW</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>Codigo TipoContrato</t>
+          <t>Codigo DH Equipo De Medida</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Periodicidad Facturacion</t>
+          <t>Codigo Accesibilidad Contador</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>Codigo BIE</t>
+          <t>Codigo PS Contratable</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Emision BIE</t>
+          <t>Motivo Estado No Contratable</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Caducidad BIE</t>
+          <t>Codigo Tension Medida</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>Codigo APM</t>
+          <t>Codigo Clase Expediente</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Emision APM</t>
+          <t>Codigo Motivo Expediente</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Caducidad APM</t>
+          <t>Codigo Tipo Suministro</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>Relacion Transformacion Intensidad</t>
+          <t>Aplicacion Bono Social</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>CNAE</t>
+          <t>Descripcion Provincia PS</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Modo Control Potencia</t>
+          <t>Descripcion Municipio PS</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>Potencia CGPW</t>
+          <t>Tipo Via PS</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>Codigo DH Equipo De Medida</t>
+          <t>Via PS</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Accesibilidad Contador</t>
+          <t>Num Finca PS</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>Codigo PS Contratable</t>
+          <t>Portal PS</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>Motivo Estado No Contratable</t>
+          <t>Escalera PS</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Tension Medida</t>
+          <t>Piso PS</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Clase Expediente</t>
+          <t>Puerta PS</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Motivo Expediente</t>
+          <t>Codigo Presion</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>Codigo Tipo Suministro</t>
+          <t>Codigo Peaje En Vigor</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>Aplicacion Bono Social</t>
+          <t>Caudal Maximo Diario En Wh</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>Descripcion Provincia PS</t>
+          <t>Caudal Horario En Wh</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>Descripcion Municipio PS</t>
+          <t>Derecho TUR</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>Tipo Via PS</t>
+          <t>Fecha Ultima Inspeccion</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>Via PS</t>
+          <t>Codigo Resultado Inspeccion</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>Num Finca PS</t>
+          <t>Codigo Contador</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>Portal PS</t>
+          <t>Calibre Contador</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>Escalera PS</t>
+          <t>Tipo Contador</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>Piso PS</t>
+          <t>Propiedad Equipo Medida</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>Puerta PS</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>Codigo Presion</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>Codigo Peaje En Vigor</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>Caudal Maximo Diario En Wh</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>Caudal Horario En Wh</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>Derecho TUR</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha Ultima Inspeccion</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>Codigo Resultado Inspeccion</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>Codigo Contador</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>Calibre Contador</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo Contador</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>Propiedad Equipo Medida</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
           <t>Codigo Telemedida</t>
         </is>
       </c>
+      <c r="CC1" s="1" t="n"/>
+      <c r="CD1" s="1" t="n"/>
+      <c r="CE1" s="1" t="n"/>
+      <c r="CF1" s="1" t="n"/>
+      <c r="CG1" s="1" t="n"/>
+      <c r="CH1" s="1" t="n"/>
+      <c r="CI1" s="1" t="n"/>
+      <c r="CJ1" s="1" t="n"/>
+      <c r="CK1" s="1" t="n"/>
+      <c r="CL1" s="1" t="n"/>
+      <c r="CM1" s="1" t="n"/>
+      <c r="CN1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1038,219 +990,187 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
         <v>2005</v>
       </c>
+      <c r="C2" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3.0TD ML</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="n">
-        <v>2003</v>
+        <v>67102</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>3.0TD ML</t>
-        </is>
+        <v>17320</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>17320</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>17320</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>67102</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2009-05-21T00:00:00</t>
-        </is>
+        <v>14155</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>13329</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>6</v>
+        <v>7040</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>17320</v>
+        <v>5360</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>1938</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>4</v>
+        <v>25280</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
+        <v>17.32</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>17.32</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>17320</v>
+        <v>17.32</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>17320</v>
+        <v>17.32</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>1</v>
+        <v>17.32</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>14155</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>13329</v>
-      </c>
-      <c r="W2" s="2" t="n">
-        <v>7040</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>5360</v>
-      </c>
-      <c r="Y2" s="2" t="n">
-        <v>1938</v>
-      </c>
-      <c r="Z2" s="2" t="n">
-        <v>25280</v>
-      </c>
-      <c r="AA2" s="2" t="n">
         <v>17.32</v>
       </c>
-      <c r="AB2" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AE2" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AG2" s="6">
+      <c r="U2" s="6">
         <f>IFERROR(AVERAGEIF(P34:P71,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH2" s="6">
+      <c r="V2" s="6">
         <f>IFERROR(AVERAGEIF(Q34:Q71,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI2" s="6">
+      <c r="W2" s="6">
         <f>IFERROR(AVERAGEIF(R34:R71,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ2" s="6">
+      <c r="X2" s="6">
         <f>IFERROR(AVERAGEIF(S34:S71,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK2" s="6">
+      <c r="Y2" s="6">
         <f>IFERROR(AVERAGEIF(T34:T71,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL2" s="6">
+      <c r="Z2" s="6">
         <f>IFERROR(AVERAGEIF(U34:U71,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>2025-10-28T00:00:00</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>2025-10-28T00:00:00</t>
         </is>
       </c>
+      <c r="AC2" s="3" t="n"/>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="n"/>
+      <c r="AH2" s="3" t="n"/>
+      <c r="AI2" s="3" t="n"/>
+      <c r="AJ2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO2" s="3" t="n"/>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR2" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP2" s="3" t="n"/>
+      <c r="AQ2" s="3" t="n"/>
+      <c r="AR2" s="3" t="n"/>
       <c r="AS2" s="3" t="n"/>
       <c r="AT2" s="3" t="n"/>
       <c r="AU2" s="3" t="n"/>
       <c r="AV2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="3" t="n"/>
+        <v>9531</v>
+      </c>
+      <c r="AW2" s="3" t="n"/>
+      <c r="AX2" s="3" t="n"/>
+      <c r="AY2" s="3" t="n"/>
+      <c r="AZ2" s="3" t="n"/>
+      <c r="BA2" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB2" s="3" t="n"/>
-      <c r="BC2" s="3" t="n"/>
+      <c r="BC2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD2" s="3" t="n"/>
       <c r="BE2" s="3" t="n"/>
       <c r="BF2" s="3" t="n"/>
-      <c r="BG2" s="3" t="n"/>
-      <c r="BH2" s="2" t="n">
-        <v>9531</v>
-      </c>
-      <c r="BI2" s="3" t="n"/>
+      <c r="BG2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH2" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
       <c r="BJ2" s="3" t="n"/>
       <c r="BK2" s="3" t="n"/>
       <c r="BL2" s="3" t="n"/>
-      <c r="BM2" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM2" s="3" t="n"/>
       <c r="BN2" s="3" t="n"/>
-      <c r="BO2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO2" s="3" t="n"/>
       <c r="BP2" s="3" t="n"/>
       <c r="BQ2" s="3" t="n"/>
       <c r="BR2" s="3" t="n"/>
-      <c r="BS2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT2" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU2" s="2" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
+      <c r="BS2" s="3" t="n"/>
+      <c r="BT2" s="3" t="n"/>
+      <c r="BU2" s="3" t="n"/>
       <c r="BV2" s="3" t="n"/>
       <c r="BW2" s="3" t="n"/>
       <c r="BX2" s="3" t="n"/>
@@ -1278,223 +1198,191 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
         <v>2611</v>
       </c>
+      <c r="C3" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>3.0TD ML</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="n">
-        <v>2057</v>
+        <v>34290</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>3.0TD ML</t>
-        </is>
+        <v>17321</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>13856</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>13856</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34290</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>1993-12-01T00:00:00</t>
-        </is>
+        <v>5854</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>6325</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>6</v>
+        <v>3705</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>17321</v>
+        <v>3980</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0</v>
+        <v>1496</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>4</v>
+        <v>12930</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
+        <v>13.86</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>13.86</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>13856</v>
+        <v>13.86</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>13856</v>
+        <v>13.86</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>1</v>
+        <v>13.86</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>5854</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>6325</v>
-      </c>
-      <c r="W3" s="2" t="n">
-        <v>3705</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>3980</v>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>1496</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>12930</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AB3" s="2" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AC3" s="2" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AD3" s="2" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AE3" s="2" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AF3" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="AG3" s="6">
+      <c r="U3" s="6">
         <f>IFERROR(AVERAGEIF(P73:P110,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH3" s="6">
+      <c r="V3" s="6">
         <f>IFERROR(AVERAGEIF(Q73:Q110,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI3" s="6">
+      <c r="W3" s="6">
         <f>IFERROR(AVERAGEIF(R73:R110,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ3" s="6">
+      <c r="X3" s="6">
         <f>IFERROR(AVERAGEIF(S73:S110,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK3" s="6">
+      <c r="Y3" s="6">
         <f>IFERROR(AVERAGEIF(T73:T110,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL3" s="6">
+      <c r="Z3" s="6">
         <f>IFERROR(AVERAGEIF(U73:U110,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AN3" s="2" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AO3" s="2" t="inlineStr">
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>2027-01-10T00:00:00</t>
         </is>
       </c>
-      <c r="AP3" s="2" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AQ3" s="2" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AR3" s="2" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
+      <c r="AG3" s="3" t="n"/>
+      <c r="AH3" s="3" t="n"/>
+      <c r="AI3" s="3" t="n"/>
+      <c r="AJ3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="3" t="n"/>
+      <c r="AP3" s="3" t="n"/>
+      <c r="AQ3" s="3" t="n"/>
+      <c r="AR3" s="3" t="n"/>
       <c r="AS3" s="3" t="n"/>
       <c r="AT3" s="3" t="n"/>
       <c r="AU3" s="3" t="n"/>
       <c r="AV3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW3" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" s="3" t="n"/>
+        <v>5210</v>
+      </c>
+      <c r="AW3" s="3" t="n"/>
+      <c r="AX3" s="3" t="n"/>
+      <c r="AY3" s="3" t="n"/>
+      <c r="AZ3" s="3" t="n"/>
+      <c r="BA3" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB3" s="3" t="n"/>
-      <c r="BC3" s="3" t="n"/>
+      <c r="BC3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD3" s="3" t="n"/>
       <c r="BE3" s="3" t="n"/>
       <c r="BF3" s="3" t="n"/>
-      <c r="BG3" s="3" t="n"/>
-      <c r="BH3" s="2" t="n">
-        <v>5210</v>
-      </c>
-      <c r="BI3" s="3" t="n"/>
+      <c r="BG3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH3" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BJ3" s="3" t="n"/>
       <c r="BK3" s="3" t="n"/>
       <c r="BL3" s="3" t="n"/>
-      <c r="BM3" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM3" s="3" t="n"/>
       <c r="BN3" s="3" t="n"/>
-      <c r="BO3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO3" s="3" t="n"/>
       <c r="BP3" s="3" t="n"/>
       <c r="BQ3" s="3" t="n"/>
       <c r="BR3" s="3" t="n"/>
-      <c r="BS3" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT3" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU3" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
-      </c>
+      <c r="BS3" s="3" t="n"/>
+      <c r="BT3" s="3" t="n"/>
+      <c r="BU3" s="3" t="n"/>
       <c r="BV3" s="3" t="n"/>
       <c r="BW3" s="3" t="n"/>
       <c r="BX3" s="3" t="n"/>
@@ -1522,215 +1410,189 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>UFD DISTRIBUCIÓN ELECTRICIDAD, SA</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
         <v>45730</v>
       </c>
+      <c r="C4" s="2" t="n">
+        <v>451875</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6.1TD ML</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="n">
-        <v>451875</v>
+        <v>25438</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>17000</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6.1TD ML</t>
-        </is>
+        <v>50000</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>16000</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25438</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2008-05-16T00:00:00</t>
-        </is>
+        <v>1560</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>2171</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>26</v>
+        <v>1323</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>50000</v>
+        <v>1584</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>40000</v>
+        <v>754</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2</v>
+        <v>18046</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" s="3" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="Q4" s="2" t="n">
-        <v>16000</v>
+        <v>16</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>16000</v>
+        <v>16</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>1560</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>2171</v>
-      </c>
-      <c r="W4" s="2" t="n">
-        <v>1323</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>1584</v>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>754</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18046</v>
-      </c>
-      <c r="AA4" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="AB4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG4" s="6">
+      <c r="U4" s="6">
         <f>IFERROR(AVERAGEIF(P112:P146,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH4" s="6">
+      <c r="V4" s="6">
         <f>IFERROR(AVERAGEIF(Q112:Q146,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI4" s="6">
+      <c r="W4" s="6">
         <f>IFERROR(AVERAGEIF(R112:R146,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ4" s="6">
+      <c r="X4" s="6">
         <f>IFERROR(AVERAGEIF(S112:S146,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK4" s="6">
+      <c r="Y4" s="6">
         <f>IFERROR(AVERAGEIF(T112:T146,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL4" s="6">
+      <c r="Z4" s="6">
         <f>IFERROR(AVERAGEIF(U112:U146,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="AN4" s="2" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>2022-05-28T00:00:00</t>
         </is>
       </c>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="n"/>
+      <c r="AH4" s="3" t="n"/>
+      <c r="AI4" s="3" t="n"/>
+      <c r="AJ4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AO4" s="3" t="n"/>
-      <c r="AP4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR4" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP4" s="3" t="n"/>
+      <c r="AQ4" s="3" t="n"/>
+      <c r="AR4" s="3" t="n"/>
       <c r="AS4" s="3" t="n"/>
       <c r="AT4" s="3" t="n"/>
-      <c r="AU4" s="3" t="n"/>
+      <c r="AU4" s="2" t="inlineStr">
+        <is>
+          <t>100/5</t>
+        </is>
+      </c>
       <c r="AV4" s="2" t="n">
+        <v>3511</v>
+      </c>
+      <c r="AW4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AW4" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ4" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AX4" s="3" t="n"/>
+      <c r="AY4" s="3" t="n"/>
+      <c r="AZ4" s="3" t="n"/>
       <c r="BA4" s="3" t="n"/>
       <c r="BB4" s="3" t="n"/>
-      <c r="BC4" s="3" t="n"/>
+      <c r="BC4" s="2" t="n">
+        <v>26</v>
+      </c>
       <c r="BD4" s="3" t="n"/>
       <c r="BE4" s="3" t="n"/>
       <c r="BF4" s="3" t="n"/>
       <c r="BG4" s="2" t="inlineStr">
         <is>
-          <t>100/5</t>
-        </is>
-      </c>
-      <c r="BH4" s="2" t="n">
-        <v>3511</v>
-      </c>
-      <c r="BI4" s="2" t="n">
-        <v>2</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH4" s="2" t="inlineStr">
+        <is>
+          <t>TOLEDO</t>
+        </is>
+      </c>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Villafranca de los Caballeros</t>
+        </is>
       </c>
       <c r="BJ4" s="3" t="n"/>
       <c r="BK4" s="3" t="n"/>
       <c r="BL4" s="3" t="n"/>
       <c r="BM4" s="3" t="n"/>
       <c r="BN4" s="3" t="n"/>
-      <c r="BO4" s="2" t="n">
-        <v>26</v>
-      </c>
+      <c r="BO4" s="3" t="n"/>
       <c r="BP4" s="3" t="n"/>
       <c r="BQ4" s="3" t="n"/>
       <c r="BR4" s="3" t="n"/>
-      <c r="BS4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT4" s="2" t="inlineStr">
-        <is>
-          <t>TOLEDO</t>
-        </is>
-      </c>
-      <c r="BU4" s="2" t="inlineStr">
-        <is>
-          <t>Villafranca de los Caballeros</t>
-        </is>
-      </c>
+      <c r="BS4" s="3" t="n"/>
+      <c r="BT4" s="3" t="n"/>
+      <c r="BU4" s="3" t="n"/>
       <c r="BV4" s="3" t="n"/>
       <c r="BW4" s="3" t="n"/>
       <c r="BX4" s="3" t="n"/>
@@ -1758,219 +1620,187 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
         <v>2611</v>
       </c>
+      <c r="C5" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3.0TD ML</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
-        <v>2057</v>
+        <v>9410</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3.0TD ML</t>
-        </is>
+        <v>17321</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>17321</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>17321</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>9410</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1999-06-17T00:00:00</t>
-        </is>
+        <v>1281</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1547</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>6</v>
+        <v>916</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>17321</v>
+        <v>1210</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>4</v>
+        <v>3890</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
+        <v>17.32</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>17.32</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>17321</v>
+        <v>17.32</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>17321</v>
+        <v>17.32</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1</v>
+        <v>17.32</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>1281</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>1547</v>
-      </c>
-      <c r="W5" s="2" t="n">
-        <v>916</v>
-      </c>
-      <c r="X5" s="2" t="n">
-        <v>1210</v>
-      </c>
-      <c r="Y5" s="2" t="n">
-        <v>566</v>
-      </c>
-      <c r="Z5" s="2" t="n">
-        <v>3890</v>
-      </c>
-      <c r="AA5" s="2" t="n">
         <v>17.32</v>
       </c>
-      <c r="AB5" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AC5" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AD5" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AE5" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AG5" s="6">
+      <c r="U5" s="6">
         <f>IFERROR(AVERAGEIF(P148:P182,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH5" s="6">
+      <c r="V5" s="6">
         <f>IFERROR(AVERAGEIF(Q148:Q182,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI5" s="6">
+      <c r="W5" s="6">
         <f>IFERROR(AVERAGEIF(R148:R182,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ5" s="6">
+      <c r="X5" s="6">
         <f>IFERROR(AVERAGEIF(S148:S182,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK5" s="6">
+      <c r="Y5" s="6">
         <f>IFERROR(AVERAGEIF(T148:T182,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL5" s="6">
+      <c r="Z5" s="6">
         <f>IFERROR(AVERAGEIF(U148:U182,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>2026-02-28T00:00:00</t>
         </is>
       </c>
-      <c r="AN5" s="2" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>2021-11-22T00:00:00</t>
         </is>
       </c>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="n"/>
+      <c r="AH5" s="3" t="n"/>
+      <c r="AI5" s="3" t="n"/>
+      <c r="AJ5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO5" s="3" t="n"/>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR5" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP5" s="3" t="n"/>
+      <c r="AQ5" s="3" t="n"/>
+      <c r="AR5" s="3" t="n"/>
       <c r="AS5" s="3" t="n"/>
       <c r="AT5" s="3" t="n"/>
       <c r="AU5" s="3" t="n"/>
       <c r="AV5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="3" t="n"/>
+        <v>9820</v>
+      </c>
+      <c r="AW5" s="3" t="n"/>
+      <c r="AX5" s="3" t="n"/>
+      <c r="AY5" s="3" t="n"/>
+      <c r="AZ5" s="3" t="n"/>
+      <c r="BA5" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB5" s="3" t="n"/>
-      <c r="BC5" s="3" t="n"/>
+      <c r="BC5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD5" s="3" t="n"/>
       <c r="BE5" s="3" t="n"/>
       <c r="BF5" s="3" t="n"/>
-      <c r="BG5" s="3" t="n"/>
-      <c r="BH5" s="2" t="n">
-        <v>9820</v>
-      </c>
-      <c r="BI5" s="3" t="n"/>
+      <c r="BG5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH5" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BJ5" s="3" t="n"/>
       <c r="BK5" s="3" t="n"/>
       <c r="BL5" s="3" t="n"/>
-      <c r="BM5" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM5" s="3" t="n"/>
       <c r="BN5" s="3" t="n"/>
-      <c r="BO5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO5" s="3" t="n"/>
       <c r="BP5" s="3" t="n"/>
       <c r="BQ5" s="3" t="n"/>
       <c r="BR5" s="3" t="n"/>
-      <c r="BS5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT5" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU5" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
-      </c>
+      <c r="BS5" s="3" t="n"/>
+      <c r="BT5" s="3" t="n"/>
+      <c r="BU5" s="3" t="n"/>
       <c r="BV5" s="3" t="n"/>
       <c r="BW5" s="3" t="n"/>
       <c r="BX5" s="3" t="n"/>
@@ -1998,219 +1828,187 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
         <v>2008</v>
       </c>
+      <c r="C6" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>2003</v>
+        <v>1829</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1X230</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>5750</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>5750</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>5750</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1829</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2018-05-21T00:00:00</t>
-        </is>
+        <v>492</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>501</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
+        <v>836</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5750</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+        <v>5.75</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>5.75</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>5750</v>
+        <v>0</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>5750</v>
+        <v>0</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>492</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>501</v>
-      </c>
-      <c r="W6" s="2" t="n">
-        <v>836</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6">
         <f>IFERROR(AVERAGEIF(P184:P218,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH6" s="6">
+      <c r="V6" s="6">
         <f>IFERROR(AVERAGEIF(Q184:Q218,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI6" s="6">
+      <c r="W6" s="6">
         <f>IFERROR(AVERAGEIF(R184:R218,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ6" s="6">
+      <c r="X6" s="6">
         <f>IFERROR(AVERAGEIF(S184:S218,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK6" s="6">
+      <c r="Y6" s="6">
         <f>IFERROR(AVERAGEIF(T184:T218,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL6" s="6">
+      <c r="Z6" s="6">
         <f>IFERROR(AVERAGEIF(U184:U218,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>2021-05-31T00:00:00</t>
         </is>
       </c>
-      <c r="AN6" s="2" t="inlineStr">
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>2018-05-22T00:00:00</t>
         </is>
       </c>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="n"/>
+      <c r="AH6" s="3" t="n"/>
+      <c r="AI6" s="3" t="n"/>
+      <c r="AJ6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO6" s="3" t="n"/>
-      <c r="AP6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-02T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ6" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR6" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP6" s="3" t="n"/>
+      <c r="AQ6" s="3" t="n"/>
+      <c r="AR6" s="3" t="n"/>
       <c r="AS6" s="3" t="n"/>
       <c r="AT6" s="3" t="n"/>
       <c r="AU6" s="3" t="n"/>
       <c r="AV6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW6" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AX6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" s="3" t="n"/>
+        <v>9820</v>
+      </c>
+      <c r="AW6" s="3" t="n"/>
+      <c r="AX6" s="3" t="n"/>
+      <c r="AY6" s="3" t="n"/>
+      <c r="AZ6" s="3" t="n"/>
+      <c r="BA6" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB6" s="3" t="n"/>
-      <c r="BC6" s="3" t="n"/>
+      <c r="BC6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD6" s="3" t="n"/>
       <c r="BE6" s="3" t="n"/>
       <c r="BF6" s="3" t="n"/>
-      <c r="BG6" s="3" t="n"/>
-      <c r="BH6" s="2" t="n">
-        <v>9820</v>
-      </c>
-      <c r="BI6" s="3" t="n"/>
+      <c r="BG6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH6" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="n"/>
       <c r="BK6" s="3" t="n"/>
       <c r="BL6" s="3" t="n"/>
-      <c r="BM6" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM6" s="3" t="n"/>
       <c r="BN6" s="3" t="n"/>
-      <c r="BO6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO6" s="3" t="n"/>
       <c r="BP6" s="3" t="n"/>
       <c r="BQ6" s="3" t="n"/>
       <c r="BR6" s="3" t="n"/>
-      <c r="BS6" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT6" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU6" s="2" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
+      <c r="BS6" s="3" t="n"/>
+      <c r="BT6" s="3" t="n"/>
+      <c r="BU6" s="3" t="n"/>
       <c r="BV6" s="3" t="n"/>
       <c r="BW6" s="3" t="n"/>
       <c r="BX6" s="3" t="n"/>
@@ -2238,219 +2036,187 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
         <v>2007</v>
       </c>
+      <c r="C7" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3.0TD ML</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="n">
-        <v>2003</v>
+        <v>53715</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3.0TD ML</t>
-        </is>
+        <v>35800</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>20000</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>53715</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2008-11-21T00:00:00</t>
-        </is>
+        <v>9011</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>10188</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>6</v>
+        <v>7299</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>35800</v>
+        <v>5870</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>1401</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4</v>
+        <v>19946</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>20000</v>
+        <v>20</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>20000</v>
+        <v>20</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>9011</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>10188</v>
-      </c>
-      <c r="W7" s="2" t="n">
-        <v>7299</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>5870</v>
-      </c>
-      <c r="Y7" s="2" t="n">
-        <v>1401</v>
-      </c>
-      <c r="Z7" s="2" t="n">
-        <v>19946</v>
-      </c>
-      <c r="AA7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AB7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG7" s="6">
+      <c r="U7" s="6">
         <f>IFERROR(AVERAGEIF(P220:P255,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH7" s="6">
+      <c r="V7" s="6">
         <f>IFERROR(AVERAGEIF(Q220:Q255,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI7" s="6">
+      <c r="W7" s="6">
         <f>IFERROR(AVERAGEIF(R220:R255,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ7" s="6">
+      <c r="X7" s="6">
         <f>IFERROR(AVERAGEIF(S220:S255,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK7" s="6">
+      <c r="Y7" s="6">
         <f>IFERROR(AVERAGEIF(T220:T255,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL7" s="6">
+      <c r="Z7" s="6">
         <f>IFERROR(AVERAGEIF(U220:U255,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM7" s="2" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>2025-10-28T00:00:00</t>
         </is>
       </c>
-      <c r="AN7" s="2" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>2025-10-28T00:00:00</t>
         </is>
       </c>
+      <c r="AC7" s="3" t="n"/>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="n"/>
+      <c r="AH7" s="3" t="n"/>
+      <c r="AI7" s="3" t="n"/>
+      <c r="AJ7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO7" s="3" t="n"/>
-      <c r="AP7" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ7" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR7" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP7" s="3" t="n"/>
+      <c r="AQ7" s="3" t="n"/>
+      <c r="AR7" s="3" t="n"/>
       <c r="AS7" s="3" t="n"/>
       <c r="AT7" s="3" t="n"/>
       <c r="AU7" s="3" t="n"/>
       <c r="AV7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW7" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" s="3" t="n"/>
+        <v>4321</v>
+      </c>
+      <c r="AW7" s="3" t="n"/>
+      <c r="AX7" s="3" t="n"/>
+      <c r="AY7" s="3" t="n"/>
+      <c r="AZ7" s="3" t="n"/>
+      <c r="BA7" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB7" s="3" t="n"/>
-      <c r="BC7" s="3" t="n"/>
+      <c r="BC7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD7" s="3" t="n"/>
       <c r="BE7" s="3" t="n"/>
       <c r="BF7" s="3" t="n"/>
-      <c r="BG7" s="3" t="n"/>
-      <c r="BH7" s="2" t="n">
-        <v>4321</v>
-      </c>
-      <c r="BI7" s="3" t="n"/>
+      <c r="BG7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH7" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
       <c r="BJ7" s="3" t="n"/>
       <c r="BK7" s="3" t="n"/>
       <c r="BL7" s="3" t="n"/>
-      <c r="BM7" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM7" s="3" t="n"/>
       <c r="BN7" s="3" t="n"/>
-      <c r="BO7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO7" s="3" t="n"/>
       <c r="BP7" s="3" t="n"/>
       <c r="BQ7" s="3" t="n"/>
       <c r="BR7" s="3" t="n"/>
-      <c r="BS7" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT7" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU7" s="2" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
+      <c r="BS7" s="3" t="n"/>
+      <c r="BT7" s="3" t="n"/>
+      <c r="BU7" s="3" t="n"/>
       <c r="BV7" s="3" t="n"/>
       <c r="BW7" s="3" t="n"/>
       <c r="BX7" s="3" t="n"/>
@@ -2478,223 +2244,191 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
         <v>28816</v>
       </c>
+      <c r="C8" s="2" t="n">
+        <v>28032</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3.0TD ML</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>28032</v>
+        <v>2335</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3.0TD ML</t>
-        </is>
+        <v>22170</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>20000</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2335</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2015-08-27T00:00:00</t>
-        </is>
+        <v>295</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>325</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>6</v>
+        <v>329</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>22170</v>
+        <v>384</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4</v>
+        <v>862</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>20000</v>
+        <v>5</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>20000</v>
+        <v>5</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>295</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="W8" s="2" t="n">
-        <v>329</v>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>384</v>
-      </c>
-      <c r="Y8" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="Z8" s="2" t="n">
-        <v>862</v>
-      </c>
-      <c r="AA8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF8" s="2" t="n">
         <v>15.01</v>
       </c>
-      <c r="AG8" s="6">
+      <c r="U8" s="6">
         <f>IFERROR(AVERAGEIF(P257:P292,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH8" s="6">
+      <c r="V8" s="6">
         <f>IFERROR(AVERAGEIF(Q257:Q292,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI8" s="6">
+      <c r="W8" s="6">
         <f>IFERROR(AVERAGEIF(R257:R292,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ8" s="6">
+      <c r="X8" s="6">
         <f>IFERROR(AVERAGEIF(S257:S292,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK8" s="6">
+      <c r="Y8" s="6">
         <f>IFERROR(AVERAGEIF(T257:T292,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL8" s="6">
+      <c r="Z8" s="6">
         <f>IFERROR(AVERAGEIF(U257:U292,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>2024-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AN8" s="2" t="inlineStr">
+      <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>2024-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AO8" s="2" t="inlineStr">
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>2027-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AP8" s="2" t="inlineStr">
+      <c r="AD8" s="2" t="inlineStr">
         <is>
           <t>2026-07-31T00:00:00</t>
         </is>
       </c>
-      <c r="AQ8" s="2" t="inlineStr">
+      <c r="AE8" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AR8" s="2" t="inlineStr">
+      <c r="AF8" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
+      <c r="AG8" s="3" t="n"/>
+      <c r="AH8" s="3" t="n"/>
+      <c r="AI8" s="3" t="n"/>
+      <c r="AJ8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="3" t="n"/>
+      <c r="AP8" s="3" t="n"/>
+      <c r="AQ8" s="3" t="n"/>
+      <c r="AR8" s="3" t="n"/>
       <c r="AS8" s="3" t="n"/>
       <c r="AT8" s="3" t="n"/>
       <c r="AU8" s="3" t="n"/>
       <c r="AV8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW8" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" s="3" t="n"/>
+        <v>4321</v>
+      </c>
+      <c r="AW8" s="3" t="n"/>
+      <c r="AX8" s="3" t="n"/>
+      <c r="AY8" s="3" t="n"/>
+      <c r="AZ8" s="3" t="n"/>
+      <c r="BA8" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB8" s="3" t="n"/>
-      <c r="BC8" s="3" t="n"/>
+      <c r="BC8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD8" s="3" t="n"/>
       <c r="BE8" s="3" t="n"/>
       <c r="BF8" s="3" t="n"/>
-      <c r="BG8" s="3" t="n"/>
-      <c r="BH8" s="2" t="n">
-        <v>4321</v>
-      </c>
-      <c r="BI8" s="3" t="n"/>
+      <c r="BG8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH8" s="2" t="inlineStr">
+        <is>
+          <t>MADRID</t>
+        </is>
+      </c>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Camarma de Esteruelas</t>
+        </is>
+      </c>
       <c r="BJ8" s="3" t="n"/>
       <c r="BK8" s="3" t="n"/>
       <c r="BL8" s="3" t="n"/>
-      <c r="BM8" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM8" s="3" t="n"/>
       <c r="BN8" s="3" t="n"/>
-      <c r="BO8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO8" s="3" t="n"/>
       <c r="BP8" s="3" t="n"/>
       <c r="BQ8" s="3" t="n"/>
       <c r="BR8" s="3" t="n"/>
-      <c r="BS8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT8" s="2" t="inlineStr">
-        <is>
-          <t>MADRID</t>
-        </is>
-      </c>
-      <c r="BU8" s="2" t="inlineStr">
-        <is>
-          <t>Camarma de Esteruelas</t>
-        </is>
-      </c>
+      <c r="BS8" s="3" t="n"/>
+      <c r="BT8" s="3" t="n"/>
+      <c r="BU8" s="3" t="n"/>
       <c r="BV8" s="3" t="n"/>
       <c r="BW8" s="3" t="n"/>
       <c r="BX8" s="3" t="n"/>
@@ -2722,219 +2456,187 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
         <v>28816</v>
       </c>
+      <c r="C9" s="2" t="n">
+        <v>28032</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3.0TD ML</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="n">
-        <v>28032</v>
+        <v>25806</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3.0TD ML</t>
-        </is>
+        <v>43640</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>20000</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25806</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2008-04-15T00:00:00</t>
-        </is>
+        <v>3526</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>4607</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>6</v>
+        <v>4548</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43640</v>
+        <v>4736</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>1683</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4</v>
+        <v>6706</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>20000</v>
+        <v>20</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>20000</v>
+        <v>20</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>3526</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>4607</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>4548</v>
-      </c>
-      <c r="X9" s="2" t="n">
-        <v>4736</v>
-      </c>
-      <c r="Y9" s="2" t="n">
-        <v>1683</v>
-      </c>
-      <c r="Z9" s="2" t="n">
-        <v>6706</v>
-      </c>
-      <c r="AA9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AB9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG9" s="6">
+      <c r="U9" s="6">
         <f>IFERROR(AVERAGEIF(P294:P329,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH9" s="6">
+      <c r="V9" s="6">
         <f>IFERROR(AVERAGEIF(Q294:Q329,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI9" s="6">
+      <c r="W9" s="6">
         <f>IFERROR(AVERAGEIF(R294:R329,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ9" s="6">
+      <c r="X9" s="6">
         <f>IFERROR(AVERAGEIF(S294:S329,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK9" s="6">
+      <c r="Y9" s="6">
         <f>IFERROR(AVERAGEIF(T294:T329,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL9" s="6">
+      <c r="Z9" s="6">
         <f>IFERROR(AVERAGEIF(U294:U329,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM9" s="2" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>2024-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AN9" s="2" t="inlineStr">
+      <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>2024-11-26T00:00:00</t>
         </is>
       </c>
+      <c r="AC9" s="3" t="n"/>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="n"/>
+      <c r="AH9" s="3" t="n"/>
+      <c r="AI9" s="3" t="n"/>
+      <c r="AJ9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO9" s="3" t="n"/>
-      <c r="AP9" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ9" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR9" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP9" s="3" t="n"/>
+      <c r="AQ9" s="3" t="n"/>
+      <c r="AR9" s="3" t="n"/>
       <c r="AS9" s="3" t="n"/>
       <c r="AT9" s="3" t="n"/>
       <c r="AU9" s="3" t="n"/>
       <c r="AV9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW9" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" s="3" t="n"/>
+        <v>4321</v>
+      </c>
+      <c r="AW9" s="3" t="n"/>
+      <c r="AX9" s="3" t="n"/>
+      <c r="AY9" s="3" t="n"/>
+      <c r="AZ9" s="3" t="n"/>
+      <c r="BA9" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB9" s="3" t="n"/>
-      <c r="BC9" s="3" t="n"/>
+      <c r="BC9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD9" s="3" t="n"/>
       <c r="BE9" s="3" t="n"/>
       <c r="BF9" s="3" t="n"/>
-      <c r="BG9" s="3" t="n"/>
-      <c r="BH9" s="2" t="n">
-        <v>4321</v>
-      </c>
-      <c r="BI9" s="3" t="n"/>
+      <c r="BG9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH9" s="2" t="inlineStr">
+        <is>
+          <t>MADRID</t>
+        </is>
+      </c>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Camarma de Esteruelas</t>
+        </is>
+      </c>
       <c r="BJ9" s="3" t="n"/>
       <c r="BK9" s="3" t="n"/>
       <c r="BL9" s="3" t="n"/>
-      <c r="BM9" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM9" s="3" t="n"/>
       <c r="BN9" s="3" t="n"/>
-      <c r="BO9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO9" s="3" t="n"/>
       <c r="BP9" s="3" t="n"/>
       <c r="BQ9" s="3" t="n"/>
       <c r="BR9" s="3" t="n"/>
-      <c r="BS9" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT9" s="2" t="inlineStr">
-        <is>
-          <t>MADRID</t>
-        </is>
-      </c>
-      <c r="BU9" s="2" t="inlineStr">
-        <is>
-          <t>Camarma de Esteruelas</t>
-        </is>
-      </c>
+      <c r="BS9" s="3" t="n"/>
+      <c r="BT9" s="3" t="n"/>
+      <c r="BU9" s="3" t="n"/>
       <c r="BV9" s="3" t="n"/>
       <c r="BW9" s="3" t="n"/>
       <c r="BX9" s="3" t="n"/>
@@ -2962,219 +2664,187 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
         <v>2611</v>
       </c>
+      <c r="C10" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3.0TD ML</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="n">
-        <v>2057</v>
+        <v>11543</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3.0TD ML</t>
-        </is>
+        <v>17321</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>15100</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>15100</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>11543</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2022-01-31T00:00:00</t>
-        </is>
+        <v>1191</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1834</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>6</v>
+        <v>1373</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>17321</v>
+        <v>1126</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>4</v>
+        <v>5571</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>15100</v>
+        <v>10</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>15100</v>
+        <v>10</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1191</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>1834</v>
-      </c>
-      <c r="W10" s="2" t="n">
-        <v>1373</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>1126</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>448</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>5571</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="AG10" s="6">
+      <c r="U10" s="6">
         <f>IFERROR(AVERAGEIF(P331:P368,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH10" s="6">
+      <c r="V10" s="6">
         <f>IFERROR(AVERAGEIF(Q331:Q368,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI10" s="6">
+      <c r="W10" s="6">
         <f>IFERROR(AVERAGEIF(R331:R368,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ10" s="6">
+      <c r="X10" s="6">
         <f>IFERROR(AVERAGEIF(S331:S368,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK10" s="6">
+      <c r="Y10" s="6">
         <f>IFERROR(AVERAGEIF(T331:T368,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL10" s="6">
+      <c r="Z10" s="6">
         <f>IFERROR(AVERAGEIF(U331:U368,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM10" s="2" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>2025-10-22T00:00:00</t>
         </is>
       </c>
-      <c r="AN10" s="2" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>2025-10-22T00:00:00</t>
         </is>
       </c>
+      <c r="AC10" s="3" t="n"/>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="n"/>
+      <c r="AH10" s="3" t="n"/>
+      <c r="AI10" s="3" t="n"/>
+      <c r="AJ10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO10" s="3" t="n"/>
-      <c r="AP10" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ10" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR10" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP10" s="3" t="n"/>
+      <c r="AQ10" s="3" t="n"/>
+      <c r="AR10" s="3" t="n"/>
       <c r="AS10" s="3" t="n"/>
       <c r="AT10" s="3" t="n"/>
       <c r="AU10" s="3" t="n"/>
       <c r="AV10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW10" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX10" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" s="3" t="n"/>
+        <v>5520</v>
+      </c>
+      <c r="AW10" s="3" t="n"/>
+      <c r="AX10" s="3" t="n"/>
+      <c r="AY10" s="3" t="n"/>
+      <c r="AZ10" s="3" t="n"/>
+      <c r="BA10" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB10" s="3" t="n"/>
-      <c r="BC10" s="3" t="n"/>
+      <c r="BC10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD10" s="3" t="n"/>
       <c r="BE10" s="3" t="n"/>
       <c r="BF10" s="3" t="n"/>
-      <c r="BG10" s="3" t="n"/>
-      <c r="BH10" s="2" t="n">
-        <v>5520</v>
-      </c>
-      <c r="BI10" s="3" t="n"/>
+      <c r="BG10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH10" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BJ10" s="3" t="n"/>
       <c r="BK10" s="3" t="n"/>
       <c r="BL10" s="3" t="n"/>
-      <c r="BM10" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM10" s="3" t="n"/>
       <c r="BN10" s="3" t="n"/>
-      <c r="BO10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO10" s="3" t="n"/>
       <c r="BP10" s="3" t="n"/>
       <c r="BQ10" s="3" t="n"/>
       <c r="BR10" s="3" t="n"/>
-      <c r="BS10" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT10" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU10" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
-      </c>
+      <c r="BS10" s="3" t="n"/>
+      <c r="BT10" s="3" t="n"/>
+      <c r="BU10" s="3" t="n"/>
       <c r="BV10" s="3" t="n"/>
       <c r="BW10" s="3" t="n"/>
       <c r="BX10" s="3" t="n"/>
@@ -3202,42 +2872,36 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
         <v>46940</v>
       </c>
+      <c r="C11" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="n">
-        <v>46159</v>
+        <v>1825</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1X220</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>3300</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1825</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1994-10-24T00:00:00</t>
-        </is>
+        <v>559</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>590</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>676</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -3246,175 +2910,149 @@
         <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+        <v>3.3</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>559</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>590</v>
-      </c>
-      <c r="W11" s="2" t="n">
-        <v>676</v>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB11" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="6">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6">
         <f>IFERROR(AVERAGEIF(P370:P407,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH11" s="6">
+      <c r="V11" s="6">
         <f>IFERROR(AVERAGEIF(Q370:Q407,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI11" s="6">
+      <c r="W11" s="6">
         <f>IFERROR(AVERAGEIF(R370:R407,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ11" s="6">
+      <c r="X11" s="6">
         <f>IFERROR(AVERAGEIF(S370:S407,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK11" s="6">
+      <c r="Y11" s="6">
         <f>IFERROR(AVERAGEIF(T370:T407,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL11" s="6">
+      <c r="Z11" s="6">
         <f>IFERROR(AVERAGEIF(U370:U407,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM11" s="2" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AN11" s="2" t="inlineStr">
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="n"/>
+      <c r="AH11" s="3" t="n"/>
+      <c r="AI11" s="3" t="n"/>
+      <c r="AJ11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AL11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO11" s="3" t="n"/>
-      <c r="AP11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-05T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ11" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR11" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP11" s="3" t="n"/>
+      <c r="AQ11" s="3" t="n"/>
+      <c r="AR11" s="3" t="n"/>
       <c r="AS11" s="3" t="n"/>
       <c r="AT11" s="3" t="n"/>
       <c r="AU11" s="3" t="n"/>
       <c r="AV11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW11" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AX11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" s="3" t="n"/>
+        <v>4321</v>
+      </c>
+      <c r="AW11" s="3" t="n"/>
+      <c r="AX11" s="3" t="n"/>
+      <c r="AY11" s="3" t="n"/>
+      <c r="AZ11" s="3" t="n"/>
+      <c r="BA11" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB11" s="3" t="n"/>
-      <c r="BC11" s="3" t="n"/>
+      <c r="BC11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD11" s="3" t="n"/>
       <c r="BE11" s="3" t="n"/>
       <c r="BF11" s="3" t="n"/>
-      <c r="BG11" s="3" t="n"/>
-      <c r="BH11" s="2" t="n">
-        <v>4321</v>
-      </c>
-      <c r="BI11" s="3" t="n"/>
+      <c r="BG11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH11" s="2" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Manises</t>
+        </is>
+      </c>
       <c r="BJ11" s="3" t="n"/>
       <c r="BK11" s="3" t="n"/>
       <c r="BL11" s="3" t="n"/>
-      <c r="BM11" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM11" s="3" t="n"/>
       <c r="BN11" s="3" t="n"/>
-      <c r="BO11" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO11" s="3" t="n"/>
       <c r="BP11" s="3" t="n"/>
       <c r="BQ11" s="3" t="n"/>
       <c r="BR11" s="3" t="n"/>
-      <c r="BS11" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT11" s="2" t="inlineStr">
-        <is>
-          <t>VALENCIA</t>
-        </is>
-      </c>
-      <c r="BU11" s="2" t="inlineStr">
-        <is>
-          <t>Manises</t>
-        </is>
-      </c>
+      <c r="BS11" s="3" t="n"/>
+      <c r="BT11" s="3" t="n"/>
+      <c r="BU11" s="3" t="n"/>
       <c r="BV11" s="3" t="n"/>
       <c r="BW11" s="3" t="n"/>
       <c r="BX11" s="3" t="n"/>
@@ -3442,219 +3080,187 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
         <v>48110</v>
       </c>
+      <c r="C12" s="2" t="n">
+        <v>48040</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="n">
-        <v>48040</v>
+        <v>4714</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>34640</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>4600</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4714</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2022-05-02T00:00:00</t>
-        </is>
+        <v>1575</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1736</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>6</v>
+        <v>1403</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>34640</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+        <v>4.6</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>4.6</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>1575</v>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>1736</v>
-      </c>
-      <c r="W12" s="2" t="n">
-        <v>1403</v>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB12" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="6">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6">
         <f>IFERROR(AVERAGEIF(P409:P446,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH12" s="6">
+      <c r="V12" s="6">
         <f>IFERROR(AVERAGEIF(Q409:Q446,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI12" s="6">
+      <c r="W12" s="6">
         <f>IFERROR(AVERAGEIF(R409:R446,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ12" s="6">
+      <c r="X12" s="6">
         <f>IFERROR(AVERAGEIF(S409:S446,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK12" s="6">
+      <c r="Y12" s="6">
         <f>IFERROR(AVERAGEIF(T409:T446,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL12" s="6">
+      <c r="Z12" s="6">
         <f>IFERROR(AVERAGEIF(U409:U446,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM12" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AN12" s="2" t="inlineStr">
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="n"/>
+      <c r="AH12" s="3" t="n"/>
+      <c r="AI12" s="3" t="n"/>
+      <c r="AJ12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO12" s="3" t="n"/>
-      <c r="AP12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-09T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ12" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR12" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP12" s="3" t="n"/>
+      <c r="AQ12" s="3" t="n"/>
+      <c r="AR12" s="3" t="n"/>
       <c r="AS12" s="3" t="n"/>
       <c r="AT12" s="3" t="n"/>
       <c r="AU12" s="3" t="n"/>
       <c r="AV12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW12" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="3" t="n"/>
+        <v>2370</v>
+      </c>
+      <c r="AW12" s="3" t="n"/>
+      <c r="AX12" s="3" t="n"/>
+      <c r="AY12" s="3" t="n"/>
+      <c r="AZ12" s="3" t="n"/>
+      <c r="BA12" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB12" s="3" t="n"/>
-      <c r="BC12" s="3" t="n"/>
+      <c r="BC12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD12" s="3" t="n"/>
       <c r="BE12" s="3" t="n"/>
       <c r="BF12" s="3" t="n"/>
-      <c r="BG12" s="3" t="n"/>
-      <c r="BH12" s="2" t="n">
-        <v>2370</v>
-      </c>
-      <c r="BI12" s="3" t="n"/>
+      <c r="BG12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH12" s="2" t="inlineStr">
+        <is>
+          <t>BIZKAIA</t>
+        </is>
+      </c>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Gatika</t>
+        </is>
+      </c>
       <c r="BJ12" s="3" t="n"/>
       <c r="BK12" s="3" t="n"/>
       <c r="BL12" s="3" t="n"/>
-      <c r="BM12" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM12" s="3" t="n"/>
       <c r="BN12" s="3" t="n"/>
-      <c r="BO12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO12" s="3" t="n"/>
       <c r="BP12" s="3" t="n"/>
       <c r="BQ12" s="3" t="n"/>
       <c r="BR12" s="3" t="n"/>
-      <c r="BS12" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT12" s="2" t="inlineStr">
-        <is>
-          <t>BIZKAIA</t>
-        </is>
-      </c>
-      <c r="BU12" s="2" t="inlineStr">
-        <is>
-          <t>Gatika</t>
-        </is>
-      </c>
+      <c r="BS12" s="3" t="n"/>
+      <c r="BT12" s="3" t="n"/>
+      <c r="BU12" s="3" t="n"/>
       <c r="BV12" s="3" t="n"/>
       <c r="BW12" s="3" t="n"/>
       <c r="BX12" s="3" t="n"/>
@@ -3682,219 +3288,187 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
         <v>2611</v>
       </c>
+      <c r="C13" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3.0TD ML</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="n">
-        <v>2057</v>
+        <v>18939</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3.0TD ML</t>
-        </is>
+        <v>19985</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>17320</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>17320</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18939</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1970-01-01T00:00:00</t>
-        </is>
+        <v>2408</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>2463</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>6</v>
+        <v>1198</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>19985</v>
+        <v>885</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>4</v>
+        <v>11588</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
+        <v>17.32</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>17.32</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>17320</v>
+        <v>17.32</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>17320</v>
+        <v>17.32</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>1</v>
+        <v>17.32</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>2408</v>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>2463</v>
-      </c>
-      <c r="W13" s="2" t="n">
-        <v>1198</v>
-      </c>
-      <c r="X13" s="2" t="n">
-        <v>885</v>
-      </c>
-      <c r="Y13" s="2" t="n">
-        <v>398</v>
-      </c>
-      <c r="Z13" s="2" t="n">
-        <v>11588</v>
-      </c>
-      <c r="AA13" s="2" t="n">
         <v>17.32</v>
       </c>
-      <c r="AB13" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AC13" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AD13" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AE13" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AF13" s="2" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AG13" s="6">
+      <c r="U13" s="6">
         <f>IFERROR(AVERAGEIF(P448:P485,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH13" s="6">
+      <c r="V13" s="6">
         <f>IFERROR(AVERAGEIF(Q448:Q485,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI13" s="6">
+      <c r="W13" s="6">
         <f>IFERROR(AVERAGEIF(R448:R485,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ13" s="6">
+      <c r="X13" s="6">
         <f>IFERROR(AVERAGEIF(S448:S485,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK13" s="6">
+      <c r="Y13" s="6">
         <f>IFERROR(AVERAGEIF(T448:T485,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL13" s="6">
+      <c r="Z13" s="6">
         <f>IFERROR(AVERAGEIF(U448:U485,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM13" s="2" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>2025-10-23T00:00:00</t>
         </is>
       </c>
-      <c r="AN13" s="2" t="inlineStr">
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>2025-10-23T00:00:00</t>
         </is>
       </c>
+      <c r="AC13" s="3" t="n"/>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="n"/>
+      <c r="AH13" s="3" t="n"/>
+      <c r="AI13" s="3" t="n"/>
+      <c r="AJ13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO13" s="3" t="n"/>
-      <c r="AP13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ13" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR13" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP13" s="3" t="n"/>
+      <c r="AQ13" s="3" t="n"/>
+      <c r="AR13" s="3" t="n"/>
       <c r="AS13" s="3" t="n"/>
       <c r="AT13" s="3" t="n"/>
       <c r="AU13" s="3" t="n"/>
       <c r="AV13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW13" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" s="3" t="n"/>
+        <v>5630</v>
+      </c>
+      <c r="AW13" s="3" t="n"/>
+      <c r="AX13" s="3" t="n"/>
+      <c r="AY13" s="3" t="n"/>
+      <c r="AZ13" s="3" t="n"/>
+      <c r="BA13" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB13" s="3" t="n"/>
-      <c r="BC13" s="3" t="n"/>
+      <c r="BC13" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD13" s="3" t="n"/>
       <c r="BE13" s="3" t="n"/>
       <c r="BF13" s="3" t="n"/>
-      <c r="BG13" s="3" t="n"/>
-      <c r="BH13" s="2" t="n">
-        <v>5630</v>
-      </c>
-      <c r="BI13" s="3" t="n"/>
+      <c r="BG13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH13" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BJ13" s="3" t="n"/>
       <c r="BK13" s="3" t="n"/>
       <c r="BL13" s="3" t="n"/>
-      <c r="BM13" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM13" s="3" t="n"/>
       <c r="BN13" s="3" t="n"/>
-      <c r="BO13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO13" s="3" t="n"/>
       <c r="BP13" s="3" t="n"/>
       <c r="BQ13" s="3" t="n"/>
       <c r="BR13" s="3" t="n"/>
-      <c r="BS13" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT13" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU13" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
-      </c>
+      <c r="BS13" s="3" t="n"/>
+      <c r="BT13" s="3" t="n"/>
+      <c r="BU13" s="3" t="n"/>
       <c r="BV13" s="3" t="n"/>
       <c r="BW13" s="3" t="n"/>
       <c r="BX13" s="3" t="n"/>
@@ -3922,241 +3496,215 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>EDISTRIBUCIÓN REDES DIGITALES S.L.U.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
         <v>41900</v>
       </c>
+      <c r="C14" s="2" t="n">
+        <v>41021</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>41021</v>
+        <v>5311</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Otra tensión obsoleta</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>35000</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>10392</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>10392</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5311</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2014-03-27T00:00:00</t>
-        </is>
+        <v>1782</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1891</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>99</v>
+        <v>1637</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>35000</v>
-      </c>
-      <c r="M14" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="N14" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="3" t="n"/>
+        <v>10.39</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>10.39</v>
+      </c>
       <c r="Q14" s="2" t="n">
-        <v>10392</v>
+        <v>0</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>10392</v>
+        <v>0</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>1782</v>
-      </c>
-      <c r="V14" s="2" t="n">
-        <v>1891</v>
-      </c>
-      <c r="W14" s="2" t="n">
-        <v>1637</v>
-      </c>
-      <c r="X14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="2" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="AB14" s="2" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="AC14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="6">
+        <v>0</v>
+      </c>
+      <c r="U14" s="6">
         <f>IFERROR(AVERAGEIF(P487:P522,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH14" s="6">
+      <c r="V14" s="6">
         <f>IFERROR(AVERAGEIF(Q487:Q522,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI14" s="6">
+      <c r="W14" s="6">
         <f>IFERROR(AVERAGEIF(R487:R522,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ14" s="6">
+      <c r="X14" s="6">
         <f>IFERROR(AVERAGEIF(S487:S522,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK14" s="6">
+      <c r="Y14" s="6">
         <f>IFERROR(AVERAGEIF(T487:T522,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL14" s="6">
+      <c r="Z14" s="6">
         <f>IFERROR(AVERAGEIF(U487:U522,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM14" s="2" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>2021-05-31T00:00:00</t>
         </is>
       </c>
-      <c r="AN14" s="2" t="inlineStr">
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>2021-02-19T00:00:00</t>
         </is>
       </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2099-12-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="n"/>
+      <c r="AH14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n"/>
+      <c r="AJ14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AO14" s="2" t="inlineStr">
         <is>
-          <t>2099-12-31T00:00:00</t>
+          <t>A000775/09</t>
         </is>
       </c>
       <c r="AP14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11T00:00:00</t>
+          <t>2009-04-13T00:00:00</t>
         </is>
       </c>
       <c r="AQ14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR14" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+          <t>9999-12-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="n"/>
       <c r="AS14" s="3" t="n"/>
-      <c r="AT14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT14" s="3" t="n"/>
       <c r="AU14" s="3" t="n"/>
       <c r="AV14" s="2" t="n">
+        <v>5210</v>
+      </c>
+      <c r="AW14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AW14" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="AX14" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AY14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AZ14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AZ14" s="3" t="n"/>
       <c r="BA14" s="2" t="inlineStr">
         <is>
-          <t>A000775/09</t>
-        </is>
-      </c>
-      <c r="BB14" s="2" t="inlineStr">
-        <is>
-          <t>2009-04-13T00:00:00</t>
-        </is>
-      </c>
-      <c r="BC14" s="2" t="inlineStr">
-        <is>
-          <t>9999-12-31T00:00:00</t>
-        </is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BB14" s="3" t="n"/>
+      <c r="BC14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BD14" s="3" t="n"/>
       <c r="BE14" s="3" t="n"/>
-      <c r="BF14" s="3" t="n"/>
-      <c r="BG14" s="3" t="n"/>
-      <c r="BH14" s="2" t="n">
-        <v>5210</v>
-      </c>
-      <c r="BI14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ14" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="BK14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="BF14" s="2" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="BG14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH14" s="2" t="inlineStr">
+        <is>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>CAMAS</t>
+        </is>
+      </c>
+      <c r="BJ14" s="3" t="n"/>
+      <c r="BK14" s="3" t="n"/>
       <c r="BL14" s="3" t="n"/>
-      <c r="BM14" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM14" s="3" t="n"/>
       <c r="BN14" s="3" t="n"/>
-      <c r="BO14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO14" s="3" t="n"/>
       <c r="BP14" s="3" t="n"/>
       <c r="BQ14" s="3" t="n"/>
-      <c r="BR14" s="2" t="inlineStr">
-        <is>
-          <t>UV</t>
-        </is>
-      </c>
-      <c r="BS14" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT14" s="2" t="inlineStr">
-        <is>
-          <t>SEVILLA</t>
-        </is>
-      </c>
-      <c r="BU14" s="2" t="inlineStr">
-        <is>
-          <t>CAMAS</t>
-        </is>
-      </c>
+      <c r="BR14" s="3" t="n"/>
+      <c r="BS14" s="3" t="n"/>
+      <c r="BT14" s="3" t="n"/>
+      <c r="BU14" s="3" t="n"/>
       <c r="BV14" s="3" t="n"/>
       <c r="BW14" s="3" t="n"/>
       <c r="BX14" s="3" t="n"/>
@@ -4184,239 +3732,213 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>EDISTRIBUCIÓN REDES DIGITALES S.L.U.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
         <v>8160</v>
       </c>
+      <c r="C15" s="2" t="n">
+        <v>8135</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="n">
-        <v>8135</v>
+        <v>5177</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Otra tensión obsoleta</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>27713</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>13856</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>13856</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5177</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2009-07-01T00:00:00</t>
-        </is>
+        <v>1979</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>2342</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>99</v>
+        <v>856</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>27713</v>
-      </c>
-      <c r="M15" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="3" t="n"/>
+        <v>13.86</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>13.86</v>
+      </c>
       <c r="Q15" s="2" t="n">
-        <v>13856</v>
+        <v>0</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>13856</v>
+        <v>0</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>1979</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>2342</v>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>856</v>
-      </c>
-      <c r="X15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="2" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AB15" s="2" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AC15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="6">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6">
         <f>IFERROR(AVERAGEIF(P524:P559,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH15" s="6">
+      <c r="V15" s="6">
         <f>IFERROR(AVERAGEIF(Q524:Q559,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI15" s="6">
+      <c r="W15" s="6">
         <f>IFERROR(AVERAGEIF(R524:R559,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ15" s="6">
+      <c r="X15" s="6">
         <f>IFERROR(AVERAGEIF(S524:S559,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK15" s="6">
+      <c r="Y15" s="6">
         <f>IFERROR(AVERAGEIF(T524:T559,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL15" s="6">
+      <c r="Z15" s="6">
         <f>IFERROR(AVERAGEIF(U524:U559,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM15" s="2" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>2021-05-31T00:00:00</t>
         </is>
       </c>
-      <c r="AN15" s="2" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>2021-03-01T00:00:00</t>
         </is>
       </c>
-      <c r="AO15" s="2" t="inlineStr">
+      <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>2099-12-31T00:00:00</t>
         </is>
       </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="n"/>
+      <c r="AH15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n"/>
+      <c r="AJ15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK15" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" s="2" t="n">
+        <v>9999</v>
+      </c>
       <c r="AP15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09T00:00:00</t>
+          <t>2004-11-05T00:00:00</t>
         </is>
       </c>
       <c r="AQ15" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR15" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+          <t>9999-12-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="n"/>
       <c r="AS15" s="3" t="n"/>
-      <c r="AT15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT15" s="3" t="n"/>
       <c r="AU15" s="3" t="n"/>
       <c r="AV15" s="2" t="n">
+        <v>9820</v>
+      </c>
+      <c r="AW15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AW15" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="AX15" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AY15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AZ15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA15" s="2" t="n">
-        <v>9999</v>
-      </c>
-      <c r="BB15" s="2" t="inlineStr">
-        <is>
-          <t>2004-11-05T00:00:00</t>
-        </is>
-      </c>
-      <c r="BC15" s="2" t="inlineStr">
-        <is>
-          <t>9999-12-31T00:00:00</t>
-        </is>
+      <c r="AZ15" s="3" t="n"/>
+      <c r="BA15" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BB15" s="3" t="n"/>
+      <c r="BC15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="BD15" s="3" t="n"/>
       <c r="BE15" s="3" t="n"/>
-      <c r="BF15" s="3" t="n"/>
-      <c r="BG15" s="3" t="n"/>
-      <c r="BH15" s="2" t="n">
-        <v>9820</v>
-      </c>
-      <c r="BI15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BK15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="BF15" s="2" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="BG15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH15" s="2" t="inlineStr">
+        <is>
+          <t>BARCELONA</t>
+        </is>
+      </c>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>MONTMELO</t>
+        </is>
+      </c>
+      <c r="BJ15" s="3" t="n"/>
+      <c r="BK15" s="3" t="n"/>
       <c r="BL15" s="3" t="n"/>
-      <c r="BM15" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM15" s="3" t="n"/>
       <c r="BN15" s="3" t="n"/>
-      <c r="BO15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO15" s="3" t="n"/>
       <c r="BP15" s="3" t="n"/>
       <c r="BQ15" s="3" t="n"/>
-      <c r="BR15" s="2" t="inlineStr">
-        <is>
-          <t>UV</t>
-        </is>
-      </c>
-      <c r="BS15" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT15" s="2" t="inlineStr">
-        <is>
-          <t>BARCELONA</t>
-        </is>
-      </c>
-      <c r="BU15" s="2" t="inlineStr">
-        <is>
-          <t>MONTMELO</t>
-        </is>
-      </c>
+      <c r="BR15" s="3" t="n"/>
+      <c r="BS15" s="3" t="n"/>
+      <c r="BT15" s="3" t="n"/>
+      <c r="BU15" s="3" t="n"/>
       <c r="BV15" s="3" t="n"/>
       <c r="BW15" s="3" t="n"/>
       <c r="BX15" s="3" t="n"/>
@@ -4444,211 +3966,185 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>UFD DISTRIBUCIÓN ELECTRICIDAD, SA</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
         <v>45730</v>
       </c>
+      <c r="C16" s="2" t="n">
+        <v>451875</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6.1TD ML</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="n">
-        <v>451875</v>
+        <v>21667</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>17000</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6.1TD ML</t>
-        </is>
+        <v>40000</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>40000</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21667</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2008-04-04T00:00:00</t>
-        </is>
+        <v>1290</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1947</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>26</v>
+        <v>1444</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>40000</v>
+        <v>1714</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>40000</v>
+        <v>838</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4</v>
+        <v>14434</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" s="3" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="Q16" s="2" t="n">
-        <v>40000</v>
+        <v>12</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>40000</v>
+        <v>12</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <v>1290</v>
-      </c>
-      <c r="V16" s="2" t="n">
-        <v>1947</v>
-      </c>
-      <c r="W16" s="2" t="n">
-        <v>1444</v>
-      </c>
-      <c r="X16" s="2" t="n">
-        <v>1714</v>
-      </c>
-      <c r="Y16" s="2" t="n">
-        <v>838</v>
-      </c>
-      <c r="Z16" s="2" t="n">
-        <v>14434</v>
-      </c>
-      <c r="AA16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF16" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="AG16" s="6">
+      <c r="U16" s="6">
         <f>IFERROR(AVERAGEIF(P561:P599,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH16" s="6">
+      <c r="V16" s="6">
         <f>IFERROR(AVERAGEIF(Q561:Q599,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI16" s="6">
+      <c r="W16" s="6">
         <f>IFERROR(AVERAGEIF(R561:R599,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ16" s="6">
+      <c r="X16" s="6">
         <f>IFERROR(AVERAGEIF(S561:S599,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK16" s="6">
+      <c r="Y16" s="6">
         <f>IFERROR(AVERAGEIF(T561:T599,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL16" s="6">
+      <c r="Z16" s="6">
         <f>IFERROR(AVERAGEIF(U561:U599,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM16" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="AN16" s="2" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>2025-03-20T00:00:00</t>
         </is>
       </c>
+      <c r="AC16" s="3" t="n"/>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="n"/>
+      <c r="AH16" s="3" t="n"/>
+      <c r="AI16" s="3" t="n"/>
+      <c r="AJ16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AO16" s="3" t="n"/>
-      <c r="AP16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ16" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR16" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP16" s="3" t="n"/>
+      <c r="AQ16" s="3" t="n"/>
+      <c r="AR16" s="3" t="n"/>
       <c r="AS16" s="3" t="n"/>
       <c r="AT16" s="3" t="n"/>
       <c r="AU16" s="3" t="n"/>
       <c r="AV16" s="2" t="n">
+        <v>9810</v>
+      </c>
+      <c r="AW16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AW16" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AX16" s="3" t="n"/>
+      <c r="AY16" s="3" t="n"/>
+      <c r="AZ16" s="3" t="n"/>
       <c r="BA16" s="3" t="n"/>
       <c r="BB16" s="3" t="n"/>
-      <c r="BC16" s="3" t="n"/>
+      <c r="BC16" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="BD16" s="3" t="n"/>
       <c r="BE16" s="3" t="n"/>
       <c r="BF16" s="3" t="n"/>
-      <c r="BG16" s="3" t="n"/>
-      <c r="BH16" s="2" t="n">
-        <v>9810</v>
-      </c>
-      <c r="BI16" s="2" t="n">
-        <v>2</v>
+      <c r="BG16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH16" s="2" t="inlineStr">
+        <is>
+          <t>TOLEDO</t>
+        </is>
+      </c>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Villafranca de los Caballeros</t>
+        </is>
       </c>
       <c r="BJ16" s="3" t="n"/>
       <c r="BK16" s="3" t="n"/>
       <c r="BL16" s="3" t="n"/>
       <c r="BM16" s="3" t="n"/>
       <c r="BN16" s="3" t="n"/>
-      <c r="BO16" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="BO16" s="3" t="n"/>
       <c r="BP16" s="3" t="n"/>
       <c r="BQ16" s="3" t="n"/>
       <c r="BR16" s="3" t="n"/>
-      <c r="BS16" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT16" s="2" t="inlineStr">
-        <is>
-          <t>TOLEDO</t>
-        </is>
-      </c>
-      <c r="BU16" s="2" t="inlineStr">
-        <is>
-          <t>Villafranca de los Caballeros</t>
-        </is>
-      </c>
+      <c r="BS16" s="3" t="n"/>
+      <c r="BT16" s="3" t="n"/>
+      <c r="BU16" s="3" t="n"/>
       <c r="BV16" s="3" t="n"/>
       <c r="BW16" s="3" t="n"/>
       <c r="BX16" s="3" t="n"/>
@@ -4676,219 +4172,187 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
         <v>2611</v>
       </c>
+      <c r="C17" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="n">
-        <v>2057</v>
+        <v>4705</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>6920</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>6928</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>6928</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4705</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2008-04-24T00:00:00</t>
-        </is>
+        <v>1833</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1832</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>6</v>
+        <v>1040</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6920</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+        <v>6.93</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>6.93</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>6928</v>
+        <v>0</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>6928</v>
+        <v>0</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" s="2" t="n">
-        <v>1833</v>
-      </c>
-      <c r="V17" s="2" t="n">
-        <v>1832</v>
-      </c>
-      <c r="W17" s="2" t="n">
-        <v>1040</v>
-      </c>
-      <c r="X17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AB17" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AC17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="6">
+        <v>0</v>
+      </c>
+      <c r="U17" s="6">
         <f>IFERROR(AVERAGEIF(P601:P638,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH17" s="6">
+      <c r="V17" s="6">
         <f>IFERROR(AVERAGEIF(Q601:Q638,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI17" s="6">
+      <c r="W17" s="6">
         <f>IFERROR(AVERAGEIF(R601:R638,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ17" s="6">
+      <c r="X17" s="6">
         <f>IFERROR(AVERAGEIF(S601:S638,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK17" s="6">
+      <c r="Y17" s="6">
         <f>IFERROR(AVERAGEIF(T601:T638,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL17" s="6">
+      <c r="Z17" s="6">
         <f>IFERROR(AVERAGEIF(U601:U638,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM17" s="2" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AN17" s="2" t="inlineStr">
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
+      <c r="AC17" s="3" t="n"/>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="n"/>
+      <c r="AH17" s="3" t="n"/>
+      <c r="AI17" s="3" t="n"/>
+      <c r="AJ17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO17" s="3" t="n"/>
-      <c r="AP17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ17" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR17" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP17" s="3" t="n"/>
+      <c r="AQ17" s="3" t="n"/>
+      <c r="AR17" s="3" t="n"/>
       <c r="AS17" s="3" t="n"/>
       <c r="AT17" s="3" t="n"/>
       <c r="AU17" s="3" t="n"/>
       <c r="AV17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW17" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" s="3" t="n"/>
+        <v>9810</v>
+      </c>
+      <c r="AW17" s="3" t="n"/>
+      <c r="AX17" s="3" t="n"/>
+      <c r="AY17" s="3" t="n"/>
+      <c r="AZ17" s="3" t="n"/>
+      <c r="BA17" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB17" s="3" t="n"/>
-      <c r="BC17" s="3" t="n"/>
+      <c r="BC17" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD17" s="3" t="n"/>
       <c r="BE17" s="3" t="n"/>
       <c r="BF17" s="3" t="n"/>
-      <c r="BG17" s="3" t="n"/>
-      <c r="BH17" s="2" t="n">
-        <v>9810</v>
-      </c>
-      <c r="BI17" s="3" t="n"/>
+      <c r="BG17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH17" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI17" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BJ17" s="3" t="n"/>
       <c r="BK17" s="3" t="n"/>
       <c r="BL17" s="3" t="n"/>
-      <c r="BM17" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM17" s="3" t="n"/>
       <c r="BN17" s="3" t="n"/>
-      <c r="BO17" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO17" s="3" t="n"/>
       <c r="BP17" s="3" t="n"/>
       <c r="BQ17" s="3" t="n"/>
       <c r="BR17" s="3" t="n"/>
-      <c r="BS17" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT17" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU17" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
-      </c>
+      <c r="BS17" s="3" t="n"/>
+      <c r="BT17" s="3" t="n"/>
+      <c r="BU17" s="3" t="n"/>
       <c r="BV17" s="3" t="n"/>
       <c r="BW17" s="3" t="n"/>
       <c r="BX17" s="3" t="n"/>
@@ -4916,219 +4380,187 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
         <v>2611</v>
       </c>
+      <c r="C18" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="n">
-        <v>2057</v>
+        <v>2624</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>6920</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>6920</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>6920</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2624</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2006-08-23T00:00:00</t>
-        </is>
+        <v>862</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>794</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>6</v>
+        <v>968</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6920</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+        <v>6.92</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>6.92</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>6920</v>
+        <v>0</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>6920</v>
+        <v>0</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>862</v>
-      </c>
-      <c r="V18" s="2" t="n">
-        <v>794</v>
-      </c>
-      <c r="W18" s="2" t="n">
-        <v>968</v>
-      </c>
-      <c r="X18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="2" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="AB18" s="2" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="AC18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="6">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6">
         <f>IFERROR(AVERAGEIF(P640:P677,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH18" s="6">
+      <c r="V18" s="6">
         <f>IFERROR(AVERAGEIF(Q640:Q677,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI18" s="6">
+      <c r="W18" s="6">
         <f>IFERROR(AVERAGEIF(R640:R677,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ18" s="6">
+      <c r="X18" s="6">
         <f>IFERROR(AVERAGEIF(S640:S677,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK18" s="6">
+      <c r="Y18" s="6">
         <f>IFERROR(AVERAGEIF(T640:T677,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL18" s="6">
+      <c r="Z18" s="6">
         <f>IFERROR(AVERAGEIF(U640:U677,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM18" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AN18" s="2" t="inlineStr">
+      <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
+      <c r="AC18" s="3" t="n"/>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="n"/>
+      <c r="AH18" s="3" t="n"/>
+      <c r="AI18" s="3" t="n"/>
+      <c r="AJ18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO18" s="3" t="n"/>
-      <c r="AP18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ18" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR18" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP18" s="3" t="n"/>
+      <c r="AQ18" s="3" t="n"/>
+      <c r="AR18" s="3" t="n"/>
       <c r="AS18" s="3" t="n"/>
       <c r="AT18" s="3" t="n"/>
       <c r="AU18" s="3" t="n"/>
       <c r="AV18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW18" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" s="3" t="n"/>
+        <v>6820</v>
+      </c>
+      <c r="AW18" s="3" t="n"/>
+      <c r="AX18" s="3" t="n"/>
+      <c r="AY18" s="3" t="n"/>
+      <c r="AZ18" s="3" t="n"/>
+      <c r="BA18" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB18" s="3" t="n"/>
-      <c r="BC18" s="3" t="n"/>
+      <c r="BC18" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD18" s="3" t="n"/>
       <c r="BE18" s="3" t="n"/>
       <c r="BF18" s="3" t="n"/>
-      <c r="BG18" s="3" t="n"/>
-      <c r="BH18" s="2" t="n">
-        <v>6820</v>
-      </c>
-      <c r="BI18" s="3" t="n"/>
+      <c r="BG18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH18" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BJ18" s="3" t="n"/>
       <c r="BK18" s="3" t="n"/>
       <c r="BL18" s="3" t="n"/>
-      <c r="BM18" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM18" s="3" t="n"/>
       <c r="BN18" s="3" t="n"/>
-      <c r="BO18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO18" s="3" t="n"/>
       <c r="BP18" s="3" t="n"/>
       <c r="BQ18" s="3" t="n"/>
       <c r="BR18" s="3" t="n"/>
-      <c r="BS18" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT18" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU18" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
-      </c>
+      <c r="BS18" s="3" t="n"/>
+      <c r="BT18" s="3" t="n"/>
+      <c r="BU18" s="3" t="n"/>
       <c r="BV18" s="3" t="n"/>
       <c r="BW18" s="3" t="n"/>
       <c r="BX18" s="3" t="n"/>
@@ -5156,219 +4588,187 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
         <v>2611</v>
       </c>
+      <c r="C19" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="n">
-        <v>2057</v>
+        <v>1306</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>6600</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>6600</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1306</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2019-05-15T00:00:00</t>
-        </is>
+        <v>280</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>296</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>6</v>
+        <v>730</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+        <v>6.6</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>6.6</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>296</v>
-      </c>
-      <c r="W19" s="2" t="n">
-        <v>730</v>
-      </c>
-      <c r="X19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AB19" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="6">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6">
         <f>IFERROR(AVERAGEIF(P679:P716,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH19" s="6">
+      <c r="V19" s="6">
         <f>IFERROR(AVERAGEIF(Q679:Q716,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI19" s="6">
+      <c r="W19" s="6">
         <f>IFERROR(AVERAGEIF(R679:R716,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ19" s="6">
+      <c r="X19" s="6">
         <f>IFERROR(AVERAGEIF(S679:S716,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK19" s="6">
+      <c r="Y19" s="6">
         <f>IFERROR(AVERAGEIF(T679:T716,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL19" s="6">
+      <c r="Z19" s="6">
         <f>IFERROR(AVERAGEIF(U679:U716,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
-      <c r="AN19" s="2" t="inlineStr">
+      <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>2024-12-14T00:00:00</t>
         </is>
       </c>
+      <c r="AC19" s="3" t="n"/>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="n"/>
+      <c r="AH19" s="3" t="n"/>
+      <c r="AI19" s="3" t="n"/>
+      <c r="AJ19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO19" s="3" t="n"/>
-      <c r="AP19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ19" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR19" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP19" s="3" t="n"/>
+      <c r="AQ19" s="3" t="n"/>
+      <c r="AR19" s="3" t="n"/>
       <c r="AS19" s="3" t="n"/>
       <c r="AT19" s="3" t="n"/>
       <c r="AU19" s="3" t="n"/>
       <c r="AV19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW19" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" s="3" t="n"/>
+        <v>5221</v>
+      </c>
+      <c r="AW19" s="3" t="n"/>
+      <c r="AX19" s="3" t="n"/>
+      <c r="AY19" s="3" t="n"/>
+      <c r="AZ19" s="3" t="n"/>
+      <c r="BA19" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB19" s="3" t="n"/>
-      <c r="BC19" s="3" t="n"/>
+      <c r="BC19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD19" s="3" t="n"/>
       <c r="BE19" s="3" t="n"/>
       <c r="BF19" s="3" t="n"/>
-      <c r="BG19" s="3" t="n"/>
-      <c r="BH19" s="2" t="n">
-        <v>5221</v>
-      </c>
-      <c r="BI19" s="3" t="n"/>
+      <c r="BG19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH19" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BJ19" s="3" t="n"/>
       <c r="BK19" s="3" t="n"/>
       <c r="BL19" s="3" t="n"/>
-      <c r="BM19" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM19" s="3" t="n"/>
       <c r="BN19" s="3" t="n"/>
-      <c r="BO19" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO19" s="3" t="n"/>
       <c r="BP19" s="3" t="n"/>
       <c r="BQ19" s="3" t="n"/>
       <c r="BR19" s="3" t="n"/>
-      <c r="BS19" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT19" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU19" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
-      </c>
+      <c r="BS19" s="3" t="n"/>
+      <c r="BT19" s="3" t="n"/>
+      <c r="BU19" s="3" t="n"/>
       <c r="BV19" s="3" t="n"/>
       <c r="BW19" s="3" t="n"/>
       <c r="BX19" s="3" t="n"/>
@@ -5396,219 +4796,187 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
         <v>2611</v>
       </c>
+      <c r="C20" s="2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="n">
-        <v>2057</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3X400/230</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>6928</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>6928</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>6928</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2016-04-18T00:00:00</t>
-        </is>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6928</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+        <v>6.93</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>6.93</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>6928</v>
+        <v>0</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>6928</v>
+        <v>0</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AB20" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AC20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="6">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6">
         <f>IFERROR(AVERAGEIF(P718:P754,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH20" s="6">
+      <c r="V20" s="6">
         <f>IFERROR(AVERAGEIF(Q718:Q754,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI20" s="6">
+      <c r="W20" s="6">
         <f>IFERROR(AVERAGEIF(R718:R754,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ20" s="6">
+      <c r="X20" s="6">
         <f>IFERROR(AVERAGEIF(S718:S754,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK20" s="6">
+      <c r="Y20" s="6">
         <f>IFERROR(AVERAGEIF(T718:T754,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL20" s="6">
+      <c r="Z20" s="6">
         <f>IFERROR(AVERAGEIF(U718:U754,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM20" s="2" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>2025-11-26T00:00:00</t>
         </is>
       </c>
-      <c r="AN20" s="2" t="inlineStr">
+      <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>2025-11-26T00:00:00</t>
         </is>
       </c>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="n"/>
+      <c r="AH20" s="3" t="n"/>
+      <c r="AI20" s="3" t="n"/>
+      <c r="AJ20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO20" s="3" t="n"/>
-      <c r="AP20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ20" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR20" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP20" s="3" t="n"/>
+      <c r="AQ20" s="3" t="n"/>
+      <c r="AR20" s="3" t="n"/>
       <c r="AS20" s="3" t="n"/>
       <c r="AT20" s="3" t="n"/>
       <c r="AU20" s="3" t="n"/>
       <c r="AV20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW20" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" s="3" t="n"/>
+        <v>5210</v>
+      </c>
+      <c r="AW20" s="3" t="n"/>
+      <c r="AX20" s="3" t="n"/>
+      <c r="AY20" s="3" t="n"/>
+      <c r="AZ20" s="3" t="n"/>
+      <c r="BA20" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB20" s="3" t="n"/>
-      <c r="BC20" s="3" t="n"/>
+      <c r="BC20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD20" s="3" t="n"/>
       <c r="BE20" s="3" t="n"/>
       <c r="BF20" s="3" t="n"/>
-      <c r="BG20" s="3" t="n"/>
-      <c r="BH20" s="2" t="n">
-        <v>5210</v>
-      </c>
-      <c r="BI20" s="3" t="n"/>
+      <c r="BG20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH20" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Ossa de Montiel</t>
+        </is>
+      </c>
       <c r="BJ20" s="3" t="n"/>
       <c r="BK20" s="3" t="n"/>
       <c r="BL20" s="3" t="n"/>
-      <c r="BM20" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM20" s="3" t="n"/>
       <c r="BN20" s="3" t="n"/>
-      <c r="BO20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO20" s="3" t="n"/>
       <c r="BP20" s="3" t="n"/>
       <c r="BQ20" s="3" t="n"/>
       <c r="BR20" s="3" t="n"/>
-      <c r="BS20" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT20" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU20" s="2" t="inlineStr">
-        <is>
-          <t>Ossa de Montiel</t>
-        </is>
-      </c>
+      <c r="BS20" s="3" t="n"/>
+      <c r="BT20" s="3" t="n"/>
+      <c r="BU20" s="3" t="n"/>
       <c r="BV20" s="3" t="n"/>
       <c r="BW20" s="3" t="n"/>
       <c r="BX20" s="3" t="n"/>
@@ -5636,217 +5004,185 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>HIDROCANTÁBRICO DISTRIBUCIÓN ELÉCTRICA S.A.U</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
         <v>46190</v>
       </c>
+      <c r="C21" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="n">
-        <v>46214</v>
+        <v>5981</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>3X400</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>17330</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>10390</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>10390</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5981</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-20T00:00:00</t>
-        </is>
+        <v>2255</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>2126</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5</v>
+        <v>1600</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>17330</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17330</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
+        <v>10.39</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>10.39</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>10390</v>
+        <v>0</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>10390</v>
+        <v>0</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>2255</v>
-      </c>
-      <c r="V21" s="2" t="n">
-        <v>2126</v>
-      </c>
-      <c r="W21" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="X21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="2" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="AB21" s="2" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="AC21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="6">
+        <v>0</v>
+      </c>
+      <c r="U21" s="6">
         <f>IFERROR(AVERAGEIF(P756:P786,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH21" s="6">
+      <c r="V21" s="6">
         <f>IFERROR(AVERAGEIF(Q756:Q786,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI21" s="6">
+      <c r="W21" s="6">
         <f>IFERROR(AVERAGEIF(R756:R786,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ21" s="6">
+      <c r="X21" s="6">
         <f>IFERROR(AVERAGEIF(S756:S786,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK21" s="6">
+      <c r="Y21" s="6">
         <f>IFERROR(AVERAGEIF(T756:T786,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL21" s="6">
+      <c r="Z21" s="6">
         <f>IFERROR(AVERAGEIF(U756:U786,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM21" s="2" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="n"/>
-      <c r="AO21" s="2" t="inlineStr">
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>9999-12-31T00:00:00</t>
         </is>
       </c>
-      <c r="AP21" s="2" t="inlineStr">
+      <c r="AD21" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T00:00:00</t>
         </is>
       </c>
-      <c r="AQ21" s="2" t="inlineStr">
+      <c r="AE21" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AR21" s="2" t="inlineStr">
+      <c r="AF21" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
+      <c r="AG21" s="3" t="n"/>
+      <c r="AH21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n"/>
+      <c r="AJ21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="3" t="n"/>
+      <c r="AP21" s="3" t="n"/>
+      <c r="AQ21" s="3" t="n"/>
+      <c r="AR21" s="3" t="n"/>
       <c r="AS21" s="3" t="n"/>
-      <c r="AT21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT21" s="3" t="n"/>
       <c r="AU21" s="3" t="n"/>
       <c r="AV21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW21" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>4321</v>
+      </c>
+      <c r="AW21" s="3" t="n"/>
+      <c r="AX21" s="3" t="n"/>
+      <c r="AY21" s="3" t="n"/>
+      <c r="AZ21" s="3" t="n"/>
       <c r="BA21" s="3" t="n"/>
       <c r="BB21" s="3" t="n"/>
-      <c r="BC21" s="3" t="n"/>
+      <c r="BC21" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD21" s="3" t="n"/>
       <c r="BE21" s="3" t="n"/>
       <c r="BF21" s="3" t="n"/>
-      <c r="BG21" s="3" t="n"/>
-      <c r="BH21" s="2" t="n">
-        <v>4321</v>
-      </c>
-      <c r="BI21" s="3" t="n"/>
+      <c r="BG21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH21" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>RIBA-ROJA DE TURIA</t>
+        </is>
+      </c>
       <c r="BJ21" s="3" t="n"/>
       <c r="BK21" s="3" t="n"/>
       <c r="BL21" s="3" t="n"/>
       <c r="BM21" s="3" t="n"/>
       <c r="BN21" s="3" t="n"/>
-      <c r="BO21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO21" s="3" t="n"/>
       <c r="BP21" s="3" t="n"/>
       <c r="BQ21" s="3" t="n"/>
       <c r="BR21" s="3" t="n"/>
-      <c r="BS21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT21" s="2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="BU21" s="2" t="inlineStr">
-        <is>
-          <t>RIBA-ROJA DE TURIA</t>
-        </is>
-      </c>
+      <c r="BS21" s="3" t="n"/>
+      <c r="BT21" s="3" t="n"/>
+      <c r="BU21" s="3" t="n"/>
       <c r="BV21" s="3" t="n"/>
       <c r="BW21" s="3" t="n"/>
       <c r="BX21" s="3" t="n"/>
@@ -5874,217 +5210,185 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>HIDROCANTÁBRICO DISTRIBUCIÓN ELÉCTRICA S.A.U</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
         <v>46190</v>
       </c>
+      <c r="C22" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="n">
-        <v>46214</v>
+        <v>556</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3X400</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>9200</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>6930</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>6930</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>556</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2020-03-09T00:00:00</t>
-        </is>
+        <v>159</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>189</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5</v>
+        <v>208</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
+        <v>6.93</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>6.93</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>6930</v>
+        <v>0</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>6930</v>
+        <v>0</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="V22" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="W22" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="X22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AB22" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AC22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="6">
+        <v>0</v>
+      </c>
+      <c r="U22" s="6">
         <f>IFERROR(AVERAGEIF(P788:P818,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH22" s="6">
+      <c r="V22" s="6">
         <f>IFERROR(AVERAGEIF(Q788:Q818,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI22" s="6">
+      <c r="W22" s="6">
         <f>IFERROR(AVERAGEIF(R788:R818,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ22" s="6">
+      <c r="X22" s="6">
         <f>IFERROR(AVERAGEIF(S788:S818,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK22" s="6">
+      <c r="Y22" s="6">
         <f>IFERROR(AVERAGEIF(T788:T818,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL22" s="6">
+      <c r="Z22" s="6">
         <f>IFERROR(AVERAGEIF(U788:U818,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM22" s="2" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="n"/>
-      <c r="AO22" s="2" t="inlineStr">
+      <c r="AB22" s="3" t="n"/>
+      <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>9999-12-31T00:00:00</t>
         </is>
       </c>
-      <c r="AP22" s="2" t="inlineStr">
+      <c r="AD22" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T00:00:00</t>
         </is>
       </c>
-      <c r="AQ22" s="2" t="inlineStr">
+      <c r="AE22" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AR22" s="2" t="inlineStr">
+      <c r="AF22" s="2" t="inlineStr">
         <is>
           <t>NaN</t>
         </is>
       </c>
+      <c r="AG22" s="3" t="n"/>
+      <c r="AH22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n"/>
+      <c r="AJ22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AL22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3" t="n"/>
+      <c r="AP22" s="3" t="n"/>
+      <c r="AQ22" s="3" t="n"/>
+      <c r="AR22" s="3" t="n"/>
       <c r="AS22" s="3" t="n"/>
-      <c r="AT22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT22" s="3" t="n"/>
       <c r="AU22" s="3" t="n"/>
       <c r="AV22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW22" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AX22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>5210</v>
+      </c>
+      <c r="AW22" s="3" t="n"/>
+      <c r="AX22" s="3" t="n"/>
+      <c r="AY22" s="3" t="n"/>
+      <c r="AZ22" s="3" t="n"/>
       <c r="BA22" s="3" t="n"/>
       <c r="BB22" s="3" t="n"/>
-      <c r="BC22" s="3" t="n"/>
+      <c r="BC22" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD22" s="3" t="n"/>
       <c r="BE22" s="3" t="n"/>
       <c r="BF22" s="3" t="n"/>
-      <c r="BG22" s="3" t="n"/>
-      <c r="BH22" s="2" t="n">
-        <v>5210</v>
-      </c>
-      <c r="BI22" s="3" t="n"/>
+      <c r="BG22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH22" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>RIBA-ROJA DE TURIA</t>
+        </is>
+      </c>
       <c r="BJ22" s="3" t="n"/>
       <c r="BK22" s="3" t="n"/>
       <c r="BL22" s="3" t="n"/>
       <c r="BM22" s="3" t="n"/>
       <c r="BN22" s="3" t="n"/>
-      <c r="BO22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO22" s="3" t="n"/>
       <c r="BP22" s="3" t="n"/>
       <c r="BQ22" s="3" t="n"/>
       <c r="BR22" s="3" t="n"/>
-      <c r="BS22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT22" s="2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="BU22" s="2" t="inlineStr">
-        <is>
-          <t>RIBA-ROJA DE TURIA</t>
-        </is>
-      </c>
+      <c r="BS22" s="3" t="n"/>
+      <c r="BT22" s="3" t="n"/>
+      <c r="BU22" s="3" t="n"/>
       <c r="BV22" s="3" t="n"/>
       <c r="BW22" s="3" t="n"/>
       <c r="BX22" s="3" t="n"/>
@@ -6112,219 +5416,187 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>i-DE REDES ELÉCTRICAS INTELIGENTES, S.A.U</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
         <v>2003</v>
       </c>
+      <c r="C23" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2.0TD ML</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="n">
-        <v>2003</v>
+        <v>2163</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1X230</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2.0TD ML</t>
-        </is>
+        <v>6900</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>6900</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>6900</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2163</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1999-08-16T00:00:00</t>
-        </is>
+        <v>1314</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>380</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2</v>
+        <v>468</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+        <v>6.9</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>6.9</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="2" t="n">
-        <v>1314</v>
-      </c>
-      <c r="V23" s="2" t="n">
-        <v>380</v>
-      </c>
-      <c r="W23" s="2" t="n">
-        <v>468</v>
-      </c>
-      <c r="X23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AB23" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AC23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="6">
+        <v>0</v>
+      </c>
+      <c r="U23" s="6">
         <f>IFERROR(AVERAGEIF(P820:P857,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AH23" s="6">
+      <c r="V23" s="6">
         <f>IFERROR(AVERAGEIF(Q820:Q857,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AI23" s="6">
+      <c r="W23" s="6">
         <f>IFERROR(AVERAGEIF(R820:R857,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AJ23" s="6">
+      <c r="X23" s="6">
         <f>IFERROR(AVERAGEIF(S820:S857,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AK23" s="6">
+      <c r="Y23" s="6">
         <f>IFERROR(AVERAGEIF(T820:T857,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AL23" s="6">
+      <c r="Z23" s="6">
         <f>IFERROR(AVERAGEIF(U820:U857,"&gt;0"),0)</f>
         <v/>
       </c>
-      <c r="AM23" s="2" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>2025-12-10T00:00:00</t>
         </is>
       </c>
-      <c r="AN23" s="2" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>2025-12-10T00:00:00</t>
         </is>
       </c>
+      <c r="AC23" s="3" t="n"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T00:00:00</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="n"/>
+      <c r="AH23" s="3" t="n"/>
+      <c r="AI23" s="3" t="n"/>
+      <c r="AJ23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AL23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO23" s="3" t="n"/>
-      <c r="AP23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12T00:00:00</t>
-        </is>
-      </c>
-      <c r="AQ23" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AR23" s="2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
+      <c r="AP23" s="3" t="n"/>
+      <c r="AQ23" s="3" t="n"/>
+      <c r="AR23" s="3" t="n"/>
       <c r="AS23" s="3" t="n"/>
       <c r="AT23" s="3" t="n"/>
       <c r="AU23" s="3" t="n"/>
       <c r="AV23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW23" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="AX23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" s="3" t="n"/>
+        <v>9820</v>
+      </c>
+      <c r="AW23" s="3" t="n"/>
+      <c r="AX23" s="3" t="n"/>
+      <c r="AY23" s="3" t="n"/>
+      <c r="AZ23" s="3" t="n"/>
+      <c r="BA23" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="BB23" s="3" t="n"/>
-      <c r="BC23" s="3" t="n"/>
+      <c r="BC23" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD23" s="3" t="n"/>
       <c r="BE23" s="3" t="n"/>
       <c r="BF23" s="3" t="n"/>
-      <c r="BG23" s="3" t="n"/>
-      <c r="BH23" s="2" t="n">
-        <v>9820</v>
-      </c>
-      <c r="BI23" s="3" t="n"/>
+      <c r="BG23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BH23" s="2" t="inlineStr">
+        <is>
+          <t>ALBACETE</t>
+        </is>
+      </c>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
       <c r="BJ23" s="3" t="n"/>
       <c r="BK23" s="3" t="n"/>
       <c r="BL23" s="3" t="n"/>
-      <c r="BM23" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="BM23" s="3" t="n"/>
       <c r="BN23" s="3" t="n"/>
-      <c r="BO23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO23" s="3" t="n"/>
       <c r="BP23" s="3" t="n"/>
       <c r="BQ23" s="3" t="n"/>
       <c r="BR23" s="3" t="n"/>
-      <c r="BS23" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BT23" s="2" t="inlineStr">
-        <is>
-          <t>ALBACETE</t>
-        </is>
-      </c>
-      <c r="BU23" s="2" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
+      <c r="BS23" s="3" t="n"/>
+      <c r="BT23" s="3" t="n"/>
+      <c r="BU23" s="3" t="n"/>
       <c r="BV23" s="3" t="n"/>
       <c r="BW23" s="3" t="n"/>
       <c r="BX23" s="3" t="n"/>
@@ -6345,14 +5617,7 @@
       <c r="CM23" s="3" t="n"/>
       <c r="CN23" s="3" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" customFormat="1" s="5"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
